--- a/docs/chapter-graph-sample.xlsx
+++ b/docs/chapter-graph-sample.xlsx
@@ -918,7 +918,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="48" t="inlineStr">
         <is>
           <t>main05.01</t>
         </is>
@@ -928,7 +928,7 @@
           <t>닫힌 문 앞에서</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="C2" s="52" t="inlineStr">
         <is>
           <t>05</t>
         </is>
@@ -938,20 +938,20 @@
           <t>Main</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr">
+      <c r="E2" s="52" t="inlineStr">
         <is>
           <t>Story_ch05_01</t>
         </is>
       </c>
-      <c r="F2" s="4" t="n">
+      <c r="F2" s="52" t="n">
         <v>0</v>
       </c>
-      <c r="G2" s="4" t="n">
+      <c r="G2" s="52" t="n">
         <v>0</v>
       </c>
       <c r="H2" s="3" t="inlineStr"/>
-      <c r="I2" s="4" t="inlineStr"/>
-      <c r="J2" s="4" t="inlineStr"/>
+      <c r="I2" s="52" t="inlineStr"/>
+      <c r="J2" s="52" t="inlineStr"/>
       <c r="K2" s="5" t="inlineStr">
         <is>
           <t>챕터 진입점</t>
@@ -959,7 +959,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="48" t="inlineStr">
         <is>
           <t>main05.02</t>
         </is>
@@ -969,7 +969,7 @@
           <t>조용한 복도</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C3" s="52" t="inlineStr">
         <is>
           <t>05</t>
         </is>
@@ -979,24 +979,24 @@
           <t>Main</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="E3" s="52" t="inlineStr">
         <is>
           <t>Story_ch05_02</t>
         </is>
       </c>
-      <c r="F3" s="4" t="n">
+      <c r="F3" s="52" t="n">
         <v>220</v>
       </c>
-      <c r="G3" s="4" t="n">
+      <c r="G3" s="52" t="n">
         <v>0</v>
       </c>
       <c r="H3" s="3" t="inlineStr"/>
-      <c r="I3" s="4" t="inlineStr"/>
-      <c r="J3" s="4" t="inlineStr"/>
+      <c r="I3" s="52" t="inlineStr"/>
+      <c r="J3" s="52" t="inlineStr"/>
       <c r="K3" s="5" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="48" t="inlineStr">
         <is>
           <t>branch05.02A</t>
         </is>
@@ -1006,7 +1006,7 @@
           <t>라루의 제안</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" s="52" t="inlineStr">
         <is>
           <t>05A</t>
         </is>
@@ -1016,24 +1016,24 @@
           <t>Main</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="E4" s="52" t="inlineStr">
         <is>
           <t>Story_ch05_02A</t>
         </is>
       </c>
-      <c r="F4" s="4" t="n">
+      <c r="F4" s="52" t="n">
         <v>440</v>
       </c>
-      <c r="G4" s="4" t="n">
+      <c r="G4" s="52" t="n">
         <v>-120</v>
       </c>
       <c r="H4" s="3" t="inlineStr"/>
-      <c r="I4" s="4" t="inlineStr">
+      <c r="I4" s="52" t="inlineStr">
         <is>
           <t>신뢰높음</t>
         </is>
       </c>
-      <c r="J4" s="4" t="inlineStr"/>
+      <c r="J4" s="52" t="inlineStr"/>
       <c r="K4" s="5" t="inlineStr">
         <is>
           <t>신뢰 루트</t>
@@ -1041,7 +1041,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="48" t="inlineStr">
         <is>
           <t>main05.03</t>
         </is>
@@ -1051,7 +1051,7 @@
           <t>문 너머</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" s="52" t="inlineStr">
         <is>
           <t>06</t>
         </is>
@@ -1061,20 +1061,20 @@
           <t>Main</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E5" s="52" t="inlineStr">
         <is>
           <t>Story_ch05_03</t>
         </is>
       </c>
-      <c r="F5" s="4" t="n">
+      <c r="F5" s="52" t="n">
         <v>440</v>
       </c>
-      <c r="G5" s="4" t="n">
+      <c r="G5" s="52" t="n">
         <v>120</v>
       </c>
       <c r="H5" s="3" t="inlineStr"/>
-      <c r="I5" s="4" t="inlineStr"/>
-      <c r="J5" s="4" t="inlineStr"/>
+      <c r="I5" s="52" t="inlineStr"/>
+      <c r="J5" s="52" t="inlineStr"/>
       <c r="K5" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
@@ -1082,7 +1082,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="48" t="inlineStr">
         <is>
           <t>attach05.02s</t>
         </is>
@@ -1092,7 +1092,7 @@
           <t>샘플 섬 회상</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" s="52" t="inlineStr">
         <is>
           <t>★</t>
         </is>
@@ -1102,15 +1102,15 @@
           <t>Attachment</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="E6" s="52" t="inlineStr">
         <is>
           <t>Story_ch05_02_side</t>
         </is>
       </c>
-      <c r="F6" s="4" t="n">
+      <c r="F6" s="52" t="n">
         <v>220</v>
       </c>
-      <c r="G6" s="4" t="n">
+      <c r="G6" s="52" t="n">
         <v>170</v>
       </c>
       <c r="H6" s="3" t="inlineStr">
@@ -1118,8 +1118,8 @@
           <t>복도완료</t>
         </is>
       </c>
-      <c r="I6" s="4" t="inlineStr"/>
-      <c r="J6" s="4" t="inlineStr"/>
+      <c r="I6" s="52" t="inlineStr"/>
+      <c r="J6" s="52" t="inlineStr"/>
       <c r="K6" s="5" t="inlineStr">
         <is>
           <t>부착(사이드)</t>
@@ -1127,7 +1127,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="48" t="inlineStr">
         <is>
           <t>main05.end</t>
         </is>
@@ -1137,7 +1137,7 @@
           <t>선택의 밤</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C7" s="52" t="inlineStr">
         <is>
           <t>07</t>
         </is>
@@ -1147,20 +1147,20 @@
           <t>Main</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="E7" s="52" t="inlineStr">
         <is>
           <t>Story_ch05_end</t>
         </is>
       </c>
-      <c r="F7" s="4" t="n">
+      <c r="F7" s="52" t="n">
         <v>680</v>
       </c>
-      <c r="G7" s="4" t="n">
+      <c r="G7" s="52" t="n">
         <v>0</v>
       </c>
       <c r="H7" s="3" t="inlineStr"/>
-      <c r="I7" s="4" t="inlineStr"/>
-      <c r="J7" s="4" t="inlineStr">
+      <c r="I7" s="52" t="inlineStr"/>
+      <c r="J7" s="52" t="inlineStr">
         <is>
           <t>ch05_normal</t>
         </is>
@@ -1232,7 +1232,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="48" t="inlineStr">
         <is>
           <t>main05.01</t>
         </is>
@@ -1242,17 +1242,17 @@
           <t>main05.02</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr"/>
+      <c r="C2" s="52" t="inlineStr"/>
       <c r="D2" s="3" t="inlineStr"/>
-      <c r="E2" s="4" t="inlineStr">
+      <c r="E2" s="52" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr"/>
+      <c r="F2" s="52" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="48" t="inlineStr">
         <is>
           <t>main05.02</t>
         </is>
@@ -1262,7 +1262,7 @@
           <t>branch05.02A</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C3" s="52" t="inlineStr">
         <is>
           <t>라루의 제안을 듣는다</t>
         </is>
@@ -1272,19 +1272,19 @@
           <t>신뢰높음</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="E3" s="52" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="F3" s="52" t="inlineStr">
         <is>
           <t>신뢰가 부족하다</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="48" t="inlineStr">
         <is>
           <t>main05.02</t>
         </is>
@@ -1294,21 +1294,21 @@
           <t>main05.03</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" s="52" t="inlineStr">
         <is>
           <t>혼자 문을 연다</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr"/>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="E4" s="52" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr"/>
+      <c r="F4" s="52" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="48" t="inlineStr">
         <is>
           <t>branch05.02A</t>
         </is>
@@ -1318,17 +1318,17 @@
           <t>main05.03</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr"/>
+      <c r="C5" s="52" t="inlineStr"/>
       <c r="D5" s="3" t="inlineStr"/>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E5" s="52" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr"/>
+      <c r="F5" s="52" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="48" t="inlineStr">
         <is>
           <t>main05.03</t>
         </is>
@@ -1338,14 +1338,14 @@
           <t>main05.end</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr"/>
+      <c r="C6" s="52" t="inlineStr"/>
       <c r="D6" s="3" t="inlineStr"/>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="E6" s="52" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr"/>
+      <c r="F6" s="52" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -1394,7 +1394,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="52" t="inlineStr">
         <is>
           <t>신뢰높음</t>
         </is>
@@ -1404,14 +1404,14 @@
           <t>trust &gt;= 3</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="C2" s="52" t="inlineStr">
         <is>
           <t>라루를 신뢰하는 상태</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="52" t="inlineStr">
         <is>
           <t>분노누적</t>
         </is>
@@ -1421,14 +1421,14 @@
           <t>anger &gt;= 5</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C3" s="52" t="inlineStr">
         <is>
           <t>분노가 임계에 닿음</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="52" t="inlineStr">
         <is>
           <t>지쳐있음</t>
         </is>
@@ -1438,14 +1438,14 @@
           <t>fatigue &gt;= 4; anger &lt;= 2</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" s="52" t="inlineStr">
         <is>
           <t>피로하지만 화는 안 난 상태 (AND는 ; 로)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="52" t="inlineStr">
         <is>
           <t>복도완료</t>
         </is>
@@ -1455,7 +1455,7 @@
           <t>cleared:main05.02</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" s="52" t="inlineStr">
         <is>
           <t>해당 에피소드 클리어 여부</t>
         </is>
@@ -2339,12 +2339,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:C33"/>
+  <dimension ref="B1:C46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="84" customWidth="1" min="3" max="3"/>
+    <col width="86" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2355,305 +2355,446 @@
       </c>
     </row>
     <row r="2">
-      <c r="B2" s="44" t="inlineStr"/>
-      <c r="C2" s="45" t="inlineStr"/>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="B3" s="46" t="inlineStr">
         <is>
-          <t>변수는 두 층이다 (핵심)</t>
-        </is>
-      </c>
+          <t>이 파일의 구성</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="B4" s="44" t="inlineStr">
         <is>
-          <t>Tier 2 — 고정 스탯</t>
+          <t>에피소드 / 간선</t>
         </is>
       </c>
       <c r="C4" s="45" t="inlineStr">
         <is>
-          <t>'스탯' 시트의 2~5개. 정수. 세이브에 남고 챕터를 넘나든다. 그래프 해금·선택 가능을 정한다.</t>
+          <t>챕터 워크북의 본체. 노드와 관계·위치가 전부 여기서 정해진다.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="B5" s="44" t="inlineStr">
         <is>
-          <t>Tier 1 — 로컬</t>
+          <t>조건</t>
         </is>
       </c>
       <c r="C5" s="45" t="inlineStr">
         <is>
-          <t>기존 툴에서 만든 조건·선택지·set. 에피소드 안에서만 논다.</t>
+          <t>라벨↔조건식 표. 에피소드 엑셀은 라벨만 적는다.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="B6" s="44" t="inlineStr">
         <is>
-          <t>환산은 에피소드 끝 1회</t>
+          <t>스탯</t>
         </is>
       </c>
       <c r="C6" s="45" t="inlineStr">
         <is>
-          <t>엑셀의 '스탯변화'도 즉시 반영이 아니라 로컬 누적 → 끝에서 한 번 커밋. 그래서 중도 이탈·롤백·중간 로드가 안전하다.</t>
+          <t>읽기전용 미러(회색). 원천은 game.definition.json. 브리지가 왕복하는 Tier 2 키 목록이기도 하다.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="44" t="inlineStr"/>
-      <c r="C7" s="45" t="inlineStr"/>
+      <c r="B7" s="44" t="inlineStr">
+        <is>
+          <t>픽스처</t>
+        </is>
+      </c>
+      <c r="C7" s="45" t="inlineStr">
+        <is>
+          <t>재생루트 테스트용(주황). 내보내기에서 제외된다.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="B8" s="46" t="inlineStr">
-        <is>
-          <t>조건 행은 라인이 아니다</t>
+      <c r="B8" s="44" t="inlineStr">
+        <is>
+          <t>견본_에피소드</t>
+        </is>
+      </c>
+      <c r="C8" s="45" t="inlineStr">
+        <is>
+          <t>실제로는 episodes/{EpisodeId}.xlsx 로 파일이 분리된다.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="44" t="inlineStr">
-        <is>
-          <t>IF 행</t>
-        </is>
-      </c>
-      <c r="C9" s="45" t="inlineStr">
-        <is>
-          <t>LineId 없음. 연출·세이브 타깃이 아니다. 조건라벨 + IN + OUT만 적는다.</t>
-        </is>
-      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="B10" s="44" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="C10" s="45" t="inlineStr">
-        <is>
-          <t>조건이 참일 때 진행할 구간의 시작 인덱스.</t>
-        </is>
-      </c>
+      <c r="B10" s="46" t="inlineStr">
+        <is>
+          <t>변수는 두 층이다 (핵심)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="B11" s="44" t="inlineStr">
         <is>
-          <t>OUT</t>
+          <t>Tier 2 — 고정 스탯</t>
         </is>
       </c>
       <c r="C11" s="45" t="inlineStr">
         <is>
-          <t>구간의 끝 경계. 이 인덱스는 구간에 포함되지 않는다.</t>
+          <t>'스탯' 시트의 2~5개. 정수. 세이브에 남고 챕터를 넘나든다. 그래프의 해금·선택 가능을 정한다.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="44" t="inlineStr">
         <is>
-          <t>구간 재사용 금지</t>
+          <t>Tier 1 — 로컬</t>
         </is>
       </c>
       <c r="C12" s="45" t="inlineStr">
         <is>
-          <t>한 구간은 한 조건의 소유. 둘이 가리키면 검증 오류(복제되면 LineId 유일성이 깨진다).</t>
+          <t>기존 툴에서 만든 조건·선택지·set. 에피소드 안에서만 논다. 저장되지 않는다.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="44" t="inlineStr"/>
-      <c r="C13" s="45" t="inlineStr"/>
+      <c r="B13" s="44" t="inlineStr">
+        <is>
+          <t>환산은 에피소드 끝 1회</t>
+        </is>
+      </c>
+      <c r="C13" s="45" t="inlineStr">
+        <is>
+          <t>엑셀의 '스탯변화'도 즉시 반영이 아니라 로컬 누적 → 끝에서 한 번 커밋. 그래서 중도 이탈·롤백·중간 로드가 안전하다.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="B14" s="46" t="inlineStr">
-        <is>
-          <t>인덱스는 10·20·30 방식</t>
-        </is>
-      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="B15" s="44" t="inlineStr">
-        <is>
-          <t>왜</t>
-        </is>
-      </c>
-      <c r="C15" s="45" t="inlineStr">
-        <is>
-          <t>사이에 말을 넣으려면 15를 적으면 된다. 행을 아무리 삽입해도 IN/OUT 참조가 밀리지 않는다.</t>
-        </is>
-      </c>
+      <c r="B15" s="46" t="inlineStr">
+        <is>
+          <t>그래프 뷰는 읽기전용이다</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="B16" s="44" t="inlineStr">
         <is>
-          <t>간격이 다 차면</t>
+          <t>위치</t>
         </is>
       </c>
       <c r="C16" s="45" t="inlineStr">
         <is>
-          <t>툴이 자동 재번호하지 않는다. '간격 부족' 경고만 내고 사람이 재번호한다.</t>
+          <t>'에피소드' 시트의 X·Y 열이 노드 위치를 정한다. 뷰에서 드래그로 옮길 수 없다.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="44" t="inlineStr"/>
-      <c r="C17" s="45" t="inlineStr"/>
+      <c r="B17" s="44" t="inlineStr">
+        <is>
+          <t>관계</t>
+        </is>
+      </c>
+      <c r="C17" s="45" t="inlineStr">
+        <is>
+          <t>'간선' 시트가 정한다. 선택지 라벨이 비면 분기 없는 일반 진행이다.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="B18" s="46" t="inlineStr">
-        <is>
-          <t>선택지</t>
-        </is>
-      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="B19" s="44" t="inlineStr">
-        <is>
-          <t>맨 끝 1개</t>
-        </is>
-      </c>
-      <c r="C19" s="45" t="inlineStr">
-        <is>
-          <t>CHOICE 블록은 파일 맨 끝에 0개 또는 1개. 중간 선택지는 없다.</t>
-        </is>
-      </c>
+      <c r="B19" s="46" t="inlineStr">
+        <is>
+          <t>조건 문법 (한 셀, AND는 ; 로 구분)</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="B20" s="44" t="inlineStr">
         <is>
-          <t>라벨·선택조건</t>
+          <t>trust &gt;= 3</t>
         </is>
       </c>
       <c r="C20" s="45" t="inlineStr">
         <is>
-          <t>엑셀 소유. 단 도착 에피소드는 '간선' 시트가 원천이다.</t>
+          <t>스탯 비교. &gt;= &lt;= == != 네 가지. 값은 정수만.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="B21" s="44" t="inlineStr">
         <is>
-          <t>선택지는 라인이다</t>
+          <t>cleared:main05.02</t>
         </is>
       </c>
       <c r="C21" s="45" t="inlineStr">
         <is>
-          <t>CHOICE/OPTION은 LineId를 받아 연출·세이브 타깃이 될 수 있다.</t>
+          <t>해당 에피소드 클리어 여부.</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="44" t="inlineStr"/>
-      <c r="C22" s="45" t="inlineStr"/>
+      <c r="B22" s="44" t="inlineStr">
+        <is>
+          <t>미등록 스탯키</t>
+        </is>
+      </c>
+      <c r="C22" s="45" t="inlineStr">
+        <is>
+          <t>오류다. 오타를 자동 교정하지 않는다.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
-      <c r="B23" s="46" t="inlineStr">
-        <is>
-          <t>⚠ 이것이 없으면 전부 장식이다</t>
-        </is>
-      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="B24" s="44" t="inlineStr">
-        <is>
-          <t>YarnVariableBridge</t>
-        </is>
-      </c>
-      <c r="C24" s="45" t="inlineStr">
-        <is>
-          <t>런타임에서 이 브리지가 아직 생성되지 않아, 대사에서 바꾼 값이 에피소드 해금에 반영되지 않는다. 지시서 G9(런타임 U9)를 병행할 것.</t>
+      <c r="B24" s="46" t="inlineStr">
+        <is>
+          <t>인덱스는 10·20·30 방식</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="B25" s="44" t="inlineStr">
+        <is>
+          <t>왜</t>
+        </is>
+      </c>
+      <c r="C25" s="45" t="inlineStr">
+        <is>
+          <t>사이에 말을 넣으려면 15를 적으면 된다. 행을 아무리 삽입해도 IN/OUT 참조가 밀리지 않는다.</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="46" t="inlineStr">
-        <is>
-          <t>구간은 INPUT/OUT 태그로 감싼다</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr"/>
+      <c r="B26" s="44" t="inlineStr">
+        <is>
+          <t>간격이 다 차면</t>
+        </is>
+      </c>
+      <c r="C26" s="45" t="inlineStr">
+        <is>
+          <t>툴이 자동 재번호하지 않는다. '간격 부족' 경고만 내고 사람이 재번호한다.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
-      <c r="B27" s="44" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="C27" s="45" t="inlineStr">
-        <is>
-          <t>IF 행과 OPTION 행에 붙는다. 들어갈 구간의 인덱스.</t>
-        </is>
-      </c>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="B28" s="44" t="inlineStr">
-        <is>
-          <t>INPUT 태그</t>
-        </is>
-      </c>
-      <c r="C28" s="45" t="inlineStr">
-        <is>
-          <t>구간 첫 줄에 붙는다. IN이 가리키는 대상.</t>
-        </is>
-      </c>
+      <c r="B28" s="46" t="inlineStr">
+        <is>
+          <t>구간은 INPUT / OUT 태그로 감싼다</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="B29" s="44" t="inlineStr">
         <is>
-          <t>OUT 태그</t>
+          <t>IF 행</t>
         </is>
       </c>
       <c r="C29" s="45" t="inlineStr">
         <is>
-          <t>구간 마지막 줄에 붙는다. 값은 나갈 목적지 인덱스 또는 END.</t>
+          <t>LineId가 없다. 라인이 아니므로 연출·세이브 타깃이 아니다. 조건라벨과 IN만 적는다.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="B30" s="44" t="inlineStr">
         <is>
-          <t>짝은 강제</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="C30" s="45" t="inlineStr">
         <is>
-          <t>INPUT이 있으면 그 아래 OUT이 반드시 있어야 한다. 없으면 검증 오류.</t>
+          <t>IF 행과 OPTION 행에 붙는다. 들어갈 구간의 시작 인덱스.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="B31" s="44" t="inlineStr">
         <is>
-          <t>구간 = 양끝 포함</t>
+          <t>INPUT 태그</t>
         </is>
       </c>
       <c r="C31" s="45" t="inlineStr">
         <is>
-          <t>INPUT 행부터 OUT 행까지 전부 구간이다.</t>
+          <t>구간의 첫 줄에 붙는다. IN이 가리키는 대상이다.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="B32" s="44" t="inlineStr">
         <is>
-          <t>중첩 금지 (v1)</t>
+          <t>OUT 태그</t>
         </is>
       </c>
       <c r="C32" s="45" t="inlineStr">
         <is>
-          <t>구간 안에 또 IN이 있으면 오류. 마스터 플랜의 중첩 조건 비범위와 같은 선.</t>
+          <t>구간의 마지막 줄에 붙는다. 값은 '나갈 목적지 인덱스' 또는 END다. ※ 구간의 끝 경계를 표시하는 숫자가 아니라 목적지다.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="B33" s="44" t="inlineStr">
         <is>
+          <t>구간 = 양끝 포함</t>
+        </is>
+      </c>
+      <c r="C33" s="45" t="inlineStr">
+        <is>
+          <t>INPUT 행부터 OUT 행까지 전부가 구간이다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="44" t="inlineStr">
+        <is>
+          <t>짝은 강제</t>
+        </is>
+      </c>
+      <c r="C34" s="45" t="inlineStr">
+        <is>
+          <t>INPUT이 있으면 그 아래에 반드시 OUT이 있어야 한다. 없으면 검증 오류.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="44" t="inlineStr">
+        <is>
+          <t>구간 재사용 금지</t>
+        </is>
+      </c>
+      <c r="C35" s="45" t="inlineStr">
+        <is>
+          <t>한 구간은 한 진입점의 소유다. 둘 이상이 가리키면 검증 오류 (평평화 시 복제되어 LineId 유일성이 깨진다).</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="44" t="inlineStr">
+        <is>
+          <t>중첩 금지 (v1)</t>
+        </is>
+      </c>
+      <c r="C36" s="45" t="inlineStr">
+        <is>
+          <t>구간 안에 또 IN이 있으면 오류. 엑셀의 인덱스·태그 모델로는 중첩의 경계가 모호해지기 때문이다 — 하위 툴의 지원 여부와 무관한 이 규격 자체의 제약이다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" s="44" t="inlineStr">
+        <is>
           <t>OUT은 선언이다</t>
         </is>
       </c>
-      <c r="C33" s="45" t="inlineStr">
-        <is>
-          <t>Yarn에 노드 내 goto가 없다. 평평화하면 자연히 그리로 흐르는지 검증기가 대조한다.</t>
+      <c r="C37" s="45" t="inlineStr">
+        <is>
+          <t>Yarn에 노드 안의 줄 단위 goto가 없다. 평평화하면 자연히 그리로 흐르는지를 검증기가 대조한다. 손으로 적은 숫자가 곧 기대값이고 툴이 그것을 검사한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" t="inlineStr"/>
+      <c r="C38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="B39" s="46" t="inlineStr">
+        <is>
+          <t>선택지</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="B40" s="44" t="inlineStr">
+        <is>
+          <t>맨 끝 1개</t>
+        </is>
+      </c>
+      <c r="C40" s="45" t="inlineStr">
+        <is>
+          <t>CHOICE 블록은 파일 맨 끝에 0개 또는 1개. 중간 선택지는 없다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="44" t="inlineStr">
+        <is>
+          <t>라벨·선택조건</t>
+        </is>
+      </c>
+      <c r="C41" s="45" t="inlineStr">
+        <is>
+          <t>엑셀 소유. 단 도착 에피소드는 '간선' 시트가 원천이다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="44" t="inlineStr">
+        <is>
+          <t>선택지는 라인이다</t>
+        </is>
+      </c>
+      <c r="C42" s="45" t="inlineStr">
+        <is>
+          <t>CHOICE/OPTION은 LineId를 받아 연출·세이브 타깃이 될 수 있다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" s="44" t="inlineStr">
+        <is>
+          <t>OPTION도 IN을 갖는다</t>
+        </is>
+      </c>
+      <c r="C43" s="45" t="inlineStr">
+        <is>
+          <t>조건뿐 아니라 선택지 옵션도 구간으로 들어간다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" t="inlineStr"/>
+      <c r="C44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="B45" s="46" t="inlineStr">
+        <is>
+          <t>⚠ 이것이 없으면 전부 장식이다</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="B46" s="44" t="inlineStr">
+        <is>
+          <t>YarnVariableBridge</t>
+        </is>
+      </c>
+      <c r="C46" s="45" t="inlineStr">
+        <is>
+          <t>런타임에서 이 브리지가 생성되지 않아, 대사에서 바꾼 값이 에피소드 해금에 반영되지 않는다. 지시서 G9-a(런타임 U9)를 병행할 것.</t>
         </is>
       </c>
     </row>

--- a/docs/chapter-graph-sample.xlsx
+++ b/docs/chapter-graph-sample.xlsx
@@ -2251,6 +2251,7 @@
         </is>
       </c>
     </row>
+    <row r="16"/>
     <row r="17">
       <c r="C17" s="8" t="inlineStr">
         <is>
@@ -2339,7 +2340,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:C46"/>
+  <dimension ref="A1:C46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -2354,17 +2355,13 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-    </row>
+    <row r="2"/>
     <row r="3">
       <c r="B3" s="46" t="inlineStr">
         <is>
           <t>이 파일의 구성</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="B4" s="44" t="inlineStr">
@@ -2426,17 +2423,13 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-    </row>
+    <row r="9"/>
     <row r="10">
       <c r="B10" s="46" t="inlineStr">
         <is>
           <t>변수는 두 층이다 (핵심)</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="B11" s="44" t="inlineStr">
@@ -2474,17 +2467,13 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-    </row>
+    <row r="14"/>
     <row r="15">
       <c r="B15" s="46" t="inlineStr">
         <is>
           <t>그래프 뷰는 읽기전용이다</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="B16" s="44" t="inlineStr">
@@ -2510,17 +2499,13 @@
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
-    </row>
+    <row r="18"/>
     <row r="19">
       <c r="B19" s="46" t="inlineStr">
         <is>
           <t>조건 문법 (한 셀, AND는 ; 로 구분)</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="B20" s="44" t="inlineStr">
@@ -2530,7 +2515,7 @@
       </c>
       <c r="C20" s="45" t="inlineStr">
         <is>
-          <t>스탯 비교. &gt;= &lt;= == != 네 가지. 값은 정수만.</t>
+          <t>스탯 비교. &gt;= &lt;= == 세 가지. 값은 정수만. (!= 는 런타임 평가 지원이 확인될 때까지 비범위)</t>
         </is>
       </c>
     </row>
@@ -2558,17 +2543,13 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="B23" t="inlineStr"/>
-      <c r="C23" t="inlineStr"/>
-    </row>
+    <row r="23"/>
     <row r="24">
       <c r="B24" s="46" t="inlineStr">
         <is>
           <t>인덱스는 10·20·30 방식</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="B25" s="44" t="inlineStr">
@@ -2594,17 +2575,13 @@
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="B27" t="inlineStr"/>
-      <c r="C27" t="inlineStr"/>
-    </row>
+    <row r="27"/>
     <row r="28">
       <c r="B28" s="46" t="inlineStr">
         <is>
           <t>구간은 INPUT / OUT 태그로 감싼다</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="B29" s="44" t="inlineStr">
@@ -2714,17 +2691,13 @@
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="B38" t="inlineStr"/>
-      <c r="C38" t="inlineStr"/>
-    </row>
+    <row r="38"/>
     <row r="39">
       <c r="B39" s="46" t="inlineStr">
         <is>
           <t>선택지</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="B40" s="44" t="inlineStr">
@@ -2774,17 +2747,13 @@
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="B44" t="inlineStr"/>
-      <c r="C44" t="inlineStr"/>
-    </row>
+    <row r="44"/>
     <row r="45">
       <c r="B45" s="46" t="inlineStr">
         <is>
           <t>⚠ 이것이 없으면 전부 장식이다</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="B46" s="44" t="inlineStr">

--- a/docs/chapter-graph-sample.xlsx
+++ b/docs/chapter-graph-sample.xlsx
@@ -14,6 +14,7 @@
     <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="픽스처" sheetId="5" r:id="rId5"/>
     <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="견본_에피소드 main05.02" sheetId="6" r:id="rId6"/>
     <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="규격 안내" sheetId="7" r:id="rId7"/>
+    <x:sheet name="선택지" sheetId="8" r:id="rId11"/>
   </x:sheets>
   <x:definedNames>
     <x:definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">에피소드!$A$1:$J$7</x:definedName>
@@ -27,9 +28,6 @@
 <x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:si>
     <x:t>스탯변화</x:t>
-  </x:si>
-  <x:si>
-    <x:t>선택지</x:t>
   </x:si>
   <x:si>
     <x:t>스탯</x:t>
@@ -62,6 +60,9 @@
     <x:t>⚠ 읽기전용 미러 — 원천은 game.definition.json. 브리지가 왕복하는 Tier 2 키 목록이기도 하다(2~5개).</x:t>
   </x:si>
   <x:si>
+    <x:t>챕터·에피소드 그래프 엑셀 규격 v5 (2026-08-16) — 실물 견본</x:t>
+  </x:si>
+  <x:si>
     <x:t>재생루트 테스트용 — 임시 제거됨(2026-08-16). 시트가 있으면 여전히 읽고, 내보내기에서는 제외된다.</x:t>
   </x:si>
   <x:si>
@@ -80,7 +81,43 @@
     <x:t>대본(에피소드 워크북)의 인덱스는 그대로 10·20·30 방식이다. 챕터 시트의 표시용 인덱스만 없앴다.</x:t>
   </x:si>
   <x:si>
-    <x:t>챕터·에피소드 그래프 엑셀 규격 v5 (2026-08-16) — 실물 견본</x:t>
+    <x:t>출발</x:t>
+  </x:si>
+  <x:si>
+    <x:t>도착</x:t>
+  </x:si>
+  <x:si>
+    <x:t>인덱스</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대본</x:t>
+  </x:si>
+  <x:si>
+    <x:t>메모</x:t>
+  </x:si>
+  <x:si>
+    <x:t>main05.01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>main05.02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>branch05.02A</x:t>
+  </x:si>
+  <x:si>
+    <x:t>라루의 제안을 듣는다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>main05.03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>혼자 문을 연다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>main05.end</x:t>
+  </x:si>
+  <x:si>
+    <x:t>선택지수</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1738,7 +1775,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D1" s="99" t="s">
-        <x:v>1</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="E1" s="99" t="inlineStr">
         <x:is>
@@ -1768,7 +1805,9 @@
         </x:is>
       </x:c>
       <x:c r="C2" s="104"/>
-      <x:c r="D2" s="102"/>
+      <x:c r="D2" s="102">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="E2" s="101"/>
       <x:c r="F2" s="102" t="inlineStr">
         <x:is>
@@ -1789,10 +1828,8 @@
         </x:is>
       </x:c>
       <x:c r="C3" s="104"/>
-      <x:c r="D3" s="102" t="inlineStr">
-        <x:is>
-          <x:t>라루의 제안을 듣는다</x:t>
-        </x:is>
+      <x:c r="D3" s="102">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E3" s="101" t="inlineStr">
         <x:is>
@@ -1822,10 +1859,8 @@
         </x:is>
       </x:c>
       <x:c r="C4" s="104"/>
-      <x:c r="D4" s="102" t="inlineStr">
-        <x:is>
-          <x:t>혼자 문을 연다</x:t>
-        </x:is>
+      <x:c r="D4" s="102">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E4" s="101"/>
       <x:c r="F4" s="102" t="inlineStr">
@@ -1847,7 +1882,9 @@
         </x:is>
       </x:c>
       <x:c r="C5" s="104"/>
-      <x:c r="D5" s="102"/>
+      <x:c r="D5" s="102">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="E5" s="101"/>
       <x:c r="F5" s="102" t="inlineStr">
         <x:is>
@@ -1868,7 +1905,9 @@
         </x:is>
       </x:c>
       <x:c r="C6" s="104"/>
-      <x:c r="D6" s="102"/>
+      <x:c r="D6" s="102">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="E6" s="101"/>
       <x:c r="F6" s="102" t="inlineStr">
         <x:is>
@@ -1878,13 +1917,17 @@
       <x:c r="G6" s="102"/>
     </x:row>
   </x:sheetData>
-  <x:dataValidations count="2">
+  <x:dataValidations count="3">
     <x:dataValidation type="list" errorStyle="stop" operator="between" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="" error="" promptTitle="" prompt="" sqref="E2:E200">
       <x:formula1>='조건'!$A$2:$A$200</x:formula1>
       <x:formula2/>
     </x:dataValidation>
     <x:dataValidation type="list" errorStyle="stop" operator="between" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="" error="" promptTitle="" prompt="" sqref="F2:F200">
       <x:formula1>"TRUE,FALSE"</x:formula1>
+      <x:formula2/>
+    </x:dataValidation>
+    <x:dataValidation type="list" errorStyle="stop" operator="between" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="" error="" promptTitle="" prompt="" sqref="D2:D200">
+      <x:formula1>"1,2,3"</x:formula1>
       <x:formula2/>
     </x:dataValidation>
   </x:dataValidations>
@@ -1917,13 +1960,13 @@
         </x:is>
       </x:c>
       <x:c r="B1" s="105" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C1" s="105" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C1" s="105" t="s">
+      <x:c r="D1" s="105" t="s">
         <x:v>3</x:v>
-      </x:c>
-      <x:c r="D1" s="105" t="s">
-        <x:v>4</x:v>
       </x:c>
       <x:c r="E1" s="105" t="inlineStr">
         <x:is>
@@ -1943,13 +1986,13 @@
         </x:is>
       </x:c>
       <x:c r="B2" s="101" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C2" s="101" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="C2" s="101" t="s">
+      <x:c r="D2" s="101" t="s">
         <x:v>6</x:v>
-      </x:c>
-      <x:c r="D2" s="101" t="s">
-        <x:v>7</x:v>
       </x:c>
       <x:c r="E2" s="102" t="inlineStr">
         <x:is>
@@ -1964,13 +2007,13 @@
         </x:is>
       </x:c>
       <x:c r="B3" s="101" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C3" s="101" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D3" s="101" t="s">
         <x:v>8</x:v>
-      </x:c>
-      <x:c r="C3" s="101" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D3" s="101" t="s">
-        <x:v>9</x:v>
       </x:c>
       <x:c r="E3" s="102" t="inlineStr">
         <x:is>
@@ -2081,11 +2124,11 @@
         </x:is>
       </x:c>
       <x:c r="F1" s="107" t="s">
-        <x:v>10</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="G1" s="10"/>
       <x:c r="H1" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:8">
@@ -2938,7 +2981,7 @@
   <x:sheetData>
     <x:row r="1" spans="1:3">
       <x:c r="B1" s="43" t="s">
-        <x:v>18</x:v>
+        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:3">
@@ -3343,4 +3386,105 @@
   <x:headerFooter/>
   <x:tableParts count="0"/>
 </x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
+  <x:sheetPr>
+    <x:outlinePr summaryBelow="1" summaryRight="1"/>
+  </x:sheetPr>
+  <x:dimension ref="A1:E6"/>
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:sheetData>
+    <x:row r="1" spans="1:5">
+      <x:c r="A1" s="107" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B1" s="107" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C1" s="107" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="D1" s="107" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="E1" s="107" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:5">
+      <x:c r="A2" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="B2" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C2" s="0">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:5">
+      <x:c r="A3" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="B3" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C3" s="0">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D3" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:5">
+      <x:c r="A4" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="B4" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C4" s="0">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="D4" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="1:5">
+      <x:c r="A5" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B5" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C5" s="0">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:5">
+      <x:c r="A6" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B6" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C6" s="0">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:dataValidations count="1">
+    <x:dataValidation type="list" errorStyle="stop" operator="between" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="" error="" promptTitle="" prompt="" sqref="A2:B200">
+      <x:formula1>='에피소드'!$A$2:$A$200</x:formula1>
+      <x:formula2/>
+    </x:dataValidation>
+  </x:dataValidations>
+  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
+  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
+  <x:headerFooter/>
+  <x:tableParts count="0"/>
+</x:worksheet>
 </file>
--- a/docs/chapter-graph-sample.xlsx
+++ b/docs/chapter-graph-sample.xlsx
@@ -28,6 +28,9 @@
 <x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:si>
     <x:t>스탯변화</x:t>
+  </x:si>
+  <x:si>
+    <x:t>선택지수</x:t>
   </x:si>
   <x:si>
     <x:t>스탯</x:t>
@@ -84,9 +87,6 @@
     <x:t>출발</x:t>
   </x:si>
   <x:si>
-    <x:t>도착</x:t>
-  </x:si>
-  <x:si>
     <x:t>인덱스</x:t>
   </x:si>
   <x:si>
@@ -114,10 +114,7 @@
     <x:t>혼자 문을 연다</x:t>
   </x:si>
   <x:si>
-    <x:t>main05.end</x:t>
-  </x:si>
-  <x:si>
-    <x:t>선택지수</x:t>
+    <x:t>선택지</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1503,6 +1500,9 @@
           <x:t>메모</x:t>
         </x:is>
       </x:c>
+      <x:c r="K1" s="107" t="s">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="2" spans="1:11">
       <x:c r="A2" s="100" t="inlineStr">
@@ -1539,6 +1539,9 @@
           <x:t>챕터 진입점</x:t>
         </x:is>
       </x:c>
+      <x:c r="K2" s="0">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="3" spans="1:11">
       <x:c r="A3" s="100" t="inlineStr">
@@ -1571,6 +1574,9 @@
       <x:c r="H3" s="102"/>
       <x:c r="I3" s="102"/>
       <x:c r="J3" s="103"/>
+      <x:c r="K3" s="0">
+        <x:v>2</x:v>
+      </x:c>
     </x:row>
     <x:row r="4" spans="1:11">
       <x:c r="A4" s="100" t="inlineStr">
@@ -1610,6 +1616,9 @@
         <x:is>
           <x:t>신뢰 루트</x:t>
         </x:is>
+      </x:c>
+      <x:c r="K4" s="0">
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:11">
@@ -1647,6 +1656,9 @@
           <x:t xml:space="preserve"> </x:t>
         </x:is>
       </x:c>
+      <x:c r="K5" s="0">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="6" spans="1:11">
       <x:c r="A6" s="100" t="inlineStr">
@@ -1687,6 +1699,9 @@
           <x:t>부착(사이드)</x:t>
         </x:is>
       </x:c>
+      <x:c r="K6" s="0">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="7" spans="1:11">
       <x:c r="A7" s="100" t="inlineStr">
@@ -1726,6 +1741,9 @@
         <x:is>
           <x:t>엔딩 후보</x:t>
         </x:is>
+      </x:c>
+      <x:c r="K7" s="0">
+        <x:v>1</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1775,7 +1793,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D1" s="99" t="s">
-        <x:v>30</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E1" s="99" t="inlineStr">
         <x:is>
@@ -1806,7 +1824,7 @@
       </x:c>
       <x:c r="C2" s="104"/>
       <x:c r="D2" s="102">
-        <x:v>1</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E2" s="101"/>
       <x:c r="F2" s="102" t="inlineStr">
@@ -1829,7 +1847,7 @@
       </x:c>
       <x:c r="C3" s="104"/>
       <x:c r="D3" s="102">
-        <x:v>1</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E3" s="101" t="inlineStr">
         <x:is>
@@ -1860,7 +1878,7 @@
       </x:c>
       <x:c r="C4" s="104"/>
       <x:c r="D4" s="102">
-        <x:v>1</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="E4" s="101"/>
       <x:c r="F4" s="102" t="inlineStr">
@@ -1883,7 +1901,7 @@
       </x:c>
       <x:c r="C5" s="104"/>
       <x:c r="D5" s="102">
-        <x:v>1</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E5" s="101"/>
       <x:c r="F5" s="102" t="inlineStr">
@@ -1906,7 +1924,7 @@
       </x:c>
       <x:c r="C6" s="104"/>
       <x:c r="D6" s="102">
-        <x:v>1</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E6" s="101"/>
       <x:c r="F6" s="102" t="inlineStr">
@@ -1926,8 +1944,8 @@
       <x:formula1>"TRUE,FALSE"</x:formula1>
       <x:formula2/>
     </x:dataValidation>
-    <x:dataValidation type="list" errorStyle="stop" operator="between" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="" error="" promptTitle="" prompt="" sqref="D2:D200">
-      <x:formula1>"1,2,3"</x:formula1>
+    <x:dataValidation type="list" errorStyle="stop" operator="between" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="0" errorTitle="" error="" promptTitle="" prompt="" sqref="D2:D200">
+      <x:formula1>='선택지'!$B$2:$B$200</x:formula1>
       <x:formula2/>
     </x:dataValidation>
   </x:dataValidations>
@@ -1960,13 +1978,13 @@
         </x:is>
       </x:c>
       <x:c r="B1" s="105" t="s">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C1" s="105" t="s">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D1" s="105" t="s">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E1" s="105" t="inlineStr">
         <x:is>
@@ -1986,13 +2004,13 @@
         </x:is>
       </x:c>
       <x:c r="B2" s="101" t="s">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C2" s="101" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D2" s="101" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="E2" s="102" t="inlineStr">
         <x:is>
@@ -2007,13 +2025,13 @@
         </x:is>
       </x:c>
       <x:c r="B3" s="101" t="s">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C3" s="101" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D3" s="101" t="s">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E3" s="102" t="inlineStr">
         <x:is>
@@ -2124,11 +2142,11 @@
         </x:is>
       </x:c>
       <x:c r="F1" s="107" t="s">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="G1" s="10"/>
       <x:c r="H1" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:8">
@@ -2981,7 +2999,7 @@
   <x:sheetData>
     <x:row r="1" spans="1:3">
       <x:c r="B1" s="43" t="s">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:3">
@@ -3034,7 +3052,7 @@
         </x:is>
       </x:c>
       <x:c r="C7" s="45" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:3">
@@ -3118,12 +3136,12 @@
         </x:is>
       </x:c>
       <x:c r="C17" s="166" t="s">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="B19" s="46" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:3">
@@ -3133,7 +3151,7 @@
         </x:is>
       </x:c>
       <x:c r="C20" s="45" t="s">
-        <x:v>15</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:3">
@@ -3162,7 +3180,7 @@
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="B24" s="46" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:3">
@@ -3172,7 +3190,7 @@
         </x:is>
       </x:c>
       <x:c r="C25" s="45" t="s">
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:3">
@@ -3396,87 +3414,69 @@
   <x:dimension ref="A1:E6"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
-    <x:row r="1" spans="1:5">
+    <x:row r="1" spans="1:4">
       <x:c r="A1" s="107" t="s">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B1" s="107" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C1" s="107" t="s">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D1" s="107" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="E1" s="107" t="s">
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" spans="1:5">
+    <x:row r="2" spans="1:4">
       <x:c r="A2" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="B2" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C2" s="0">
+      <x:c r="B2" s="0">
         <x:v>10</x:v>
       </x:c>
     </x:row>
-    <x:row r="3" spans="1:5">
+    <x:row r="3" spans="1:4">
       <x:c r="A3" s="0" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="B3" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="C3" s="0">
+      <x:c r="B3" s="0">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="D3" s="0" t="s">
+      <x:c r="C3" s="0" t="s">
         <x:v>26</x:v>
       </x:c>
     </x:row>
-    <x:row r="4" spans="1:5">
+    <x:row r="4" spans="1:4">
       <x:c r="A4" s="0" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="B4" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C4" s="0">
+      <x:c r="B4" s="0">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="D4" s="0" t="s">
+      <x:c r="C4" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
     </x:row>
-    <x:row r="5" spans="1:5">
+    <x:row r="5" spans="1:4">
       <x:c r="A5" s="0" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="B5" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C5" s="0">
+      <x:c r="B5" s="0">
         <x:v>10</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" spans="1:5">
+    <x:row r="6" spans="1:4">
       <x:c r="A6" s="0" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="B6" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="C6" s="0">
+      <x:c r="B6" s="0">
         <x:v>10</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:dataValidations count="1">
-    <x:dataValidation type="list" errorStyle="stop" operator="between" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="" error="" promptTitle="" prompt="" sqref="A2:B200">
+    <x:dataValidation type="list" errorStyle="stop" operator="between" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="" error="" promptTitle="" prompt="" sqref="A2:A200">
       <x:formula1>='에피소드'!$A$2:$A$200</x:formula1>
       <x:formula2/>
     </x:dataValidation>

--- a/docs/chapter-graph-sample.xlsx
+++ b/docs/chapter-graph-sample.xlsx
@@ -17,7 +17,7 @@
     <x:sheet name="선택지" sheetId="8" r:id="rId11"/>
   </x:sheets>
   <x:definedNames>
-    <x:definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">에피소드!$A$1:$J$7</x:definedName>
+    <x:definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">에피소드!$A$1:$H$7</x:definedName>
     <x:definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'견본_에피소드 main05.02'!$A$1:$K$15</x:definedName>
   </x:definedNames>
   <x:calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -27,10 +27,13 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:si>
+    <x:t>선택지수</x:t>
+  </x:si>
+  <x:si>
     <x:t>스탯변화</x:t>
   </x:si>
   <x:si>
-    <x:t>선택지수</x:t>
+    <x:t>선택지</x:t>
   </x:si>
   <x:si>
     <x:t>스탯</x:t>
@@ -102,19 +105,22 @@
     <x:t>main05.02</x:t>
   </x:si>
   <x:si>
-    <x:t>branch05.02A</x:t>
+    <x:t>라루의 제안을 듣는다</x:t>
   </x:si>
   <x:si>
-    <x:t>라루의 제안을 듣는다</x:t>
+    <x:t>혼자 문을 연다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>branch05.02A</x:t>
   </x:si>
   <x:si>
     <x:t>main05.03</x:t>
   </x:si>
   <x:si>
-    <x:t>혼자 문을 연다</x:t>
+    <x:t>표시조건</x:t>
   </x:si>
   <x:si>
-    <x:t>선택지</x:t>
+    <x:t>해금조건</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1443,13 +1449,13 @@
     <x:col min="3" max="3" width="12" style="0" customWidth="1"/>
     <x:col min="4" max="4" width="20" style="0" customWidth="1"/>
     <x:col min="5" max="6" width="7" style="0" customWidth="1"/>
-    <x:col min="7" max="8" width="18" style="0" customWidth="1"/>
-    <x:col min="9" max="9" width="14" style="0" customWidth="1"/>
-    <x:col min="10" max="10" width="20" style="0" customWidth="1"/>
-    <x:col min="11" max="11" width="9.140625" style="0" customWidth="1"/>
+    <x:col min="7" max="7" width="14" style="0" customWidth="1"/>
+    <x:col min="8" max="8" width="20" style="0" customWidth="1"/>
+    <x:col min="9" max="9" width="9.140625" style="0" customWidth="1"/>
+    <x:col min="10" max="11" width="9.139196" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:11">
+    <x:row r="1" spans="1:9">
       <x:c r="A1" s="99" t="inlineStr">
         <x:is>
           <x:t>EpisodeId</x:t>
@@ -1482,29 +1488,19 @@
       </x:c>
       <x:c r="G1" s="99" t="inlineStr">
         <x:is>
-          <x:t>표시조건</x:t>
+          <x:t>엔딩키</x:t>
         </x:is>
       </x:c>
       <x:c r="H1" s="99" t="inlineStr">
         <x:is>
-          <x:t>해금조건</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I1" s="99" t="inlineStr">
-        <x:is>
-          <x:t>엔딩키</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J1" s="99" t="inlineStr">
-        <x:is>
           <x:t>메모</x:t>
         </x:is>
       </x:c>
-      <x:c r="K1" s="107" t="s">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2" spans="1:11">
+      <x:c r="I1" s="107" t="s">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:9">
       <x:c r="A2" s="100" t="inlineStr">
         <x:is>
           <x:t>main05.01</x:t>
@@ -1531,19 +1527,17 @@
       <x:c r="F2" s="102">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G2" s="101"/>
-      <x:c r="H2" s="102"/>
-      <x:c r="I2" s="102"/>
-      <x:c r="J2" s="103" t="inlineStr">
+      <x:c r="G2" s="102"/>
+      <x:c r="H2" s="103" t="inlineStr">
         <x:is>
           <x:t>챕터 진입점</x:t>
         </x:is>
       </x:c>
-      <x:c r="K2" s="0">
+      <x:c r="I2" s="0">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="3" spans="1:11">
+    <x:row r="3" spans="1:9">
       <x:c r="A3" s="100" t="inlineStr">
         <x:is>
           <x:t>main05.02</x:t>
@@ -1570,15 +1564,13 @@
       <x:c r="F3" s="102">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G3" s="101"/>
-      <x:c r="H3" s="102"/>
-      <x:c r="I3" s="102"/>
-      <x:c r="J3" s="103"/>
-      <x:c r="K3" s="0">
+      <x:c r="G3" s="102"/>
+      <x:c r="H3" s="103"/>
+      <x:c r="I3" s="0">
         <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="4" spans="1:11">
+    <x:row r="4" spans="1:9">
       <x:c r="A4" s="100" t="inlineStr">
         <x:is>
           <x:t>branch05.02A</x:t>
@@ -1605,23 +1597,17 @@
       <x:c r="F4" s="102">
         <x:v>-120</x:v>
       </x:c>
-      <x:c r="G4" s="101"/>
-      <x:c r="H4" s="102" t="inlineStr">
-        <x:is>
-          <x:t>신뢰높음</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I4" s="102"/>
-      <x:c r="J4" s="103" t="inlineStr">
+      <x:c r="G4" s="102"/>
+      <x:c r="H4" s="103" t="inlineStr">
         <x:is>
           <x:t>신뢰 루트</x:t>
         </x:is>
       </x:c>
-      <x:c r="K4" s="0">
+      <x:c r="I4" s="0">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="5" spans="1:11">
+    <x:row r="5" spans="1:9">
       <x:c r="A5" s="100" t="inlineStr">
         <x:is>
           <x:t>main05.03</x:t>
@@ -1648,19 +1634,17 @@
       <x:c r="F5" s="102">
         <x:v>120</x:v>
       </x:c>
-      <x:c r="G5" s="101"/>
-      <x:c r="H5" s="102"/>
-      <x:c r="I5" s="102"/>
-      <x:c r="J5" s="103" t="inlineStr">
+      <x:c r="G5" s="102"/>
+      <x:c r="H5" s="103" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve"> </x:t>
         </x:is>
       </x:c>
-      <x:c r="K5" s="0">
+      <x:c r="I5" s="0">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" spans="1:11">
+    <x:row r="6" spans="1:9">
       <x:c r="A6" s="100" t="inlineStr">
         <x:is>
           <x:t>attach05.02s</x:t>
@@ -1687,23 +1671,17 @@
       <x:c r="F6" s="102">
         <x:v>170</x:v>
       </x:c>
-      <x:c r="G6" s="101" t="inlineStr">
-        <x:is>
-          <x:t>복도완료</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H6" s="102"/>
-      <x:c r="I6" s="102"/>
-      <x:c r="J6" s="103" t="inlineStr">
+      <x:c r="G6" s="102"/>
+      <x:c r="H6" s="103" t="inlineStr">
         <x:is>
           <x:t>부착(사이드)</x:t>
         </x:is>
       </x:c>
-      <x:c r="K6" s="0">
+      <x:c r="I6" s="0">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="7" spans="1:11">
+    <x:row r="7" spans="1:9">
       <x:c r="A7" s="100" t="inlineStr">
         <x:is>
           <x:t>main05.end</x:t>
@@ -1730,30 +1708,22 @@
       <x:c r="F7" s="102">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G7" s="101"/>
-      <x:c r="H7" s="102"/>
-      <x:c r="I7" s="102" t="inlineStr">
+      <x:c r="G7" s="102" t="inlineStr">
         <x:is>
           <x:t>ch05_normal</x:t>
         </x:is>
       </x:c>
-      <x:c r="J7" s="103" t="inlineStr">
+      <x:c r="H7" s="103" t="inlineStr">
         <x:is>
           <x:t>엔딩 후보</x:t>
         </x:is>
       </x:c>
-      <x:c r="K7" s="0">
+      <x:c r="I7" s="0">
         <x:v>1</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:autoFilter ref="A1:J7"/>
-  <x:dataValidations count="1">
-    <x:dataValidation type="list" errorStyle="stop" operator="between" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="" error="" promptTitle="" prompt="" sqref="G2:H200">
-      <x:formula1>='조건'!$A$2:$A$200</x:formula1>
-      <x:formula2/>
-    </x:dataValidation>
-  </x:dataValidations>
+  <x:autoFilter ref="A1:H7"/>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
@@ -1772,13 +1742,13 @@
   <x:sheetFormatPr baseColWidth="8" defaultColWidth="9.139196" defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="3" width="14" style="0" customWidth="1"/>
-    <x:col min="4" max="4" width="26" style="0" customWidth="1"/>
-    <x:col min="5" max="5" width="14" style="0" customWidth="1"/>
-    <x:col min="6" max="6" width="12" style="0" customWidth="1"/>
-    <x:col min="7" max="7" width="26" style="0" customWidth="1"/>
+    <x:col min="4" max="5" width="26" style="0" customWidth="1"/>
+    <x:col min="6" max="6" width="14" style="0" customWidth="1"/>
+    <x:col min="7" max="7" width="12" style="0" customWidth="1"/>
+    <x:col min="8" max="8" width="26" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:7">
+    <x:row r="1" spans="1:8">
       <x:c r="A1" s="99" t="inlineStr">
         <x:is>
           <x:t>출발</x:t>
@@ -1790,28 +1760,29 @@
         </x:is>
       </x:c>
       <x:c r="C1" s="99" t="s">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D1" s="99" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="E1" s="99" t="inlineStr">
-        <x:is>
-          <x:t>조건</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F1" s="99" t="inlineStr">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E1" s="99" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="F1" s="99" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="G1" s="99" t="inlineStr">
         <x:is>
           <x:t>잠금시 숨김</x:t>
         </x:is>
       </x:c>
-      <x:c r="G1" s="99" t="inlineStr">
+      <x:c r="H1" s="99" t="inlineStr">
         <x:is>
           <x:t>잠금 안내문</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="2" spans="1:7">
+    <x:row r="2" spans="1:8">
       <x:c r="A2" s="100" t="inlineStr">
         <x:is>
           <x:t>main05.01</x:t>
@@ -1826,15 +1797,16 @@
       <x:c r="D2" s="102">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="E2" s="101"/>
-      <x:c r="F2" s="102" t="inlineStr">
+      <x:c r="E2" s="102"/>
+      <x:c r="F2" s="101"/>
+      <x:c r="G2" s="102" t="inlineStr">
         <x:is>
           <x:t>FALSE</x:t>
         </x:is>
       </x:c>
-      <x:c r="G2" s="102"/>
-    </x:row>
-    <x:row r="3" spans="1:7">
+      <x:c r="H2" s="102"/>
+    </x:row>
+    <x:row r="3" spans="1:8">
       <x:c r="A3" s="100" t="inlineStr">
         <x:is>
           <x:t>main05.02</x:t>
@@ -1849,23 +1821,24 @@
       <x:c r="D3" s="102">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="E3" s="101" t="inlineStr">
+      <x:c r="E3" s="102"/>
+      <x:c r="F3" s="101" t="inlineStr">
         <x:is>
           <x:t>신뢰높음</x:t>
         </x:is>
       </x:c>
-      <x:c r="F3" s="102" t="inlineStr">
+      <x:c r="G3" s="102" t="inlineStr">
         <x:is>
           <x:t>FALSE</x:t>
         </x:is>
       </x:c>
-      <x:c r="G3" s="102" t="inlineStr">
+      <x:c r="H3" s="102" t="inlineStr">
         <x:is>
           <x:t>신뢰가 부족하다</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="4" spans="1:7">
+    <x:row r="4" spans="1:8">
       <x:c r="A4" s="100" t="inlineStr">
         <x:is>
           <x:t>main05.02</x:t>
@@ -1880,15 +1853,16 @@
       <x:c r="D4" s="102">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="E4" s="101"/>
-      <x:c r="F4" s="102" t="inlineStr">
+      <x:c r="E4" s="102"/>
+      <x:c r="F4" s="101"/>
+      <x:c r="G4" s="102" t="inlineStr">
         <x:is>
           <x:t>FALSE</x:t>
         </x:is>
       </x:c>
-      <x:c r="G4" s="102"/>
-    </x:row>
-    <x:row r="5" spans="1:7">
+      <x:c r="H4" s="102"/>
+    </x:row>
+    <x:row r="5" spans="1:8">
       <x:c r="A5" s="100" t="inlineStr">
         <x:is>
           <x:t>branch05.02A</x:t>
@@ -1903,15 +1877,16 @@
       <x:c r="D5" s="102">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="E5" s="101"/>
-      <x:c r="F5" s="102" t="inlineStr">
+      <x:c r="E5" s="102"/>
+      <x:c r="F5" s="101"/>
+      <x:c r="G5" s="102" t="inlineStr">
         <x:is>
           <x:t>FALSE</x:t>
         </x:is>
       </x:c>
-      <x:c r="G5" s="102"/>
-    </x:row>
-    <x:row r="6" spans="1:7">
+      <x:c r="H5" s="102"/>
+    </x:row>
+    <x:row r="6" spans="1:8">
       <x:c r="A6" s="100" t="inlineStr">
         <x:is>
           <x:t>main05.03</x:t>
@@ -1926,21 +1901,22 @@
       <x:c r="D6" s="102">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="E6" s="101"/>
-      <x:c r="F6" s="102" t="inlineStr">
+      <x:c r="E6" s="102"/>
+      <x:c r="F6" s="101"/>
+      <x:c r="G6" s="102" t="inlineStr">
         <x:is>
           <x:t>FALSE</x:t>
         </x:is>
       </x:c>
-      <x:c r="G6" s="102"/>
+      <x:c r="H6" s="102"/>
     </x:row>
   </x:sheetData>
   <x:dataValidations count="3">
-    <x:dataValidation type="list" errorStyle="stop" operator="between" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="" error="" promptTitle="" prompt="" sqref="E2:E200">
+    <x:dataValidation type="list" errorStyle="stop" operator="between" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="" error="" promptTitle="" prompt="" sqref="E2:F200">
       <x:formula1>='조건'!$A$2:$A$200</x:formula1>
       <x:formula2/>
     </x:dataValidation>
-    <x:dataValidation type="list" errorStyle="stop" operator="between" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="" error="" promptTitle="" prompt="" sqref="F2:F200">
+    <x:dataValidation type="list" errorStyle="stop" operator="between" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="" error="" promptTitle="" prompt="" sqref="G2:G200">
       <x:formula1>"TRUE,FALSE"</x:formula1>
       <x:formula2/>
     </x:dataValidation>
@@ -1978,13 +1954,13 @@
         </x:is>
       </x:c>
       <x:c r="B1" s="105" t="s">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C1" s="105" t="s">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D1" s="105" t="s">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E1" s="105" t="inlineStr">
         <x:is>
@@ -2004,13 +1980,13 @@
         </x:is>
       </x:c>
       <x:c r="B2" s="101" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C2" s="101" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D2" s="101" t="s">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E2" s="102" t="inlineStr">
         <x:is>
@@ -2025,13 +2001,13 @@
         </x:is>
       </x:c>
       <x:c r="B3" s="101" t="s">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C3" s="101" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D3" s="101" t="s">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E3" s="102" t="inlineStr">
         <x:is>
@@ -2142,11 +2118,11 @@
         </x:is>
       </x:c>
       <x:c r="F1" s="107" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G1" s="10"/>
       <x:c r="H1" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:8">
@@ -2999,7 +2975,7 @@
   <x:sheetData>
     <x:row r="1" spans="1:3">
       <x:c r="B1" s="43" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:3">
@@ -3052,7 +3028,7 @@
         </x:is>
       </x:c>
       <x:c r="C7" s="45" t="s">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:3">
@@ -3136,12 +3112,12 @@
         </x:is>
       </x:c>
       <x:c r="C17" s="166" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="B19" s="46" t="s">
-        <x:v>15</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:3">
@@ -3151,7 +3127,7 @@
         </x:is>
       </x:c>
       <x:c r="C20" s="45" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:3">
@@ -3180,7 +3156,7 @@
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="B24" s="46" t="s">
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:3">
@@ -3190,7 +3166,7 @@
         </x:is>
       </x:c>
       <x:c r="C25" s="45" t="s">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:3">
@@ -3416,21 +3392,21 @@
   <x:sheetData>
     <x:row r="1" spans="1:4">
       <x:c r="A1" s="107" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B1" s="107" t="s">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C1" s="107" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D1" s="107" t="s">
-        <x:v>22</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:4">
       <x:c r="A2" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B2" s="0">
         <x:v>10</x:v>
@@ -3438,7 +3414,7 @@
     </x:row>
     <x:row r="3" spans="1:4">
       <x:c r="A3" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B3" s="0">
         <x:v>10</x:v>
@@ -3449,18 +3425,18 @@
     </x:row>
     <x:row r="4" spans="1:4">
       <x:c r="A4" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B4" s="0">
         <x:v>20</x:v>
       </x:c>
       <x:c r="C4" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:4">
       <x:c r="A5" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B5" s="0">
         <x:v>10</x:v>
@@ -3468,7 +3444,7 @@
     </x:row>
     <x:row r="6" spans="1:4">
       <x:c r="A6" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B6" s="0">
         <x:v>10</x:v>

--- a/docs/chapter-graph-sample.xlsx
+++ b/docs/chapter-graph-sample.xlsx
@@ -27,13 +27,16 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:si>
-    <x:t>선택지수</x:t>
-  </x:si>
-  <x:si>
     <x:t>스탯변화</x:t>
   </x:si>
   <x:si>
     <x:t>선택지</x:t>
+  </x:si>
+  <x:si>
+    <x:t>표시조건</x:t>
+  </x:si>
+  <x:si>
+    <x:t>해금조건</x:t>
   </x:si>
   <x:si>
     <x:t>스탯</x:t>
@@ -87,9 +90,6 @@
     <x:t>대본(에피소드 워크북)의 인덱스는 그대로 10·20·30 방식이다. 챕터 시트의 표시용 인덱스만 없앴다.</x:t>
   </x:si>
   <x:si>
-    <x:t>출발</x:t>
-  </x:si>
-  <x:si>
     <x:t>인덱스</x:t>
   </x:si>
   <x:si>
@@ -99,28 +99,13 @@
     <x:t>메모</x:t>
   </x:si>
   <x:si>
-    <x:t>main05.01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>main05.02</x:t>
-  </x:si>
-  <x:si>
     <x:t>라루의 제안을 듣는다</x:t>
   </x:si>
   <x:si>
     <x:t>혼자 문을 연다</x:t>
   </x:si>
   <x:si>
-    <x:t>branch05.02A</x:t>
-  </x:si>
-  <x:si>
-    <x:t>main05.03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>표시조건</x:t>
-  </x:si>
-  <x:si>
-    <x:t>해금조건</x:t>
+    <x:t/>
   </x:si>
 </x:sst>
 </file>
@@ -1451,11 +1436,10 @@
     <x:col min="5" max="6" width="7" style="0" customWidth="1"/>
     <x:col min="7" max="7" width="14" style="0" customWidth="1"/>
     <x:col min="8" max="8" width="20" style="0" customWidth="1"/>
-    <x:col min="9" max="9" width="9.140625" style="0" customWidth="1"/>
-    <x:col min="10" max="11" width="9.139196" style="0" customWidth="1"/>
+    <x:col min="9" max="11" width="9.139196" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:9">
+    <x:row r="1" spans="1:10">
       <x:c r="A1" s="99" t="inlineStr">
         <x:is>
           <x:t>EpisodeId</x:t>
@@ -1496,11 +1480,8 @@
           <x:t>메모</x:t>
         </x:is>
       </x:c>
-      <x:c r="I1" s="107" t="s">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2" spans="1:9">
+    </x:row>
+    <x:row r="2" spans="1:10">
       <x:c r="A2" s="100" t="inlineStr">
         <x:is>
           <x:t>main05.01</x:t>
@@ -1533,11 +1514,8 @@
           <x:t>챕터 진입점</x:t>
         </x:is>
       </x:c>
-      <x:c r="I2" s="0">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" spans="1:9">
+    </x:row>
+    <x:row r="3" spans="1:10">
       <x:c r="A3" s="100" t="inlineStr">
         <x:is>
           <x:t>main05.02</x:t>
@@ -1566,11 +1544,8 @@
       </x:c>
       <x:c r="G3" s="102"/>
       <x:c r="H3" s="103"/>
-      <x:c r="I3" s="0">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" spans="1:9">
+    </x:row>
+    <x:row r="4" spans="1:10">
       <x:c r="A4" s="100" t="inlineStr">
         <x:is>
           <x:t>branch05.02A</x:t>
@@ -1603,11 +1578,8 @@
           <x:t>신뢰 루트</x:t>
         </x:is>
       </x:c>
-      <x:c r="I4" s="0">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" spans="1:9">
+    </x:row>
+    <x:row r="5" spans="1:10">
       <x:c r="A5" s="100" t="inlineStr">
         <x:is>
           <x:t>main05.03</x:t>
@@ -1640,11 +1612,8 @@
           <x:t xml:space="preserve"> </x:t>
         </x:is>
       </x:c>
-      <x:c r="I5" s="0">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" spans="1:9">
+    </x:row>
+    <x:row r="6" spans="1:10">
       <x:c r="A6" s="100" t="inlineStr">
         <x:is>
           <x:t>attach05.02s</x:t>
@@ -1677,11 +1646,8 @@
           <x:t>부착(사이드)</x:t>
         </x:is>
       </x:c>
-      <x:c r="I6" s="0">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" spans="1:9">
+    </x:row>
+    <x:row r="7" spans="1:10">
       <x:c r="A7" s="100" t="inlineStr">
         <x:is>
           <x:t>main05.end</x:t>
@@ -1717,9 +1683,6 @@
         <x:is>
           <x:t>엔딩 후보</x:t>
         </x:is>
-      </x:c>
-      <x:c r="I7" s="0">
-        <x:v>1</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1760,16 +1723,16 @@
         </x:is>
       </x:c>
       <x:c r="C1" s="99" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D1" s="99" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D1" s="99" t="s">
+      <x:c r="E1" s="99" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="E1" s="99" t="s">
-        <x:v>30</x:v>
-      </x:c>
       <x:c r="F1" s="99" t="s">
-        <x:v>31</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="G1" s="99" t="inlineStr">
         <x:is>
@@ -1794,8 +1757,8 @@
         </x:is>
       </x:c>
       <x:c r="C2" s="104"/>
-      <x:c r="D2" s="102">
-        <x:v>10</x:v>
+      <x:c r="D2" s="102" t="s">
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E2" s="102"/>
       <x:c r="F2" s="101"/>
@@ -1818,8 +1781,8 @@
         </x:is>
       </x:c>
       <x:c r="C3" s="104"/>
-      <x:c r="D3" s="102">
-        <x:v>10</x:v>
+      <x:c r="D3" s="102" t="s">
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E3" s="102"/>
       <x:c r="F3" s="101" t="inlineStr">
@@ -1850,8 +1813,8 @@
         </x:is>
       </x:c>
       <x:c r="C4" s="104"/>
-      <x:c r="D4" s="102">
-        <x:v>20</x:v>
+      <x:c r="D4" s="102" t="s">
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E4" s="102"/>
       <x:c r="F4" s="101"/>
@@ -1874,8 +1837,8 @@
         </x:is>
       </x:c>
       <x:c r="C5" s="104"/>
-      <x:c r="D5" s="102">
-        <x:v>10</x:v>
+      <x:c r="D5" s="102" t="s">
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E5" s="102"/>
       <x:c r="F5" s="101"/>
@@ -1898,8 +1861,8 @@
         </x:is>
       </x:c>
       <x:c r="C6" s="104"/>
-      <x:c r="D6" s="102">
-        <x:v>10</x:v>
+      <x:c r="D6" s="102" t="s">
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E6" s="102"/>
       <x:c r="F6" s="101"/>
@@ -1954,13 +1917,13 @@
         </x:is>
       </x:c>
       <x:c r="B1" s="105" t="s">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C1" s="105" t="s">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D1" s="105" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E1" s="105" t="inlineStr">
         <x:is>
@@ -1980,13 +1943,13 @@
         </x:is>
       </x:c>
       <x:c r="B2" s="101" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C2" s="101" t="s">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D2" s="101" t="s">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E2" s="102" t="inlineStr">
         <x:is>
@@ -2001,13 +1964,13 @@
         </x:is>
       </x:c>
       <x:c r="B3" s="101" t="s">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C3" s="101" t="s">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D3" s="101" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="E3" s="102" t="inlineStr">
         <x:is>
@@ -2118,11 +2081,11 @@
         </x:is>
       </x:c>
       <x:c r="F1" s="107" t="s">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="G1" s="10"/>
       <x:c r="H1" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:8">
@@ -2975,7 +2938,7 @@
   <x:sheetData>
     <x:row r="1" spans="1:3">
       <x:c r="B1" s="43" t="s">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:3">
@@ -3028,7 +2991,7 @@
         </x:is>
       </x:c>
       <x:c r="C7" s="45" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:3">
@@ -3112,12 +3075,12 @@
         </x:is>
       </x:c>
       <x:c r="C17" s="166" t="s">
-        <x:v>15</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="B19" s="46" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:3">
@@ -3127,7 +3090,7 @@
         </x:is>
       </x:c>
       <x:c r="C20" s="45" t="s">
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:3">
@@ -3156,7 +3119,7 @@
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="B24" s="46" t="s">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:3">
@@ -3166,7 +3129,7 @@
         </x:is>
       </x:c>
       <x:c r="C25" s="45" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:3">
@@ -3390,73 +3353,34 @@
   <x:dimension ref="A1:E6"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
-    <x:row r="1" spans="1:4">
+    <x:row r="1" spans="1:3">
       <x:c r="A1" s="107" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B1" s="107" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C1" s="107" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:3">
+      <x:c r="A2" s="0">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B2" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:3">
+      <x:c r="A3" s="0">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="B1" s="107" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C1" s="107" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="D1" s="107" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2" spans="1:4">
-      <x:c r="A2" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="B2" s="0">
-        <x:v>10</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" spans="1:4">
-      <x:c r="A3" s="0" t="s">
+      <x:c r="B3" s="0" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="B3" s="0">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C3" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" spans="1:4">
-      <x:c r="A4" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="B4" s="0">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C4" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" spans="1:4">
-      <x:c r="A5" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="B5" s="0">
-        <x:v>10</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" spans="1:4">
-      <x:c r="A6" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="B6" s="0">
-        <x:v>10</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:dataValidations count="1">
-    <x:dataValidation type="list" errorStyle="stop" operator="between" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="" error="" promptTitle="" prompt="" sqref="A2:A200">
-      <x:formula1>='에피소드'!$A$2:$A$200</x:formula1>
-      <x:formula2/>
-    </x:dataValidation>
-  </x:dataValidations>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
   <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>

--- a/docs/chapter-graph-sample.xlsx
+++ b/docs/chapter-graph-sample.xlsx
@@ -39,6 +39,15 @@
     <x:t>해금조건</x:t>
   </x:si>
   <x:si>
+    <x:t/>
+  </x:si>
+  <x:si>
+    <x:t>라루의 제안을 듣는다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>혼자 문을 연다</x:t>
+  </x:si>
+  <x:si>
     <x:t>스탯</x:t>
   </x:si>
   <x:si>
@@ -69,6 +78,72 @@
     <x:t>⚠ 읽기전용 미러 — 원천은 game.definition.json. 브리지가 왕복하는 Tier 2 키 목록이기도 하다(2~5개).</x:t>
   </x:si>
   <x:si>
+    <x:t>인덱스</x:t>
+  </x:si>
+  <x:si>
+    <x:t>분노누적</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ELSEIF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENDIF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>다리가 무거워.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ln_0004</x:t>
+  </x:si>
+  <x:si>
+    <x:t>지쳐있음</x:t>
+  </x:si>
+  <x:si>
+    <x:t>유형</x:t>
+  </x:si>
+  <x:si>
+    <x:t>너를 믿어.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ln_0003</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ln_0001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>신뢰높음</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ln_0002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>여기서 기다릴까?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>라루</x:t>
+  </x:si>
+  <x:si>
+    <x:t>화자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>복도는 조용했다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>윌로</x:t>
+  </x:si>
+  <x:si>
+    <x:t>내용</x:t>
+  </x:si>
+  <x:si>
+    <x:t>조건라벨</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LineId</x:t>
+  </x:si>
+  <x:si>
     <x:t>챕터·에피소드 그래프 엑셀 규격 v5 (2026-08-16) — 실물 견본</x:t>
   </x:si>
   <x:si>
@@ -90,22 +165,22 @@
     <x:t>대본(에피소드 워크북)의 인덱스는 그대로 10·20·30 방식이다. 챕터 시트의 표시용 인덱스만 없앴다.</x:t>
   </x:si>
   <x:si>
-    <x:t>인덱스</x:t>
-  </x:si>
-  <x:si>
     <x:t>대본</x:t>
   </x:si>
   <x:si>
     <x:t>메모</x:t>
   </x:si>
   <x:si>
-    <x:t>라루의 제안을 듣는다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>혼자 문을 연다</x:t>
-  </x:si>
-  <x:si>
-    <x:t/>
+    <x:t>ln_0005</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아직도 화가 나.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ln_0006</x:t>
+  </x:si>
+  <x:si>
+    <x:t>문이 열렸다.</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -204,7 +279,7 @@
       <x:scheme val="minor"/>
     </x:font>
   </x:fonts>
-  <x:fills count="15">
+  <x:fills count="16">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -276,6 +351,11 @@
         <x:fgColor rgb="FFE8EAED"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF1F3F4"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="2">
     <x:border>
@@ -300,7 +380,7 @@
       </x:bottom>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="65">
+  <x:cellStyleXfs count="67">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -494,8 +574,14 @@
     <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" quotePrefix="1" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="15" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="15" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="167">
+  <x:cellXfs count="169">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="0" pivotButton="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" quotePrefix="0" pivotButton="0" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
@@ -1049,6 +1135,14 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellXfs>
@@ -1439,7 +1533,7 @@
     <x:col min="9" max="11" width="9.139196" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:10">
+    <x:row r="1" spans="1:11">
       <x:c r="A1" s="99" t="inlineStr">
         <x:is>
           <x:t>EpisodeId</x:t>
@@ -1481,7 +1575,7 @@
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="2" spans="1:10">
+    <x:row r="2" spans="1:11">
       <x:c r="A2" s="100" t="inlineStr">
         <x:is>
           <x:t>main05.01</x:t>
@@ -1515,7 +1609,7 @@
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="3" spans="1:10">
+    <x:row r="3" spans="1:11">
       <x:c r="A3" s="100" t="inlineStr">
         <x:is>
           <x:t>main05.02</x:t>
@@ -1545,7 +1639,7 @@
       <x:c r="G3" s="102"/>
       <x:c r="H3" s="103"/>
     </x:row>
-    <x:row r="4" spans="1:10">
+    <x:row r="4" spans="1:11">
       <x:c r="A4" s="100" t="inlineStr">
         <x:is>
           <x:t>branch05.02A</x:t>
@@ -1579,7 +1673,7 @@
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="5" spans="1:10">
+    <x:row r="5" spans="1:11">
       <x:c r="A5" s="100" t="inlineStr">
         <x:is>
           <x:t>main05.03</x:t>
@@ -1613,7 +1707,7 @@
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="6" spans="1:10">
+    <x:row r="6" spans="1:11">
       <x:c r="A6" s="100" t="inlineStr">
         <x:is>
           <x:t>attach05.02s</x:t>
@@ -1647,7 +1741,7 @@
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="7" spans="1:10">
+    <x:row r="7" spans="1:11">
       <x:c r="A7" s="100" t="inlineStr">
         <x:is>
           <x:t>main05.end</x:t>
@@ -1758,7 +1852,7 @@
       </x:c>
       <x:c r="C2" s="104"/>
       <x:c r="D2" s="102" t="s">
-        <x:v>26</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E2" s="102"/>
       <x:c r="F2" s="101"/>
@@ -1782,7 +1876,7 @@
       </x:c>
       <x:c r="C3" s="104"/>
       <x:c r="D3" s="102" t="s">
-        <x:v>24</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E3" s="102"/>
       <x:c r="F3" s="101" t="inlineStr">
@@ -1814,7 +1908,7 @@
       </x:c>
       <x:c r="C4" s="104"/>
       <x:c r="D4" s="102" t="s">
-        <x:v>25</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E4" s="102"/>
       <x:c r="F4" s="101"/>
@@ -1838,7 +1932,7 @@
       </x:c>
       <x:c r="C5" s="104"/>
       <x:c r="D5" s="102" t="s">
-        <x:v>26</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E5" s="102"/>
       <x:c r="F5" s="101"/>
@@ -1862,7 +1956,7 @@
       </x:c>
       <x:c r="C6" s="104"/>
       <x:c r="D6" s="102" t="s">
-        <x:v>26</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E6" s="102"/>
       <x:c r="F6" s="101"/>
@@ -1917,13 +2011,13 @@
         </x:is>
       </x:c>
       <x:c r="B1" s="105" t="s">
-        <x:v>4</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C1" s="105" t="s">
-        <x:v>5</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D1" s="105" t="s">
-        <x:v>6</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E1" s="105" t="inlineStr">
         <x:is>
@@ -1943,13 +2037,13 @@
         </x:is>
       </x:c>
       <x:c r="B2" s="101" t="s">
-        <x:v>7</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C2" s="101" t="s">
-        <x:v>8</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D2" s="101" t="s">
-        <x:v>9</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E2" s="102" t="inlineStr">
         <x:is>
@@ -1964,13 +2058,13 @@
         </x:is>
       </x:c>
       <x:c r="B3" s="101" t="s">
-        <x:v>10</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C3" s="101" t="s">
-        <x:v>8</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D3" s="101" t="s">
-        <x:v>11</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E3" s="102" t="inlineStr">
         <x:is>
@@ -2081,11 +2175,11 @@
         </x:is>
       </x:c>
       <x:c r="F1" s="107" t="s">
-        <x:v>12</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G1" s="10"/>
       <x:c r="H1" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:8">
@@ -2321,10 +2415,11 @@
   <x:sheetFormatPr baseColWidth="8" defaultColWidth="9.139196" defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="9" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="11" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="11" style="167" customWidth="1"/>
     <x:col min="3" max="4" width="9" style="0" customWidth="1"/>
     <x:col min="5" max="5" width="13" style="0" customWidth="1"/>
-    <x:col min="6" max="7" width="7" style="0" customWidth="1"/>
+    <x:col min="6" max="6" width="50.710625" style="0" customWidth="1"/>
+    <x:col min="7" max="7" width="7" style="0" customWidth="1"/>
     <x:col min="8" max="8" width="10" style="0" customWidth="1"/>
     <x:col min="9" max="9" width="38" style="0" customWidth="1"/>
     <x:col min="10" max="10" width="15" style="0" customWidth="1"/>
@@ -2332,584 +2427,156 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:11">
-      <x:c r="A1" s="99" t="inlineStr">
-        <x:is>
-          <x:t>인덱스</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B1" s="99" t="inlineStr">
-        <x:is>
-          <x:t>LineId</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C1" s="99" t="inlineStr">
-        <x:is>
-          <x:t>유형</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D1" s="99" t="inlineStr">
-        <x:is>
-          <x:t>태그</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E1" s="99" t="inlineStr">
-        <x:is>
-          <x:t>조건라벨</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F1" s="99" t="inlineStr">
-        <x:is>
-          <x:t>IN</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G1" s="99" t="inlineStr">
-        <x:is>
-          <x:t>OUT</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H1" s="99" t="inlineStr">
-        <x:is>
-          <x:t>화자</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I1" s="99" t="inlineStr">
-        <x:is>
-          <x:t>내용</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J1" s="99" t="inlineStr">
-        <x:is>
-          <x:t>스탯변화</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K1" s="99" t="inlineStr">
-        <x:is>
-          <x:t>메모</x:t>
-        </x:is>
+      <x:c r="A1" s="107" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B1" s="168" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C1" s="107" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="D1" s="107" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="E1" s="107" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="F1" s="107" t="s">
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:11">
-      <x:c r="A2" s="113">
+      <x:c r="A2" s="0">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="B2" s="100" t="inlineStr">
-        <x:is>
-          <x:t>ln_0001</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C2" s="114"/>
-      <x:c r="D2" s="114"/>
-      <x:c r="E2" s="114"/>
-      <x:c r="F2" s="115"/>
-      <x:c r="G2" s="116"/>
-      <x:c r="H2" s="102" t="inlineStr">
-        <x:is>
-          <x:t>윌로</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I2" s="101" t="inlineStr">
-        <x:is>
-          <x:t>복도는 생각보다 조용했다.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J2" s="102"/>
-      <x:c r="K2" s="117"/>
+      <x:c r="B2" s="167" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E2" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="F2" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
     </x:row>
     <x:row r="3" spans="1:11">
-      <x:c r="A3" s="113">
+      <x:c r="A3" s="0">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="B3" s="100" t="inlineStr">
-        <x:is>
-          <x:t>ln_0002</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C3" s="114"/>
-      <x:c r="D3" s="114"/>
-      <x:c r="E3" s="114"/>
-      <x:c r="F3" s="115"/>
-      <x:c r="G3" s="116"/>
-      <x:c r="H3" s="102" t="inlineStr">
-        <x:is>
-          <x:t>라루</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I3" s="101" t="inlineStr">
-        <x:is>
-          <x:t>여기서 잠깐 쉬어도 될까?</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J3" s="102" t="inlineStr">
-        <x:is>
-          <x:t>fatigue +1</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K3" s="117"/>
+      <x:c r="B3" s="167" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="E3" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="F3" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
     </x:row>
     <x:row r="4" spans="1:11">
-      <x:c r="A4" s="118">
+      <x:c r="A4" s="0">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="B4" s="119"/>
-      <x:c r="C4" s="120" t="inlineStr">
-        <x:is>
-          <x:t>IF</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D4" s="120"/>
-      <x:c r="E4" s="120" t="inlineStr">
-        <x:is>
-          <x:t>신뢰높음</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F4" s="121">
-        <x:v>900</x:v>
-      </x:c>
-      <x:c r="G4" s="122"/>
-      <x:c r="H4" s="123"/>
-      <x:c r="I4" s="124"/>
-      <x:c r="J4" s="123"/>
-      <x:c r="K4" s="125" t="inlineStr">
-        <x:is>
-          <x:t>라인 아님 · LineId 없음 · IN=900</x:t>
-        </x:is>
+      <x:c r="C4" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="D4" s="0" t="s">
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:11">
-      <x:c r="A5" s="113">
+      <x:c r="A5" s="0">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="B5" s="100" t="inlineStr">
-        <x:is>
-          <x:t>ln_0003</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C5" s="114"/>
-      <x:c r="D5" s="114"/>
-      <x:c r="E5" s="114"/>
-      <x:c r="F5" s="115"/>
-      <x:c r="G5" s="116"/>
-      <x:c r="H5" s="102" t="inlineStr">
-        <x:is>
-          <x:t>라루</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I5" s="101" t="inlineStr">
-        <x:is>
-          <x:t>…왜 그런 표정이야?</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J5" s="102"/>
-      <x:c r="K5" s="117" t="inlineStr">
-        <x:is>
-          <x:t>조건 거짓이면 여기 / 구간 OUT=40</x:t>
-        </x:is>
+      <x:c r="B5" s="167" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="E5" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="F5" s="0" t="s">
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:11">
-      <x:c r="A6" s="113">
+      <x:c r="A6" s="0">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="B6" s="100" t="inlineStr">
-        <x:is>
-          <x:t>ln_0004</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C6" s="114"/>
-      <x:c r="D6" s="114"/>
-      <x:c r="E6" s="114"/>
-      <x:c r="F6" s="115"/>
-      <x:c r="G6" s="116"/>
-      <x:c r="H6" s="102" t="inlineStr">
-        <x:is>
-          <x:t>윌로</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I6" s="101" t="inlineStr">
-        <x:is>
-          <x:t>아무것도 아니야.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J6" s="102" t="inlineStr">
-        <x:is>
-          <x:t>trust +1</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K6" s="117"/>
+      <x:c r="C6" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="D6" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
     </x:row>
     <x:row r="7" spans="1:11">
-      <x:c r="A7" s="113">
+      <x:c r="A7" s="0">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="B7" s="100" t="inlineStr">
-        <x:is>
-          <x:t>ln_0005</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C7" s="114"/>
-      <x:c r="D7" s="114"/>
-      <x:c r="E7" s="114"/>
-      <x:c r="F7" s="115"/>
-      <x:c r="G7" s="116"/>
-      <x:c r="H7" s="102" t="inlineStr">
-        <x:is>
-          <x:t>라루</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I7" s="101" t="inlineStr">
-        <x:is>
-          <x:t>그럼, 어떻게 할래?</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J7" s="102"/>
-      <x:c r="K7" s="117"/>
+      <x:c r="B7" s="167" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="E7" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="F7" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
     </x:row>
     <x:row r="8" spans="1:11">
-      <x:c r="A8" s="126">
+      <x:c r="A8" s="0">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="B8" s="127" t="inlineStr">
-        <x:is>
-          <x:t>ln_0006</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C8" s="128" t="inlineStr">
-        <x:is>
-          <x:t>CHOICE</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D8" s="128"/>
-      <x:c r="E8" s="128"/>
-      <x:c r="F8" s="129"/>
-      <x:c r="G8" s="130"/>
-      <x:c r="H8" s="131"/>
-      <x:c r="I8" s="132"/>
-      <x:c r="J8" s="131"/>
-      <x:c r="K8" s="133" t="inlineStr">
-        <x:is>
-          <x:t>맨 끝 1개만</x:t>
-        </x:is>
+      <x:c r="C8" s="0" t="s">
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:11">
-      <x:c r="A9" s="134">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="B9" s="135" t="inlineStr">
-        <x:is>
-          <x:t>ln_0007</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C9" s="136" t="inlineStr">
-        <x:is>
-          <x:t>OPTION</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D9" s="136"/>
-      <x:c r="E9" s="136" t="inlineStr">
-        <x:is>
-          <x:t>신뢰높음</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F9" s="137">
-        <x:v>920</x:v>
-      </x:c>
-      <x:c r="G9" s="138"/>
-      <x:c r="H9" s="139"/>
-      <x:c r="I9" s="140" t="inlineStr">
-        <x:is>
-          <x:t>라루의 제안을 듣는다</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J9" s="139"/>
-      <x:c r="K9" s="141" t="inlineStr">
-        <x:is>
-          <x:t>IN=920 · 도착지는 간선 시트</x:t>
-        </x:is>
+      <x:c r="A9" s="0">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="C9" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="D9" s="0" t="s">
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:11">
-      <x:c r="A10" s="134">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="B10" s="135" t="inlineStr">
-        <x:is>
-          <x:t>ln_0008</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C10" s="136" t="inlineStr">
-        <x:is>
-          <x:t>OPTION</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D10" s="136"/>
-      <x:c r="E10" s="136"/>
-      <x:c r="F10" s="137"/>
-      <x:c r="G10" s="138"/>
-      <x:c r="H10" s="139"/>
-      <x:c r="I10" s="140" t="inlineStr">
-        <x:is>
-          <x:t>혼자 문을 연다</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J10" s="139"/>
-      <x:c r="K10" s="141" t="inlineStr">
-        <x:is>
-          <x:t>본문 없음 · 도착지는 간선 시트</x:t>
-        </x:is>
+      <x:c r="A10" s="0">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="B10" s="167" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="E10" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="F10" s="0" t="s">
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:11">
-      <x:c r="A11" s="142">
-        <x:v>900</x:v>
-      </x:c>
-      <x:c r="B11" s="143" t="inlineStr">
-        <x:is>
-          <x:t>ln_0100</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C11" s="144"/>
-      <x:c r="D11" s="144" t="inlineStr">
-        <x:is>
-          <x:t>INPUT</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E11" s="144"/>
-      <x:c r="F11" s="145"/>
-      <x:c r="G11" s="146"/>
-      <x:c r="H11" s="147" t="inlineStr">
-        <x:is>
-          <x:t>윌로</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I11" s="148" t="inlineStr">
-        <x:is>
-          <x:t>어머니가 같은 말을 했었다.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J11" s="147"/>
-      <x:c r="K11" s="149" t="inlineStr">
-        <x:is>
-          <x:t>구간 진입 (30이 가리킴)</x:t>
-        </x:is>
+      <x:c r="A11" s="0">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="C11" s="0" t="s">
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:11">
-      <x:c r="A12" s="150">
-        <x:v>905</x:v>
-      </x:c>
-      <x:c r="B12" s="151" t="inlineStr">
-        <x:is>
-          <x:t>ln_0101</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C12" s="152"/>
-      <x:c r="D12" s="152"/>
-      <x:c r="E12" s="152"/>
-      <x:c r="F12" s="153"/>
-      <x:c r="G12" s="154"/>
-      <x:c r="H12" s="155" t="inlineStr">
-        <x:is>
-          <x:t>라루</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I12" s="156" t="inlineStr">
-        <x:is>
-          <x:t>…그 얘기 해준 적 있었나?</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J12" s="155"/>
-      <x:c r="K12" s="157"/>
-    </x:row>
-    <x:row r="13" spans="1:11">
-      <x:c r="A13" s="158">
-        <x:v>908</x:v>
-      </x:c>
-      <x:c r="B13" s="159" t="inlineStr">
-        <x:is>
-          <x:t>ln_0102</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C13" s="160"/>
-      <x:c r="D13" s="160" t="inlineStr">
-        <x:is>
-          <x:t>OUT</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E13" s="160"/>
-      <x:c r="F13" s="161"/>
-      <x:c r="G13" s="162">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="H13" s="163" t="inlineStr">
-        <x:is>
-          <x:t>윌로</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I13" s="164" t="inlineStr">
-        <x:is>
-          <x:t>아니. 처음 해.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J13" s="163"/>
-      <x:c r="K13" s="165" t="inlineStr">
-        <x:is>
-          <x:t>구간 종료 → 40으로 나감</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:11">
-      <x:c r="A14" s="142">
-        <x:v>920</x:v>
-      </x:c>
-      <x:c r="B14" s="143" t="inlineStr">
-        <x:is>
-          <x:t>ln_0110</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C14" s="144"/>
-      <x:c r="D14" s="144" t="inlineStr">
-        <x:is>
-          <x:t>INPUT</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E14" s="144"/>
-      <x:c r="F14" s="145"/>
-      <x:c r="G14" s="146"/>
-      <x:c r="H14" s="147" t="inlineStr">
-        <x:is>
-          <x:t>라루</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I14" s="148" t="inlineStr">
-        <x:is>
-          <x:t>고맙다는 말은 안 할래.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J14" s="147"/>
-      <x:c r="K14" s="149" t="inlineStr">
-        <x:is>
-          <x:t>구간 진입 (71이 가리킴)</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:11">
-      <x:c r="A15" s="158">
-        <x:v>928</x:v>
-      </x:c>
-      <x:c r="B15" s="159" t="inlineStr">
-        <x:is>
-          <x:t>ln_0111</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C15" s="160"/>
-      <x:c r="D15" s="160" t="inlineStr">
-        <x:is>
-          <x:t>OUT</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E15" s="160"/>
-      <x:c r="F15" s="161"/>
-      <x:c r="G15" s="162" t="inlineStr">
-        <x:is>
-          <x:t>END</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H15" s="163" t="inlineStr">
-        <x:is>
-          <x:t>윌로</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I15" s="164" t="inlineStr">
-        <x:is>
-          <x:t>알아. 너답네.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J15" s="163" t="inlineStr">
-        <x:is>
-          <x:t>trust +1</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K15" s="165" t="inlineStr">
-        <x:is>
-          <x:t>구간 종료 → 에피소드 끝</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:11">
-      <x:c r="C17" s="8" t="inlineStr">
-        <x:is>
-          <x:t>실행 흐름:  10 → 20 → [신뢰높음이면 900…908 → 40] → 40 → 50 → 60 → 선택지(71/72)</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:11">
-      <x:c r="C18" s="98" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">                                71 선택 → 920…928 → END(에피소드 끝)</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:11">
-      <x:c r="C19" s="98"/>
-    </x:row>
-    <x:row r="20" spans="1:11">
-      <x:c r="C20" s="8" t="inlineStr">
-        <x:is>
-          <x:t>평평화 결과 (Yarn 문법):</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:11">
-      <x:c r="C21" s="98" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">   10, 20</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:11">
-      <x:c r="C22" s="98" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">   &lt;&lt;if trust &gt;= 3&gt;&gt;   900, 905, 908   &lt;&lt;endif&gt;&gt;      ← 구간이 조건 자리로 올라오고 원위치에서 사라진다</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="23" spans="1:11">
-      <x:c r="C23" s="98" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">   40, 50, 60</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="24" spans="1:11">
-      <x:c r="C24" s="98" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">   -&gt; 라루의 제안을 듣는다   920, 928                  ← 옵션 본문으로 구간이 들어간다</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="25" spans="1:11">
-      <x:c r="C25" s="98" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">   -&gt; 혼자 문을 연다</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="26" spans="1:11">
-      <x:c r="C26" s="98"/>
-    </x:row>
-    <x:row r="27" spans="1:11">
-      <x:c r="C27" s="8" t="inlineStr">
-        <x:is>
-          <x:t>OUT은 '점프 명령'이 아니라 '여기로 수렴한다'는 선언이다 — Yarn에 노드 내 goto가 없다.</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="28" spans="1:11">
-      <x:c r="C28" s="98" t="inlineStr">
-        <x:is>
-          <x:t>검증기가 평평화 결과와 대조해서 실제로 그렇게 흐르는지 보증한다.</x:t>
-        </x:is>
+      <x:c r="A12" s="0">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="B12" s="167" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="E12" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="F12" s="0" t="s">
+        <x:v>51</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2938,7 +2605,7 @@
   <x:sheetData>
     <x:row r="1" spans="1:3">
       <x:c r="B1" s="43" t="s">
-        <x:v>14</x:v>
+        <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:3">
@@ -2991,7 +2658,7 @@
         </x:is>
       </x:c>
       <x:c r="C7" s="45" t="s">
-        <x:v>15</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:3">
@@ -3075,12 +2742,12 @@
         </x:is>
       </x:c>
       <x:c r="C17" s="166" t="s">
-        <x:v>16</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="B19" s="46" t="s">
-        <x:v>17</x:v>
+        <x:v>42</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:3">
@@ -3090,7 +2757,7 @@
         </x:is>
       </x:c>
       <x:c r="C20" s="45" t="s">
-        <x:v>18</x:v>
+        <x:v>43</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:3">
@@ -3119,7 +2786,7 @@
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="B24" s="46" t="s">
-        <x:v>19</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:3">
@@ -3129,7 +2796,7 @@
         </x:is>
       </x:c>
       <x:c r="C25" s="45" t="s">
-        <x:v>20</x:v>
+        <x:v>45</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:3">
@@ -3355,13 +3022,13 @@
   <x:sheetData>
     <x:row r="1" spans="1:3">
       <x:c r="A1" s="107" t="s">
-        <x:v>21</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B1" s="107" t="s">
-        <x:v>22</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C1" s="107" t="s">
-        <x:v>23</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:3">
@@ -3369,7 +3036,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:3">
@@ -3377,7 +3044,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>6</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/docs/chapter-graph-sample.xlsx
+++ b/docs/chapter-graph-sample.xlsx
@@ -17,7 +17,7 @@
     <x:sheet name="선택지" sheetId="8" r:id="rId11"/>
   </x:sheets>
   <x:definedNames>
-    <x:definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">에피소드!$A$1:$H$7</x:definedName>
+    <x:definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">에피소드!$A$1:$G$7</x:definedName>
     <x:definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'견본_에피소드 main05.02'!$A$1:$K$15</x:definedName>
   </x:definedNames>
   <x:calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -81,67 +81,79 @@
     <x:t>인덱스</x:t>
   </x:si>
   <x:si>
+    <x:t>LineId</x:t>
+  </x:si>
+  <x:si>
+    <x:t>유형</x:t>
+  </x:si>
+  <x:si>
+    <x:t>조건라벨</x:t>
+  </x:si>
+  <x:si>
+    <x:t>화자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>내용</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ln_0001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>윌로</x:t>
+  </x:si>
+  <x:si>
+    <x:t>복도는 조용했다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ln_0002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>라루</x:t>
+  </x:si>
+  <x:si>
+    <x:t>여기서 기다릴까?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>신뢰높음</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ln_0003</x:t>
+  </x:si>
+  <x:si>
+    <x:t>너를 믿어.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>지쳐있음</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ln_0004</x:t>
+  </x:si>
+  <x:si>
+    <x:t>다리가 무거워.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENDIF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ELSEIF</x:t>
+  </x:si>
+  <x:si>
     <x:t>분노누적</x:t>
   </x:si>
   <x:si>
-    <x:t>ELSEIF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENDIF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>다리가 무거워.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ln_0004</x:t>
-  </x:si>
-  <x:si>
-    <x:t>지쳐있음</x:t>
-  </x:si>
-  <x:si>
-    <x:t>유형</x:t>
-  </x:si>
-  <x:si>
-    <x:t>너를 믿어.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ln_0003</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ln_0001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>신뢰높음</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ln_0002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>여기서 기다릴까?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>라루</x:t>
-  </x:si>
-  <x:si>
-    <x:t>화자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>복도는 조용했다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>윌로</x:t>
-  </x:si>
-  <x:si>
-    <x:t>내용</x:t>
-  </x:si>
-  <x:si>
-    <x:t>조건라벨</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LineId</x:t>
+    <x:t>ln_0005</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아직도 화가 나.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ln_0006</x:t>
+  </x:si>
+  <x:si>
+    <x:t>문이 열렸다.</x:t>
   </x:si>
   <x:si>
     <x:t>챕터·에피소드 그래프 엑셀 규격 v5 (2026-08-16) — 실물 견본</x:t>
@@ -171,16 +183,19 @@
     <x:t>메모</x:t>
   </x:si>
   <x:si>
-    <x:t>ln_0005</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아직도 화가 나.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ln_0006</x:t>
-  </x:si>
-  <x:si>
-    <x:t>문이 열렸다.</x:t>
+    <x:t>종류</x:t>
+  </x:si>
+  <x:si>
+    <x:t>엔딩키</x:t>
+  </x:si>
+  <x:si>
+    <x:t>연출</x:t>
+  </x:si>
+  <x:si>
+    <x:t>자동</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ch05_normal</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1528,12 +1543,11 @@
     <x:col min="3" max="3" width="12" style="0" customWidth="1"/>
     <x:col min="4" max="4" width="20" style="0" customWidth="1"/>
     <x:col min="5" max="6" width="7" style="0" customWidth="1"/>
-    <x:col min="7" max="7" width="14" style="0" customWidth="1"/>
-    <x:col min="8" max="8" width="20" style="0" customWidth="1"/>
-    <x:col min="9" max="11" width="9.139196" style="0" customWidth="1"/>
+    <x:col min="7" max="7" width="20" style="0" customWidth="1"/>
+    <x:col min="8" max="11" width="9.139196" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:11">
+    <x:row r="1" spans="1:10">
       <x:c r="A1" s="99" t="inlineStr">
         <x:is>
           <x:t>EpisodeId</x:t>
@@ -1566,16 +1580,11 @@
       </x:c>
       <x:c r="G1" s="99" t="inlineStr">
         <x:is>
-          <x:t>엔딩키</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H1" s="99" t="inlineStr">
-        <x:is>
           <x:t>메모</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="2" spans="1:11">
+    <x:row r="2" spans="1:10">
       <x:c r="A2" s="100" t="inlineStr">
         <x:is>
           <x:t>main05.01</x:t>
@@ -1602,14 +1611,13 @@
       <x:c r="F2" s="102">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G2" s="102"/>
-      <x:c r="H2" s="103" t="inlineStr">
+      <x:c r="G2" s="103" t="inlineStr">
         <x:is>
           <x:t>챕터 진입점</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="3" spans="1:11">
+    <x:row r="3" spans="1:10">
       <x:c r="A3" s="100" t="inlineStr">
         <x:is>
           <x:t>main05.02</x:t>
@@ -1636,10 +1644,9 @@
       <x:c r="F3" s="102">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G3" s="102"/>
-      <x:c r="H3" s="103"/>
-    </x:row>
-    <x:row r="4" spans="1:11">
+      <x:c r="G3" s="103"/>
+    </x:row>
+    <x:row r="4" spans="1:10">
       <x:c r="A4" s="100" t="inlineStr">
         <x:is>
           <x:t>branch05.02A</x:t>
@@ -1666,14 +1673,13 @@
       <x:c r="F4" s="102">
         <x:v>-120</x:v>
       </x:c>
-      <x:c r="G4" s="102"/>
-      <x:c r="H4" s="103" t="inlineStr">
+      <x:c r="G4" s="103" t="inlineStr">
         <x:is>
           <x:t>신뢰 루트</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="5" spans="1:11">
+    <x:row r="5" spans="1:10">
       <x:c r="A5" s="100" t="inlineStr">
         <x:is>
           <x:t>main05.03</x:t>
@@ -1700,14 +1706,13 @@
       <x:c r="F5" s="102">
         <x:v>120</x:v>
       </x:c>
-      <x:c r="G5" s="102"/>
-      <x:c r="H5" s="103" t="inlineStr">
+      <x:c r="G5" s="103" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve"> </x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="6" spans="1:11">
+    <x:row r="6" spans="1:10">
       <x:c r="A6" s="100" t="inlineStr">
         <x:is>
           <x:t>attach05.02s</x:t>
@@ -1734,14 +1739,13 @@
       <x:c r="F6" s="102">
         <x:v>170</x:v>
       </x:c>
-      <x:c r="G6" s="102"/>
-      <x:c r="H6" s="103" t="inlineStr">
+      <x:c r="G6" s="103" t="inlineStr">
         <x:is>
           <x:t>부착(사이드)</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="7" spans="1:11">
+    <x:row r="7" spans="1:10">
       <x:c r="A7" s="100" t="inlineStr">
         <x:is>
           <x:t>main05.end</x:t>
@@ -1768,19 +1772,14 @@
       <x:c r="F7" s="102">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G7" s="102" t="inlineStr">
-        <x:is>
-          <x:t>ch05_normal</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H7" s="103" t="inlineStr">
+      <x:c r="G7" s="103" t="inlineStr">
         <x:is>
           <x:t>엔딩 후보</x:t>
         </x:is>
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:autoFilter ref="A1:H7"/>
+  <x:autoFilter ref="A1:G7"/>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
@@ -1805,7 +1804,7 @@
     <x:col min="8" max="8" width="26" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:8">
+    <x:row r="1" spans="1:11">
       <x:c r="A1" s="99" t="inlineStr">
         <x:is>
           <x:t>출발</x:t>
@@ -1838,8 +1837,17 @@
           <x:t>잠금 안내문</x:t>
         </x:is>
       </x:c>
-    </x:row>
-    <x:row r="2" spans="1:8">
+      <x:c r="I1" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="J1" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="K1" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:11">
       <x:c r="A2" s="100" t="inlineStr">
         <x:is>
           <x:t>main05.01</x:t>
@@ -1862,8 +1870,11 @@
         </x:is>
       </x:c>
       <x:c r="H2" s="102"/>
-    </x:row>
-    <x:row r="3" spans="1:8">
+      <x:c r="I2" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:11">
       <x:c r="A3" s="100" t="inlineStr">
         <x:is>
           <x:t>main05.02</x:t>
@@ -1894,8 +1905,11 @@
           <x:t>신뢰가 부족하다</x:t>
         </x:is>
       </x:c>
-    </x:row>
-    <x:row r="4" spans="1:8">
+      <x:c r="I3" s="0" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:11">
       <x:c r="A4" s="100" t="inlineStr">
         <x:is>
           <x:t>main05.02</x:t>
@@ -1918,8 +1932,11 @@
         </x:is>
       </x:c>
       <x:c r="H4" s="102"/>
-    </x:row>
-    <x:row r="5" spans="1:8">
+      <x:c r="I4" s="0" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="1:11">
       <x:c r="A5" s="100" t="inlineStr">
         <x:is>
           <x:t>branch05.02A</x:t>
@@ -1942,8 +1959,11 @@
         </x:is>
       </x:c>
       <x:c r="H5" s="102"/>
-    </x:row>
-    <x:row r="6" spans="1:8">
+      <x:c r="I5" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:11">
       <x:c r="A6" s="100" t="inlineStr">
         <x:is>
           <x:t>main05.03</x:t>
@@ -1966,15 +1986,25 @@
         </x:is>
       </x:c>
       <x:c r="H6" s="102"/>
+      <x:c r="I6" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="J6" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
-  <x:dataValidations count="3">
+  <x:dataValidations count="4">
     <x:dataValidation type="list" errorStyle="stop" operator="between" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="" error="" promptTitle="" prompt="" sqref="E2:F200">
       <x:formula1>='조건'!$A$2:$A$200</x:formula1>
       <x:formula2/>
     </x:dataValidation>
     <x:dataValidation type="list" errorStyle="stop" operator="between" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="" error="" promptTitle="" prompt="" sqref="G2:G200">
       <x:formula1>"TRUE,FALSE"</x:formula1>
+      <x:formula2/>
+    </x:dataValidation>
+    <x:dataValidation type="list" errorStyle="stop" operator="between" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="" error="" promptTitle="" prompt="" sqref="I2:I200">
+      <x:formula1>"선택지,자동"</x:formula1>
       <x:formula2/>
     </x:dataValidation>
     <x:dataValidation type="list" errorStyle="stop" operator="between" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="0" errorTitle="" error="" promptTitle="" prompt="" sqref="D2:D200">
@@ -2431,19 +2461,19 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B1" s="168" t="s">
-        <x:v>38</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C1" s="107" t="s">
-        <x:v>24</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D1" s="107" t="s">
-        <x:v>37</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="E1" s="107" t="s">
-        <x:v>33</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="F1" s="107" t="s">
-        <x:v>36</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:11">
@@ -2451,13 +2481,13 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B2" s="167" t="s">
-        <x:v>27</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E2" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F2" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:11">
@@ -2465,13 +2495,13 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B3" s="167" t="s">
-        <x:v>29</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E3" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:11">
@@ -2479,10 +2509,10 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="C4" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="D4" s="0" t="s">
         <x:v>30</x:v>
-      </x:c>
-      <x:c r="D4" s="0" t="s">
-        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:11">
@@ -2490,13 +2520,13 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B5" s="167" t="s">
-        <x:v>26</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E5" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F5" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:11">
@@ -2504,10 +2534,10 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="C6" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D6" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:11">
@@ -2515,13 +2545,13 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="B7" s="167" t="s">
-        <x:v>22</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E7" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F7" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:11">
@@ -2529,7 +2559,7 @@
         <x:v>70</x:v>
       </x:c>
       <x:c r="C8" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:11">
@@ -2537,10 +2567,10 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="C9" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D9" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:11">
@@ -2548,13 +2578,13 @@
         <x:v>90</x:v>
       </x:c>
       <x:c r="B10" s="167" t="s">
-        <x:v>48</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E10" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F10" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:11">
@@ -2562,7 +2592,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="C11" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:11">
@@ -2570,13 +2600,13 @@
         <x:v>110</x:v>
       </x:c>
       <x:c r="B12" s="167" t="s">
-        <x:v>50</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E12" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F12" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>42</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2605,7 +2635,7 @@
   <x:sheetData>
     <x:row r="1" spans="1:3">
       <x:c r="B1" s="43" t="s">
-        <x:v>39</x:v>
+        <x:v>43</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:3">
@@ -2658,7 +2688,7 @@
         </x:is>
       </x:c>
       <x:c r="C7" s="45" t="s">
-        <x:v>40</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:3">
@@ -2742,12 +2772,12 @@
         </x:is>
       </x:c>
       <x:c r="C17" s="166" t="s">
-        <x:v>41</x:v>
+        <x:v>45</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="B19" s="46" t="s">
-        <x:v>42</x:v>
+        <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:3">
@@ -2757,7 +2787,7 @@
         </x:is>
       </x:c>
       <x:c r="C20" s="45" t="s">
-        <x:v>43</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:3">
@@ -2786,7 +2816,7 @@
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="B24" s="46" t="s">
-        <x:v>44</x:v>
+        <x:v>48</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:3">
@@ -2796,7 +2826,7 @@
         </x:is>
       </x:c>
       <x:c r="C25" s="45" t="s">
-        <x:v>45</x:v>
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:3">
@@ -3025,10 +3055,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B1" s="107" t="s">
-        <x:v>46</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C1" s="107" t="s">
-        <x:v>47</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:3">

--- a/docs/chapter-graph-sample.xlsx
+++ b/docs/chapter-graph-sample.xlsx
@@ -39,7 +39,10 @@
     <x:t>해금조건</x:t>
   </x:si>
   <x:si>
-    <x:t/>
+    <x:t>엔딩키</x:t>
+  </x:si>
+  <x:si>
+    <x:t>계속</x:t>
   </x:si>
   <x:si>
     <x:t>라루의 제안을 듣는다</x:t>
@@ -48,6 +51,9 @@
     <x:t>혼자 문을 연다</x:t>
   </x:si>
   <x:si>
+    <x:t>ch05_normal</x:t>
+  </x:si>
+  <x:si>
     <x:t>스탯</x:t>
   </x:si>
   <x:si>
@@ -181,21 +187,6 @@
   </x:si>
   <x:si>
     <x:t>메모</x:t>
-  </x:si>
-  <x:si>
-    <x:t>종류</x:t>
-  </x:si>
-  <x:si>
-    <x:t>엔딩키</x:t>
-  </x:si>
-  <x:si>
-    <x:t>연출</x:t>
-  </x:si>
-  <x:si>
-    <x:t>자동</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ch05_normal</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1547,7 +1538,7 @@
     <x:col min="8" max="11" width="9.139196" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:10">
+    <x:row r="1" spans="1:11">
       <x:c r="A1" s="99" t="inlineStr">
         <x:is>
           <x:t>EpisodeId</x:t>
@@ -1584,7 +1575,7 @@
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="2" spans="1:10">
+    <x:row r="2" spans="1:11">
       <x:c r="A2" s="100" t="inlineStr">
         <x:is>
           <x:t>main05.01</x:t>
@@ -1617,7 +1608,7 @@
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="3" spans="1:10">
+    <x:row r="3" spans="1:11">
       <x:c r="A3" s="100" t="inlineStr">
         <x:is>
           <x:t>main05.02</x:t>
@@ -1646,7 +1637,7 @@
       </x:c>
       <x:c r="G3" s="103"/>
     </x:row>
-    <x:row r="4" spans="1:10">
+    <x:row r="4" spans="1:11">
       <x:c r="A4" s="100" t="inlineStr">
         <x:is>
           <x:t>branch05.02A</x:t>
@@ -1679,7 +1670,7 @@
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="5" spans="1:10">
+    <x:row r="5" spans="1:11">
       <x:c r="A5" s="100" t="inlineStr">
         <x:is>
           <x:t>main05.03</x:t>
@@ -1712,7 +1703,7 @@
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="6" spans="1:10">
+    <x:row r="6" spans="1:11">
       <x:c r="A6" s="100" t="inlineStr">
         <x:is>
           <x:t>attach05.02s</x:t>
@@ -1745,7 +1736,7 @@
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="7" spans="1:10">
+    <x:row r="7" spans="1:11">
       <x:c r="A7" s="100" t="inlineStr">
         <x:is>
           <x:t>main05.end</x:t>
@@ -1804,7 +1795,7 @@
     <x:col min="8" max="8" width="26" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:11">
+    <x:row r="1" spans="1:9">
       <x:c r="A1" s="99" t="inlineStr">
         <x:is>
           <x:t>출발</x:t>
@@ -1838,16 +1829,10 @@
         </x:is>
       </x:c>
       <x:c r="I1" s="0" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="J1" s="0" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="K1" s="0" t="s">
-        <x:v>54</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2" spans="1:11">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:9">
       <x:c r="A2" s="100" t="inlineStr">
         <x:is>
           <x:t>main05.01</x:t>
@@ -1860,7 +1845,7 @@
       </x:c>
       <x:c r="C2" s="104"/>
       <x:c r="D2" s="102" t="s">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E2" s="102"/>
       <x:c r="F2" s="101"/>
@@ -1870,11 +1855,8 @@
         </x:is>
       </x:c>
       <x:c r="H2" s="102"/>
-      <x:c r="I2" s="0" t="s">
-        <x:v>55</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" spans="1:11">
+    </x:row>
+    <x:row r="3" spans="1:9">
       <x:c r="A3" s="100" t="inlineStr">
         <x:is>
           <x:t>main05.02</x:t>
@@ -1887,7 +1869,7 @@
       </x:c>
       <x:c r="C3" s="104"/>
       <x:c r="D3" s="102" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E3" s="102"/>
       <x:c r="F3" s="101" t="inlineStr">
@@ -1905,11 +1887,8 @@
           <x:t>신뢰가 부족하다</x:t>
         </x:is>
       </x:c>
-      <x:c r="I3" s="0" t="s">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" spans="1:11">
+    </x:row>
+    <x:row r="4" spans="1:9">
       <x:c r="A4" s="100" t="inlineStr">
         <x:is>
           <x:t>main05.02</x:t>
@@ -1922,7 +1901,7 @@
       </x:c>
       <x:c r="C4" s="104"/>
       <x:c r="D4" s="102" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="E4" s="102"/>
       <x:c r="F4" s="101"/>
@@ -1932,11 +1911,8 @@
         </x:is>
       </x:c>
       <x:c r="H4" s="102"/>
-      <x:c r="I4" s="0" t="s">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" spans="1:11">
+    </x:row>
+    <x:row r="5" spans="1:9">
       <x:c r="A5" s="100" t="inlineStr">
         <x:is>
           <x:t>branch05.02A</x:t>
@@ -1949,7 +1925,7 @@
       </x:c>
       <x:c r="C5" s="104"/>
       <x:c r="D5" s="102" t="s">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E5" s="102"/>
       <x:c r="F5" s="101"/>
@@ -1959,11 +1935,8 @@
         </x:is>
       </x:c>
       <x:c r="H5" s="102"/>
-      <x:c r="I5" s="0" t="s">
-        <x:v>55</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" spans="1:11">
+    </x:row>
+    <x:row r="6" spans="1:9">
       <x:c r="A6" s="100" t="inlineStr">
         <x:is>
           <x:t>main05.03</x:t>
@@ -1976,7 +1949,7 @@
       </x:c>
       <x:c r="C6" s="104"/>
       <x:c r="D6" s="102" t="s">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E6" s="102"/>
       <x:c r="F6" s="101"/>
@@ -1987,24 +1960,17 @@
       </x:c>
       <x:c r="H6" s="102"/>
       <x:c r="I6" s="0" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="J6" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:dataValidations count="4">
+  <x:dataValidations count="3">
     <x:dataValidation type="list" errorStyle="stop" operator="between" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="" error="" promptTitle="" prompt="" sqref="E2:F200">
       <x:formula1>='조건'!$A$2:$A$200</x:formula1>
       <x:formula2/>
     </x:dataValidation>
     <x:dataValidation type="list" errorStyle="stop" operator="between" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="" error="" promptTitle="" prompt="" sqref="G2:G200">
       <x:formula1>"TRUE,FALSE"</x:formula1>
-      <x:formula2/>
-    </x:dataValidation>
-    <x:dataValidation type="list" errorStyle="stop" operator="between" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="" error="" promptTitle="" prompt="" sqref="I2:I200">
-      <x:formula1>"선택지,자동"</x:formula1>
       <x:formula2/>
     </x:dataValidation>
     <x:dataValidation type="list" errorStyle="stop" operator="between" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="0" errorTitle="" error="" promptTitle="" prompt="" sqref="D2:D200">
@@ -2041,13 +2007,13 @@
         </x:is>
       </x:c>
       <x:c r="B1" s="105" t="s">
-        <x:v>7</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C1" s="105" t="s">
-        <x:v>8</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D1" s="105" t="s">
-        <x:v>9</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="E1" s="105" t="inlineStr">
         <x:is>
@@ -2067,13 +2033,13 @@
         </x:is>
       </x:c>
       <x:c r="B2" s="101" t="s">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C2" s="101" t="s">
-        <x:v>11</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D2" s="101" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E2" s="102" t="inlineStr">
         <x:is>
@@ -2088,13 +2054,13 @@
         </x:is>
       </x:c>
       <x:c r="B3" s="101" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C3" s="101" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C3" s="101" t="s">
-        <x:v>11</x:v>
-      </x:c>
       <x:c r="D3" s="101" t="s">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E3" s="102" t="inlineStr">
         <x:is>
@@ -2205,11 +2171,11 @@
         </x:is>
       </x:c>
       <x:c r="F1" s="107" t="s">
-        <x:v>15</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G1" s="10"/>
       <x:c r="H1" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:8">
@@ -2458,22 +2424,22 @@
   <x:sheetData>
     <x:row r="1" spans="1:11">
       <x:c r="A1" s="107" t="s">
-        <x:v>17</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B1" s="168" t="s">
-        <x:v>18</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C1" s="107" t="s">
-        <x:v>19</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D1" s="107" t="s">
-        <x:v>20</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="E1" s="107" t="s">
-        <x:v>21</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F1" s="107" t="s">
-        <x:v>22</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:11">
@@ -2481,13 +2447,13 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B2" s="167" t="s">
-        <x:v>23</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E2" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="F2" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:11">
@@ -2495,13 +2461,13 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B3" s="167" t="s">
-        <x:v>26</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E3" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:11">
@@ -2509,10 +2475,10 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="C4" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D4" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:11">
@@ -2520,13 +2486,13 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B5" s="167" t="s">
-        <x:v>31</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E5" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="F5" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:11">
@@ -2534,10 +2500,10 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="C6" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D6" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:11">
@@ -2545,13 +2511,13 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="B7" s="167" t="s">
-        <x:v>34</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E7" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F7" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:11">
@@ -2559,7 +2525,7 @@
         <x:v>70</x:v>
       </x:c>
       <x:c r="C8" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:11">
@@ -2567,10 +2533,10 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="C9" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D9" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:11">
@@ -2578,13 +2544,13 @@
         <x:v>90</x:v>
       </x:c>
       <x:c r="B10" s="167" t="s">
-        <x:v>39</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E10" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F10" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>42</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:11">
@@ -2592,7 +2558,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="C11" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:11">
@@ -2600,13 +2566,13 @@
         <x:v>110</x:v>
       </x:c>
       <x:c r="B12" s="167" t="s">
-        <x:v>41</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E12" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="F12" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2635,7 +2601,7 @@
   <x:sheetData>
     <x:row r="1" spans="1:3">
       <x:c r="B1" s="43" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:3">
@@ -2688,7 +2654,7 @@
         </x:is>
       </x:c>
       <x:c r="C7" s="45" t="s">
-        <x:v>44</x:v>
+        <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:3">
@@ -2772,12 +2738,12 @@
         </x:is>
       </x:c>
       <x:c r="C17" s="166" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="B19" s="46" t="s">
-        <x:v>46</x:v>
+        <x:v>48</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:3">
@@ -2787,7 +2753,7 @@
         </x:is>
       </x:c>
       <x:c r="C20" s="45" t="s">
-        <x:v>47</x:v>
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:3">
@@ -2816,7 +2782,7 @@
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="B24" s="46" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:3">
@@ -2826,7 +2792,7 @@
         </x:is>
       </x:c>
       <x:c r="C25" s="45" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:3">
@@ -3052,13 +3018,13 @@
   <x:sheetData>
     <x:row r="1" spans="1:3">
       <x:c r="A1" s="107" t="s">
-        <x:v>17</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B1" s="107" t="s">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C1" s="107" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:3">
@@ -3066,7 +3032,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:3">
@@ -3074,7 +3040,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/docs/chapter-graph-sample.xlsx
+++ b/docs/chapter-graph-sample.xlsx
@@ -386,7 +386,7 @@
       </x:bottom>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="67">
+  <x:cellStyleXfs count="68">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -586,8 +586,11 @@
     <x:xf numFmtId="0" fontId="14" fillId="15" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="169">
+  <x:cellXfs count="170">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="0" pivotButton="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" quotePrefix="0" pivotButton="0" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
@@ -1148,6 +1151,10 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="14" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -2411,8 +2418,9 @@
   <x:sheetFormatPr baseColWidth="8" defaultColWidth="9.139196" defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="9" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="11" style="167" customWidth="1"/>
-    <x:col min="3" max="4" width="9" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="11" style="0" customWidth="1"/>
+    <x:col min="3" max="3" width="9" style="167" customWidth="1"/>
+    <x:col min="4" max="4" width="9" style="0" customWidth="1"/>
     <x:col min="5" max="5" width="13" style="0" customWidth="1"/>
     <x:col min="6" max="6" width="50.710625" style="0" customWidth="1"/>
     <x:col min="7" max="7" width="7" style="0" customWidth="1"/>
@@ -2426,11 +2434,11 @@
       <x:c r="A1" s="107" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="B1" s="168" t="s">
+      <x:c r="B1" s="169" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C1" s="168" t="s">
         <x:v>20</x:v>
-      </x:c>
-      <x:c r="C1" s="107" t="s">
-        <x:v>21</x:v>
       </x:c>
       <x:c r="D1" s="107" t="s">
         <x:v>22</x:v>
@@ -2446,7 +2454,7 @@
       <x:c r="A2" s="0">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="B2" s="167" t="s">
+      <x:c r="C2" s="167" t="s">
         <x:v>25</x:v>
       </x:c>
       <x:c r="E2" s="0" t="s">
@@ -2460,7 +2468,7 @@
       <x:c r="A3" s="0">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="B3" s="167" t="s">
+      <x:c r="C3" s="167" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="E3" s="0" t="s">
@@ -2474,9 +2482,10 @@
       <x:c r="A4" s="0">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="C4" s="0" t="s">
+      <x:c r="B4" s="0" t="s">
         <x:v>31</x:v>
       </x:c>
+      <x:c r="C4" s="167"/>
       <x:c r="D4" s="0" t="s">
         <x:v>32</x:v>
       </x:c>
@@ -2485,7 +2494,7 @@
       <x:c r="A5" s="0">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="B5" s="167" t="s">
+      <x:c r="C5" s="167" t="s">
         <x:v>33</x:v>
       </x:c>
       <x:c r="E5" s="0" t="s">
@@ -2499,9 +2508,10 @@
       <x:c r="A6" s="0">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="C6" s="0" t="s">
+      <x:c r="B6" s="0" t="s">
         <x:v>31</x:v>
       </x:c>
+      <x:c r="C6" s="167"/>
       <x:c r="D6" s="0" t="s">
         <x:v>35</x:v>
       </x:c>
@@ -2510,7 +2520,7 @@
       <x:c r="A7" s="0">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="B7" s="167" t="s">
+      <x:c r="C7" s="167" t="s">
         <x:v>36</x:v>
       </x:c>
       <x:c r="E7" s="0" t="s">
@@ -2524,17 +2534,19 @@
       <x:c r="A8" s="0">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="C8" s="0" t="s">
+      <x:c r="B8" s="0" t="s">
         <x:v>38</x:v>
       </x:c>
+      <x:c r="C8" s="167"/>
     </x:row>
     <x:row r="9" spans="1:11">
       <x:c r="A9" s="0">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="C9" s="0" t="s">
+      <x:c r="B9" s="0" t="s">
         <x:v>39</x:v>
       </x:c>
+      <x:c r="C9" s="167"/>
       <x:c r="D9" s="0" t="s">
         <x:v>40</x:v>
       </x:c>
@@ -2543,7 +2555,7 @@
       <x:c r="A10" s="0">
         <x:v>90</x:v>
       </x:c>
-      <x:c r="B10" s="167" t="s">
+      <x:c r="C10" s="167" t="s">
         <x:v>41</x:v>
       </x:c>
       <x:c r="E10" s="0" t="s">
@@ -2557,15 +2569,16 @@
       <x:c r="A11" s="0">
         <x:v>100</x:v>
       </x:c>
-      <x:c r="C11" s="0" t="s">
+      <x:c r="B11" s="0" t="s">
         <x:v>38</x:v>
       </x:c>
+      <x:c r="C11" s="167"/>
     </x:row>
     <x:row r="12" spans="1:11">
       <x:c r="A12" s="0">
         <x:v>110</x:v>
       </x:c>
-      <x:c r="B12" s="167" t="s">
+      <x:c r="C12" s="167" t="s">
         <x:v>43</x:v>
       </x:c>
       <x:c r="E12" s="0" t="s">

--- a/docs/chapter-graph-sample.xlsx
+++ b/docs/chapter-graph-sample.xlsx
@@ -87,12 +87,12 @@
     <x:t>인덱스</x:t>
   </x:si>
   <x:si>
+    <x:t>유형</x:t>
+  </x:si>
+  <x:si>
     <x:t>LineId</x:t>
   </x:si>
   <x:si>
-    <x:t>유형</x:t>
-  </x:si>
-  <x:si>
     <x:t>조건라벨</x:t>
   </x:si>
   <x:si>
@@ -187,6 +187,24 @@
   </x:si>
   <x:si>
     <x:t>메모</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20</x:t>
+  </x:si>
+  <x:si>
+    <x:t>40</x:t>
+  </x:si>
+  <x:si>
+    <x:t>60</x:t>
+  </x:si>
+  <x:si>
+    <x:t>90</x:t>
+  </x:si>
+  <x:si>
+    <x:t>110</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -2419,8 +2437,8 @@
   <x:cols>
     <x:col min="1" max="1" width="9" style="0" customWidth="1"/>
     <x:col min="2" max="2" width="11" style="0" customWidth="1"/>
-    <x:col min="3" max="3" width="9" style="167" customWidth="1"/>
-    <x:col min="4" max="4" width="9" style="0" customWidth="1"/>
+    <x:col min="3" max="3" width="9" style="0" customWidth="1"/>
+    <x:col min="4" max="4" width="9" style="167" customWidth="1"/>
     <x:col min="5" max="5" width="13" style="0" customWidth="1"/>
     <x:col min="6" max="6" width="50.710625" style="0" customWidth="1"/>
     <x:col min="7" max="7" width="7" style="0" customWidth="1"/>
@@ -2431,30 +2449,30 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:11">
-      <x:c r="A1" s="107" t="s">
+      <x:c r="A1" s="169" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B1" s="169" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C1" s="169" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="B1" s="169" t="s">
+      <x:c r="D1" s="168" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="C1" s="168" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D1" s="107" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="E1" s="107" t="s">
+      <x:c r="E1" s="169" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="F1" s="107" t="s">
+      <x:c r="F1" s="169" t="s">
         <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:11">
-      <x:c r="A2" s="0">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C2" s="167" t="s">
+      <x:c r="C2" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="D2" s="167" t="s">
         <x:v>25</x:v>
       </x:c>
       <x:c r="E2" s="0" t="s">
@@ -2465,10 +2483,10 @@
       </x:c>
     </x:row>
     <x:row r="3" spans="1:11">
-      <x:c r="A3" s="0">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C3" s="167" t="s">
+      <x:c r="C3" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="D3" s="167" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="E3" s="0" t="s">
@@ -2479,22 +2497,19 @@
       </x:c>
     </x:row>
     <x:row r="4" spans="1:11">
-      <x:c r="A4" s="0">
-        <x:v>30</x:v>
+      <x:c r="A4" s="0" t="s">
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="C4" s="167"/>
-      <x:c r="D4" s="0" t="s">
         <x:v>32</x:v>
       </x:c>
+      <x:c r="D4" s="167"/>
     </x:row>
     <x:row r="5" spans="1:11">
-      <x:c r="A5" s="0">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="C5" s="167" t="s">
+      <x:c r="C5" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="D5" s="167" t="s">
         <x:v>33</x:v>
       </x:c>
       <x:c r="E5" s="0" t="s">
@@ -2505,22 +2520,19 @@
       </x:c>
     </x:row>
     <x:row r="6" spans="1:11">
-      <x:c r="A6" s="0">
-        <x:v>50</x:v>
+      <x:c r="A6" s="0" t="s">
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="C6" s="167"/>
-      <x:c r="D6" s="0" t="s">
         <x:v>35</x:v>
       </x:c>
+      <x:c r="D6" s="167"/>
     </x:row>
     <x:row r="7" spans="1:11">
-      <x:c r="A7" s="0">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="C7" s="167" t="s">
+      <x:c r="C7" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="D7" s="167" t="s">
         <x:v>36</x:v>
       </x:c>
       <x:c r="E7" s="0" t="s">
@@ -2531,31 +2543,24 @@
       </x:c>
     </x:row>
     <x:row r="8" spans="1:11">
-      <x:c r="A8" s="0">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="B8" s="0" t="s">
+      <x:c r="A8" s="0" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="C8" s="167"/>
     </x:row>
     <x:row r="9" spans="1:11">
-      <x:c r="A9" s="0">
-        <x:v>80</x:v>
+      <x:c r="A9" s="0" t="s">
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="C9" s="167"/>
-      <x:c r="D9" s="0" t="s">
         <x:v>40</x:v>
       </x:c>
+      <x:c r="D9" s="167"/>
     </x:row>
     <x:row r="10" spans="1:11">
-      <x:c r="A10" s="0">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="C10" s="167" t="s">
+      <x:c r="C10" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="D10" s="167" t="s">
         <x:v>41</x:v>
       </x:c>
       <x:c r="E10" s="0" t="s">
@@ -2566,19 +2571,15 @@
       </x:c>
     </x:row>
     <x:row r="11" spans="1:11">
-      <x:c r="A11" s="0">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="B11" s="0" t="s">
+      <x:c r="A11" s="0" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="C11" s="167"/>
     </x:row>
     <x:row r="12" spans="1:11">
-      <x:c r="A12" s="0">
-        <x:v>110</x:v>
-      </x:c>
-      <x:c r="C12" s="167" t="s">
+      <x:c r="C12" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="D12" s="167" t="s">
         <x:v>43</x:v>
       </x:c>
       <x:c r="E12" s="0" t="s">

--- a/docs/chapter-graph-sample.xlsx
+++ b/docs/chapter-graph-sample.xlsx
@@ -17,7 +17,7 @@
     <x:sheet name="선택지" sheetId="8" r:id="rId11"/>
   </x:sheets>
   <x:definedNames>
-    <x:definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">에피소드!$A$1:$G$7</x:definedName>
+    <x:definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">에피소드!$A$1:$F$7</x:definedName>
     <x:definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">간선!$A$1:$K$6</x:definedName>
     <x:definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">조건!$A$1:$E$5</x:definedName>
     <x:definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">스탯!$A$1:$F$4</x:definedName>
@@ -31,6 +31,15 @@
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:si>
+    <x:t>도달불가 허용</x:t>
+  </x:si>
+  <x:si>
+    <x:t>의도한 섬 — 들어오는 간선이 없다(`도달불가 허용`으로 표시)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRUE</x:t>
+  </x:si>
   <x:si>
     <x:t>스탯변화</x:t>
   </x:si>
@@ -48,6 +57,9 @@
   </x:si>
   <x:si>
     <x:t>계속</x:t>
+  </x:si>
+  <x:si>
+    <x:t>복도지남 true</x:t>
   </x:si>
   <x:si>
     <x:t>라루의 제안을 듣는다</x:t>
@@ -83,10 +95,28 @@
     <x:t>5</x:t>
   </x:si>
   <x:si>
+    <x:t>복도지남</x:t>
+  </x:si>
+  <x:si>
+    <x:t>true</x:t>
+  </x:si>
+  <x:si>
+    <x:t>복도(main05.02)를 지났는가 — 폐지된 cleared: 를 대신하는 깃발</x:t>
+  </x:si>
+  <x:si>
     <x:t>타입</x:t>
   </x:si>
   <x:si>
     <x:t>⚠ 읽기전용 미러 — 원천은 game.definition.json. 브리지가 왕복하는 Tier 2 키 목록이기도 하다(2~5개).</x:t>
+  </x:si>
+  <x:si>
+    <x:t>복도를 지났다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FALSE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>bool</x:t>
   </x:si>
   <x:si>
     <x:t>유형</x:t>
@@ -1854,14 +1884,13 @@
   <x:cols>
     <x:col min="1" max="1" width="14.710625" style="0" customWidth="1"/>
     <x:col min="2" max="2" width="22.710625" style="0" customWidth="1"/>
-    <x:col min="3" max="3" width="12.710625" style="0" customWidth="1"/>
-    <x:col min="4" max="4" width="20.710625" style="0" customWidth="1"/>
-    <x:col min="5" max="6" width="7.710625" style="0" customWidth="1"/>
-    <x:col min="7" max="7" width="20.710625" style="0" customWidth="1"/>
-    <x:col min="8" max="11" width="9.139196" style="0" customWidth="1"/>
+    <x:col min="3" max="3" width="20.710625" style="0" customWidth="1"/>
+    <x:col min="4" max="5" width="7.710625" style="0" customWidth="1"/>
+    <x:col min="6" max="6" width="20.710625" style="0" customWidth="1"/>
+    <x:col min="7" max="11" width="9.139196" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:11">
+    <x:row r="1" spans="1:10">
       <x:c r="A1" s="170" t="inlineStr">
         <x:is>
           <x:t>EpisodeId</x:t>
@@ -1874,31 +1903,29 @@
       </x:c>
       <x:c r="C1" s="170" t="inlineStr">
         <x:is>
-          <x:t>종류</x:t>
+          <x:t>대사엔트리</x:t>
         </x:is>
       </x:c>
       <x:c r="D1" s="170" t="inlineStr">
         <x:is>
-          <x:t>대사엔트리</x:t>
+          <x:t>X</x:t>
         </x:is>
       </x:c>
       <x:c r="E1" s="170" t="inlineStr">
         <x:is>
-          <x:t>X</x:t>
+          <x:t>Y</x:t>
         </x:is>
       </x:c>
       <x:c r="F1" s="170" t="inlineStr">
         <x:is>
-          <x:t>Y</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G1" s="170" t="inlineStr">
-        <x:is>
           <x:t>메모</x:t>
         </x:is>
       </x:c>
-    </x:row>
-    <x:row r="2" spans="1:11">
+      <x:c r="J1" s="0" t="s">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:10">
       <x:c r="A2" s="171" t="inlineStr">
         <x:is>
           <x:t>main05.01</x:t>
@@ -1909,1928 +1936,1706 @@
           <x:t>닫힌 문 앞에서</x:t>
         </x:is>
       </x:c>
-      <x:c r="C2" s="172" t="inlineStr">
-        <x:is>
-          <x:t>Main</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D2" s="173" t="inlineStr">
+      <x:c r="C2" s="173" t="inlineStr">
         <x:is>
           <x:t>Story_ch05_01</x:t>
         </x:is>
+      </x:c>
+      <x:c r="D2" s="173">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E2" s="173">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F2" s="173">
+      <x:c r="F2" s="174" t="inlineStr">
+        <x:is>
+          <x:t>챕터 진입점</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:10">
+      <x:c r="A3" s="171" t="inlineStr">
+        <x:is>
+          <x:t>main05.02</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B3" s="172" t="inlineStr">
+        <x:is>
+          <x:t>조용한 복도</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C3" s="173" t="inlineStr">
+        <x:is>
+          <x:t>Story_ch05_02</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D3" s="173">
+        <x:v>220</x:v>
+      </x:c>
+      <x:c r="E3" s="173">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G2" s="174" t="inlineStr">
-        <x:is>
-          <x:t>챕터 진입점</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="3" spans="1:11">
-      <x:c r="A3" s="171" t="inlineStr">
-        <x:is>
-          <x:t>main05.02</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B3" s="172" t="inlineStr">
-        <x:is>
-          <x:t>조용한 복도</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C3" s="172" t="inlineStr">
-        <x:is>
-          <x:t>Main</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D3" s="173" t="inlineStr">
-        <x:is>
-          <x:t>Story_ch05_02</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E3" s="173">
+      <x:c r="F3" s="174"/>
+    </x:row>
+    <x:row r="4" spans="1:10">
+      <x:c r="A4" s="171" t="inlineStr">
+        <x:is>
+          <x:t>branch05.02A</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B4" s="172" t="inlineStr">
+        <x:is>
+          <x:t>라루의 제안</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C4" s="173" t="inlineStr">
+        <x:is>
+          <x:t>Story_ch05_02A</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D4" s="173">
+        <x:v>440</x:v>
+      </x:c>
+      <x:c r="E4" s="173">
+        <x:v>-120</x:v>
+      </x:c>
+      <x:c r="F4" s="174" t="inlineStr">
+        <x:is>
+          <x:t>신뢰 루트</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="1:10">
+      <x:c r="A5" s="171" t="inlineStr">
+        <x:is>
+          <x:t>main05.03</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B5" s="172" t="inlineStr">
+        <x:is>
+          <x:t>문 너머</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C5" s="173" t="inlineStr">
+        <x:is>
+          <x:t>Story_ch05_03</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D5" s="173">
+        <x:v>440</x:v>
+      </x:c>
+      <x:c r="E5" s="173">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="F5" s="174" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"> </x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:10">
+      <x:c r="A6" s="171" t="inlineStr">
+        <x:is>
+          <x:t>attach05.02s</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B6" s="172" t="inlineStr">
+        <x:is>
+          <x:t>샘플 섬 회상</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C6" s="173" t="inlineStr">
+        <x:is>
+          <x:t>Story_ch05_02_side</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D6" s="173">
         <x:v>220</x:v>
       </x:c>
-      <x:c r="F3" s="173">
+      <x:c r="E6" s="173">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="F6" s="174" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J6" s="0" t="s">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="1:10">
+      <x:c r="A7" s="171" t="inlineStr">
+        <x:is>
+          <x:t>main05.end</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B7" s="172" t="inlineStr">
+        <x:is>
+          <x:t>선택의 밤</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C7" s="173" t="inlineStr">
+        <x:is>
+          <x:t>Story_ch05_end</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D7" s="173">
+        <x:v>680</x:v>
+      </x:c>
+      <x:c r="E7" s="173">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G3" s="174"/>
-    </x:row>
-    <x:row r="4" spans="1:11">
-      <x:c r="A4" s="171" t="inlineStr">
-        <x:is>
-          <x:t>branch05.02A</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B4" s="172" t="inlineStr">
-        <x:is>
-          <x:t>라루의 제안</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C4" s="172" t="inlineStr">
-        <x:is>
-          <x:t>Main</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D4" s="173" t="inlineStr">
-        <x:is>
-          <x:t>Story_ch05_02A</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E4" s="173">
-        <x:v>440</x:v>
-      </x:c>
-      <x:c r="F4" s="173">
-        <x:v>-120</x:v>
-      </x:c>
-      <x:c r="G4" s="174" t="inlineStr">
-        <x:is>
-          <x:t>신뢰 루트</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="5" spans="1:11">
-      <x:c r="A5" s="171" t="inlineStr">
-        <x:is>
-          <x:t>main05.03</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B5" s="172" t="inlineStr">
-        <x:is>
-          <x:t>문 너머</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C5" s="172" t="inlineStr">
-        <x:is>
-          <x:t>Main</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D5" s="173" t="inlineStr">
-        <x:is>
-          <x:t>Story_ch05_03</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E5" s="173">
-        <x:v>440</x:v>
-      </x:c>
-      <x:c r="F5" s="173">
-        <x:v>120</x:v>
-      </x:c>
-      <x:c r="G5" s="174" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve"> </x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="6" spans="1:11">
-      <x:c r="A6" s="171" t="inlineStr">
-        <x:is>
-          <x:t>attach05.02s</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B6" s="172" t="inlineStr">
-        <x:is>
-          <x:t>샘플 섬 회상</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C6" s="172" t="inlineStr">
-        <x:is>
-          <x:t>Attachment</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D6" s="173" t="inlineStr">
-        <x:is>
-          <x:t>Story_ch05_02_side</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E6" s="173">
-        <x:v>220</x:v>
-      </x:c>
-      <x:c r="F6" s="173">
-        <x:v>170</x:v>
-      </x:c>
-      <x:c r="G6" s="174" t="inlineStr">
-        <x:is>
-          <x:t>부착(사이드)</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="7" spans="1:11">
-      <x:c r="A7" s="171" t="inlineStr">
-        <x:is>
-          <x:t>main05.end</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B7" s="172" t="inlineStr">
-        <x:is>
-          <x:t>선택의 밤</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C7" s="172" t="inlineStr">
-        <x:is>
-          <x:t>Main</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D7" s="173" t="inlineStr">
-        <x:is>
-          <x:t>Story_ch05_end</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E7" s="173">
-        <x:v>680</x:v>
-      </x:c>
-      <x:c r="F7" s="173">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="174" t="inlineStr">
+      <x:c r="F7" s="174" t="inlineStr">
         <x:is>
           <x:t>엔딩 후보</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="8" spans="1:11">
+    <x:row r="8" spans="1:10">
       <x:c r="A8" s="175"/>
       <x:c r="B8" s="176"/>
       <x:c r="C8" s="176"/>
       <x:c r="D8" s="176"/>
       <x:c r="E8" s="176"/>
-      <x:c r="F8" s="176"/>
-      <x:c r="G8" s="177"/>
-    </x:row>
-    <x:row r="9" spans="1:11">
+      <x:c r="F8" s="177"/>
+    </x:row>
+    <x:row r="9" spans="1:10">
       <x:c r="A9" s="175"/>
       <x:c r="B9" s="176"/>
       <x:c r="C9" s="176"/>
       <x:c r="D9" s="176"/>
       <x:c r="E9" s="176"/>
-      <x:c r="F9" s="176"/>
-      <x:c r="G9" s="177"/>
-    </x:row>
-    <x:row r="10" spans="1:11">
+      <x:c r="F9" s="177"/>
+    </x:row>
+    <x:row r="10" spans="1:10">
       <x:c r="A10" s="175"/>
       <x:c r="B10" s="176"/>
       <x:c r="C10" s="176"/>
       <x:c r="D10" s="176"/>
       <x:c r="E10" s="176"/>
-      <x:c r="F10" s="176"/>
-      <x:c r="G10" s="177"/>
-    </x:row>
-    <x:row r="11" spans="1:11">
+      <x:c r="F10" s="177"/>
+    </x:row>
+    <x:row r="11" spans="1:10">
       <x:c r="A11" s="175"/>
       <x:c r="B11" s="176"/>
       <x:c r="C11" s="176"/>
       <x:c r="D11" s="176"/>
       <x:c r="E11" s="176"/>
-      <x:c r="F11" s="176"/>
-      <x:c r="G11" s="177"/>
-    </x:row>
-    <x:row r="12" spans="1:11">
+      <x:c r="F11" s="177"/>
+    </x:row>
+    <x:row r="12" spans="1:10">
       <x:c r="A12" s="175"/>
       <x:c r="B12" s="176"/>
       <x:c r="C12" s="176"/>
       <x:c r="D12" s="176"/>
       <x:c r="E12" s="176"/>
-      <x:c r="F12" s="176"/>
-      <x:c r="G12" s="177"/>
-    </x:row>
-    <x:row r="13" spans="1:11">
+      <x:c r="F12" s="177"/>
+    </x:row>
+    <x:row r="13" spans="1:10">
       <x:c r="A13" s="175"/>
       <x:c r="B13" s="176"/>
       <x:c r="C13" s="176"/>
       <x:c r="D13" s="176"/>
       <x:c r="E13" s="176"/>
-      <x:c r="F13" s="176"/>
-      <x:c r="G13" s="177"/>
-    </x:row>
-    <x:row r="14" spans="1:11">
+      <x:c r="F13" s="177"/>
+    </x:row>
+    <x:row r="14" spans="1:10">
       <x:c r="A14" s="175"/>
       <x:c r="B14" s="176"/>
       <x:c r="C14" s="176"/>
       <x:c r="D14" s="176"/>
       <x:c r="E14" s="176"/>
-      <x:c r="F14" s="176"/>
-      <x:c r="G14" s="177"/>
-    </x:row>
-    <x:row r="15" spans="1:11">
+      <x:c r="F14" s="177"/>
+    </x:row>
+    <x:row r="15" spans="1:10">
       <x:c r="A15" s="175"/>
       <x:c r="B15" s="176"/>
       <x:c r="C15" s="176"/>
       <x:c r="D15" s="176"/>
       <x:c r="E15" s="176"/>
-      <x:c r="F15" s="176"/>
-      <x:c r="G15" s="177"/>
-    </x:row>
-    <x:row r="16" spans="1:11">
+      <x:c r="F15" s="177"/>
+    </x:row>
+    <x:row r="16" spans="1:10">
       <x:c r="A16" s="175"/>
       <x:c r="B16" s="176"/>
       <x:c r="C16" s="176"/>
       <x:c r="D16" s="176"/>
       <x:c r="E16" s="176"/>
-      <x:c r="F16" s="176"/>
-      <x:c r="G16" s="177"/>
-    </x:row>
-    <x:row r="17" spans="1:11">
+      <x:c r="F16" s="177"/>
+    </x:row>
+    <x:row r="17" spans="1:10">
       <x:c r="A17" s="175"/>
       <x:c r="B17" s="176"/>
       <x:c r="C17" s="176"/>
       <x:c r="D17" s="176"/>
       <x:c r="E17" s="176"/>
-      <x:c r="F17" s="176"/>
-      <x:c r="G17" s="177"/>
-    </x:row>
-    <x:row r="18" spans="1:11">
+      <x:c r="F17" s="177"/>
+    </x:row>
+    <x:row r="18" spans="1:10">
       <x:c r="A18" s="175"/>
       <x:c r="B18" s="176"/>
       <x:c r="C18" s="176"/>
       <x:c r="D18" s="176"/>
       <x:c r="E18" s="176"/>
-      <x:c r="F18" s="176"/>
-      <x:c r="G18" s="177"/>
-    </x:row>
-    <x:row r="19" spans="1:11">
+      <x:c r="F18" s="177"/>
+    </x:row>
+    <x:row r="19" spans="1:10">
       <x:c r="A19" s="175"/>
       <x:c r="B19" s="176"/>
       <x:c r="C19" s="176"/>
       <x:c r="D19" s="176"/>
       <x:c r="E19" s="176"/>
-      <x:c r="F19" s="176"/>
-      <x:c r="G19" s="177"/>
-    </x:row>
-    <x:row r="20" spans="1:11">
+      <x:c r="F19" s="177"/>
+    </x:row>
+    <x:row r="20" spans="1:10">
       <x:c r="A20" s="175"/>
       <x:c r="B20" s="176"/>
       <x:c r="C20" s="176"/>
       <x:c r="D20" s="176"/>
       <x:c r="E20" s="176"/>
-      <x:c r="F20" s="176"/>
-      <x:c r="G20" s="177"/>
-    </x:row>
-    <x:row r="21" spans="1:11">
+      <x:c r="F20" s="177"/>
+    </x:row>
+    <x:row r="21" spans="1:10">
       <x:c r="A21" s="175"/>
       <x:c r="B21" s="176"/>
       <x:c r="C21" s="176"/>
       <x:c r="D21" s="176"/>
       <x:c r="E21" s="176"/>
-      <x:c r="F21" s="176"/>
-      <x:c r="G21" s="177"/>
-    </x:row>
-    <x:row r="22" spans="1:11">
+      <x:c r="F21" s="177"/>
+    </x:row>
+    <x:row r="22" spans="1:10">
       <x:c r="A22" s="175"/>
       <x:c r="B22" s="176"/>
       <x:c r="C22" s="176"/>
       <x:c r="D22" s="176"/>
       <x:c r="E22" s="176"/>
-      <x:c r="F22" s="176"/>
-      <x:c r="G22" s="177"/>
-    </x:row>
-    <x:row r="23" spans="1:11">
+      <x:c r="F22" s="177"/>
+    </x:row>
+    <x:row r="23" spans="1:10">
       <x:c r="A23" s="175"/>
       <x:c r="B23" s="176"/>
       <x:c r="C23" s="176"/>
       <x:c r="D23" s="176"/>
       <x:c r="E23" s="176"/>
-      <x:c r="F23" s="176"/>
-      <x:c r="G23" s="177"/>
-    </x:row>
-    <x:row r="24" spans="1:11">
+      <x:c r="F23" s="177"/>
+    </x:row>
+    <x:row r="24" spans="1:10">
       <x:c r="A24" s="175"/>
       <x:c r="B24" s="176"/>
       <x:c r="C24" s="176"/>
       <x:c r="D24" s="176"/>
       <x:c r="E24" s="176"/>
-      <x:c r="F24" s="176"/>
-      <x:c r="G24" s="177"/>
-    </x:row>
-    <x:row r="25" spans="1:11">
+      <x:c r="F24" s="177"/>
+    </x:row>
+    <x:row r="25" spans="1:10">
       <x:c r="A25" s="175"/>
       <x:c r="B25" s="176"/>
       <x:c r="C25" s="176"/>
       <x:c r="D25" s="176"/>
       <x:c r="E25" s="176"/>
-      <x:c r="F25" s="176"/>
-      <x:c r="G25" s="177"/>
-    </x:row>
-    <x:row r="26" spans="1:11">
+      <x:c r="F25" s="177"/>
+    </x:row>
+    <x:row r="26" spans="1:10">
       <x:c r="A26" s="175"/>
       <x:c r="B26" s="176"/>
       <x:c r="C26" s="176"/>
       <x:c r="D26" s="176"/>
       <x:c r="E26" s="176"/>
-      <x:c r="F26" s="176"/>
-      <x:c r="G26" s="177"/>
-    </x:row>
-    <x:row r="27" spans="1:11">
+      <x:c r="F26" s="177"/>
+    </x:row>
+    <x:row r="27" spans="1:10">
       <x:c r="A27" s="175"/>
       <x:c r="B27" s="176"/>
       <x:c r="C27" s="176"/>
       <x:c r="D27" s="176"/>
       <x:c r="E27" s="176"/>
-      <x:c r="F27" s="176"/>
-      <x:c r="G27" s="177"/>
-    </x:row>
-    <x:row r="28" spans="1:11">
+      <x:c r="F27" s="177"/>
+    </x:row>
+    <x:row r="28" spans="1:10">
       <x:c r="A28" s="175"/>
       <x:c r="B28" s="176"/>
       <x:c r="C28" s="176"/>
       <x:c r="D28" s="176"/>
       <x:c r="E28" s="176"/>
-      <x:c r="F28" s="176"/>
-      <x:c r="G28" s="177"/>
-    </x:row>
-    <x:row r="29" spans="1:11">
+      <x:c r="F28" s="177"/>
+    </x:row>
+    <x:row r="29" spans="1:10">
       <x:c r="A29" s="175"/>
       <x:c r="B29" s="176"/>
       <x:c r="C29" s="176"/>
       <x:c r="D29" s="176"/>
       <x:c r="E29" s="176"/>
-      <x:c r="F29" s="176"/>
-      <x:c r="G29" s="177"/>
-    </x:row>
-    <x:row r="30" spans="1:11">
+      <x:c r="F29" s="177"/>
+    </x:row>
+    <x:row r="30" spans="1:10">
       <x:c r="A30" s="175"/>
       <x:c r="B30" s="176"/>
       <x:c r="C30" s="176"/>
       <x:c r="D30" s="176"/>
       <x:c r="E30" s="176"/>
-      <x:c r="F30" s="176"/>
-      <x:c r="G30" s="177"/>
-    </x:row>
-    <x:row r="31" spans="1:11">
+      <x:c r="F30" s="177"/>
+    </x:row>
+    <x:row r="31" spans="1:10">
       <x:c r="A31" s="175"/>
       <x:c r="B31" s="176"/>
       <x:c r="C31" s="176"/>
       <x:c r="D31" s="176"/>
       <x:c r="E31" s="176"/>
-      <x:c r="F31" s="176"/>
-      <x:c r="G31" s="177"/>
-    </x:row>
-    <x:row r="32" spans="1:11">
+      <x:c r="F31" s="177"/>
+    </x:row>
+    <x:row r="32" spans="1:10">
       <x:c r="A32" s="175"/>
       <x:c r="B32" s="176"/>
       <x:c r="C32" s="176"/>
       <x:c r="D32" s="176"/>
       <x:c r="E32" s="176"/>
-      <x:c r="F32" s="176"/>
-      <x:c r="G32" s="177"/>
-    </x:row>
-    <x:row r="33" spans="1:11">
+      <x:c r="F32" s="177"/>
+    </x:row>
+    <x:row r="33" spans="1:10">
       <x:c r="A33" s="175"/>
       <x:c r="B33" s="176"/>
       <x:c r="C33" s="176"/>
       <x:c r="D33" s="176"/>
       <x:c r="E33" s="176"/>
-      <x:c r="F33" s="176"/>
-      <x:c r="G33" s="177"/>
-    </x:row>
-    <x:row r="34" spans="1:11">
+      <x:c r="F33" s="177"/>
+    </x:row>
+    <x:row r="34" spans="1:10">
       <x:c r="A34" s="175"/>
       <x:c r="B34" s="176"/>
       <x:c r="C34" s="176"/>
       <x:c r="D34" s="176"/>
       <x:c r="E34" s="176"/>
-      <x:c r="F34" s="176"/>
-      <x:c r="G34" s="177"/>
-    </x:row>
-    <x:row r="35" spans="1:11">
+      <x:c r="F34" s="177"/>
+    </x:row>
+    <x:row r="35" spans="1:10">
       <x:c r="A35" s="175"/>
       <x:c r="B35" s="176"/>
       <x:c r="C35" s="176"/>
       <x:c r="D35" s="176"/>
       <x:c r="E35" s="176"/>
-      <x:c r="F35" s="176"/>
-      <x:c r="G35" s="177"/>
-    </x:row>
-    <x:row r="36" spans="1:11">
+      <x:c r="F35" s="177"/>
+    </x:row>
+    <x:row r="36" spans="1:10">
       <x:c r="A36" s="175"/>
       <x:c r="B36" s="176"/>
       <x:c r="C36" s="176"/>
       <x:c r="D36" s="176"/>
       <x:c r="E36" s="176"/>
-      <x:c r="F36" s="176"/>
-      <x:c r="G36" s="177"/>
-    </x:row>
-    <x:row r="37" spans="1:11">
+      <x:c r="F36" s="177"/>
+    </x:row>
+    <x:row r="37" spans="1:10">
       <x:c r="A37" s="175"/>
       <x:c r="B37" s="176"/>
       <x:c r="C37" s="176"/>
       <x:c r="D37" s="176"/>
       <x:c r="E37" s="176"/>
-      <x:c r="F37" s="176"/>
-      <x:c r="G37" s="177"/>
-    </x:row>
-    <x:row r="38" spans="1:11">
+      <x:c r="F37" s="177"/>
+    </x:row>
+    <x:row r="38" spans="1:10">
       <x:c r="A38" s="175"/>
       <x:c r="B38" s="176"/>
       <x:c r="C38" s="176"/>
       <x:c r="D38" s="176"/>
       <x:c r="E38" s="176"/>
-      <x:c r="F38" s="176"/>
-      <x:c r="G38" s="177"/>
-    </x:row>
-    <x:row r="39" spans="1:11">
+      <x:c r="F38" s="177"/>
+    </x:row>
+    <x:row r="39" spans="1:10">
       <x:c r="A39" s="175"/>
       <x:c r="B39" s="176"/>
       <x:c r="C39" s="176"/>
       <x:c r="D39" s="176"/>
       <x:c r="E39" s="176"/>
-      <x:c r="F39" s="176"/>
-      <x:c r="G39" s="177"/>
-    </x:row>
-    <x:row r="40" spans="1:11">
+      <x:c r="F39" s="177"/>
+    </x:row>
+    <x:row r="40" spans="1:10">
       <x:c r="A40" s="175"/>
       <x:c r="B40" s="176"/>
       <x:c r="C40" s="176"/>
       <x:c r="D40" s="176"/>
       <x:c r="E40" s="176"/>
-      <x:c r="F40" s="176"/>
-      <x:c r="G40" s="177"/>
-    </x:row>
-    <x:row r="41" spans="1:11">
+      <x:c r="F40" s="177"/>
+    </x:row>
+    <x:row r="41" spans="1:10">
       <x:c r="A41" s="175"/>
       <x:c r="B41" s="176"/>
       <x:c r="C41" s="176"/>
       <x:c r="D41" s="176"/>
       <x:c r="E41" s="176"/>
-      <x:c r="F41" s="176"/>
-      <x:c r="G41" s="177"/>
-    </x:row>
-    <x:row r="42" spans="1:11">
+      <x:c r="F41" s="177"/>
+    </x:row>
+    <x:row r="42" spans="1:10">
       <x:c r="A42" s="175"/>
       <x:c r="B42" s="176"/>
       <x:c r="C42" s="176"/>
       <x:c r="D42" s="176"/>
       <x:c r="E42" s="176"/>
-      <x:c r="F42" s="176"/>
-      <x:c r="G42" s="177"/>
-    </x:row>
-    <x:row r="43" spans="1:11">
+      <x:c r="F42" s="177"/>
+    </x:row>
+    <x:row r="43" spans="1:10">
       <x:c r="A43" s="175"/>
       <x:c r="B43" s="176"/>
       <x:c r="C43" s="176"/>
       <x:c r="D43" s="176"/>
       <x:c r="E43" s="176"/>
-      <x:c r="F43" s="176"/>
-      <x:c r="G43" s="177"/>
-    </x:row>
-    <x:row r="44" spans="1:11">
+      <x:c r="F43" s="177"/>
+    </x:row>
+    <x:row r="44" spans="1:10">
       <x:c r="A44" s="175"/>
       <x:c r="B44" s="176"/>
       <x:c r="C44" s="176"/>
       <x:c r="D44" s="176"/>
       <x:c r="E44" s="176"/>
-      <x:c r="F44" s="176"/>
-      <x:c r="G44" s="177"/>
-    </x:row>
-    <x:row r="45" spans="1:11">
+      <x:c r="F44" s="177"/>
+    </x:row>
+    <x:row r="45" spans="1:10">
       <x:c r="A45" s="175"/>
       <x:c r="B45" s="176"/>
       <x:c r="C45" s="176"/>
       <x:c r="D45" s="176"/>
       <x:c r="E45" s="176"/>
-      <x:c r="F45" s="176"/>
-      <x:c r="G45" s="177"/>
-    </x:row>
-    <x:row r="46" spans="1:11">
+      <x:c r="F45" s="177"/>
+    </x:row>
+    <x:row r="46" spans="1:10">
       <x:c r="A46" s="175"/>
       <x:c r="B46" s="176"/>
       <x:c r="C46" s="176"/>
       <x:c r="D46" s="176"/>
       <x:c r="E46" s="176"/>
-      <x:c r="F46" s="176"/>
-      <x:c r="G46" s="177"/>
-    </x:row>
-    <x:row r="47" spans="1:11">
+      <x:c r="F46" s="177"/>
+    </x:row>
+    <x:row r="47" spans="1:10">
       <x:c r="A47" s="175"/>
       <x:c r="B47" s="176"/>
       <x:c r="C47" s="176"/>
       <x:c r="D47" s="176"/>
       <x:c r="E47" s="176"/>
-      <x:c r="F47" s="176"/>
-      <x:c r="G47" s="177"/>
-    </x:row>
-    <x:row r="48" spans="1:11">
+      <x:c r="F47" s="177"/>
+    </x:row>
+    <x:row r="48" spans="1:10">
       <x:c r="A48" s="175"/>
       <x:c r="B48" s="176"/>
       <x:c r="C48" s="176"/>
       <x:c r="D48" s="176"/>
       <x:c r="E48" s="176"/>
-      <x:c r="F48" s="176"/>
-      <x:c r="G48" s="177"/>
-    </x:row>
-    <x:row r="49" spans="1:11">
+      <x:c r="F48" s="177"/>
+    </x:row>
+    <x:row r="49" spans="1:10">
       <x:c r="A49" s="175"/>
       <x:c r="B49" s="176"/>
       <x:c r="C49" s="176"/>
       <x:c r="D49" s="176"/>
       <x:c r="E49" s="176"/>
-      <x:c r="F49" s="176"/>
-      <x:c r="G49" s="177"/>
-    </x:row>
-    <x:row r="50" spans="1:11">
+      <x:c r="F49" s="177"/>
+    </x:row>
+    <x:row r="50" spans="1:10">
       <x:c r="A50" s="175"/>
       <x:c r="B50" s="176"/>
       <x:c r="C50" s="176"/>
       <x:c r="D50" s="176"/>
       <x:c r="E50" s="176"/>
-      <x:c r="F50" s="176"/>
-      <x:c r="G50" s="177"/>
-    </x:row>
-    <x:row r="51" spans="1:11">
+      <x:c r="F50" s="177"/>
+    </x:row>
+    <x:row r="51" spans="1:10">
       <x:c r="A51" s="175"/>
       <x:c r="B51" s="176"/>
       <x:c r="C51" s="176"/>
       <x:c r="D51" s="176"/>
       <x:c r="E51" s="176"/>
-      <x:c r="F51" s="176"/>
-      <x:c r="G51" s="177"/>
-    </x:row>
-    <x:row r="52" spans="1:11">
+      <x:c r="F51" s="177"/>
+    </x:row>
+    <x:row r="52" spans="1:10">
       <x:c r="A52" s="175"/>
       <x:c r="B52" s="176"/>
       <x:c r="C52" s="176"/>
       <x:c r="D52" s="176"/>
       <x:c r="E52" s="176"/>
-      <x:c r="F52" s="176"/>
-      <x:c r="G52" s="177"/>
-    </x:row>
-    <x:row r="53" spans="1:11">
+      <x:c r="F52" s="177"/>
+    </x:row>
+    <x:row r="53" spans="1:10">
       <x:c r="A53" s="175"/>
       <x:c r="B53" s="176"/>
       <x:c r="C53" s="176"/>
       <x:c r="D53" s="176"/>
       <x:c r="E53" s="176"/>
-      <x:c r="F53" s="176"/>
-      <x:c r="G53" s="177"/>
-    </x:row>
-    <x:row r="54" spans="1:11">
+      <x:c r="F53" s="177"/>
+    </x:row>
+    <x:row r="54" spans="1:10">
       <x:c r="A54" s="175"/>
       <x:c r="B54" s="176"/>
       <x:c r="C54" s="176"/>
       <x:c r="D54" s="176"/>
       <x:c r="E54" s="176"/>
-      <x:c r="F54" s="176"/>
-      <x:c r="G54" s="177"/>
-    </x:row>
-    <x:row r="55" spans="1:11">
+      <x:c r="F54" s="177"/>
+    </x:row>
+    <x:row r="55" spans="1:10">
       <x:c r="A55" s="175"/>
       <x:c r="B55" s="176"/>
       <x:c r="C55" s="176"/>
       <x:c r="D55" s="176"/>
       <x:c r="E55" s="176"/>
-      <x:c r="F55" s="176"/>
-      <x:c r="G55" s="177"/>
-    </x:row>
-    <x:row r="56" spans="1:11">
+      <x:c r="F55" s="177"/>
+    </x:row>
+    <x:row r="56" spans="1:10">
       <x:c r="A56" s="175"/>
       <x:c r="B56" s="176"/>
       <x:c r="C56" s="176"/>
       <x:c r="D56" s="176"/>
       <x:c r="E56" s="176"/>
-      <x:c r="F56" s="176"/>
-      <x:c r="G56" s="177"/>
-    </x:row>
-    <x:row r="57" spans="1:11">
+      <x:c r="F56" s="177"/>
+    </x:row>
+    <x:row r="57" spans="1:10">
       <x:c r="A57" s="175"/>
       <x:c r="B57" s="176"/>
       <x:c r="C57" s="176"/>
       <x:c r="D57" s="176"/>
       <x:c r="E57" s="176"/>
-      <x:c r="F57" s="176"/>
-      <x:c r="G57" s="177"/>
-    </x:row>
-    <x:row r="58" spans="1:11">
+      <x:c r="F57" s="177"/>
+    </x:row>
+    <x:row r="58" spans="1:10">
       <x:c r="A58" s="175"/>
       <x:c r="B58" s="176"/>
       <x:c r="C58" s="176"/>
       <x:c r="D58" s="176"/>
       <x:c r="E58" s="176"/>
-      <x:c r="F58" s="176"/>
-      <x:c r="G58" s="177"/>
-    </x:row>
-    <x:row r="59" spans="1:11">
+      <x:c r="F58" s="177"/>
+    </x:row>
+    <x:row r="59" spans="1:10">
       <x:c r="A59" s="175"/>
       <x:c r="B59" s="176"/>
       <x:c r="C59" s="176"/>
       <x:c r="D59" s="176"/>
       <x:c r="E59" s="176"/>
-      <x:c r="F59" s="176"/>
-      <x:c r="G59" s="177"/>
-    </x:row>
-    <x:row r="60" spans="1:11">
+      <x:c r="F59" s="177"/>
+    </x:row>
+    <x:row r="60" spans="1:10">
       <x:c r="A60" s="175"/>
       <x:c r="B60" s="176"/>
       <x:c r="C60" s="176"/>
       <x:c r="D60" s="176"/>
       <x:c r="E60" s="176"/>
-      <x:c r="F60" s="176"/>
-      <x:c r="G60" s="177"/>
-    </x:row>
-    <x:row r="61" spans="1:11">
+      <x:c r="F60" s="177"/>
+    </x:row>
+    <x:row r="61" spans="1:10">
       <x:c r="A61" s="175"/>
       <x:c r="B61" s="176"/>
       <x:c r="C61" s="176"/>
       <x:c r="D61" s="176"/>
       <x:c r="E61" s="176"/>
-      <x:c r="F61" s="176"/>
-      <x:c r="G61" s="177"/>
-    </x:row>
-    <x:row r="62" spans="1:11">
+      <x:c r="F61" s="177"/>
+    </x:row>
+    <x:row r="62" spans="1:10">
       <x:c r="A62" s="175"/>
       <x:c r="B62" s="176"/>
       <x:c r="C62" s="176"/>
       <x:c r="D62" s="176"/>
       <x:c r="E62" s="176"/>
-      <x:c r="F62" s="176"/>
-      <x:c r="G62" s="177"/>
-    </x:row>
-    <x:row r="63" spans="1:11">
+      <x:c r="F62" s="177"/>
+    </x:row>
+    <x:row r="63" spans="1:10">
       <x:c r="A63" s="175"/>
       <x:c r="B63" s="176"/>
       <x:c r="C63" s="176"/>
       <x:c r="D63" s="176"/>
       <x:c r="E63" s="176"/>
-      <x:c r="F63" s="176"/>
-      <x:c r="G63" s="177"/>
-    </x:row>
-    <x:row r="64" spans="1:11">
+      <x:c r="F63" s="177"/>
+    </x:row>
+    <x:row r="64" spans="1:10">
       <x:c r="A64" s="175"/>
       <x:c r="B64" s="176"/>
       <x:c r="C64" s="176"/>
       <x:c r="D64" s="176"/>
       <x:c r="E64" s="176"/>
-      <x:c r="F64" s="176"/>
-      <x:c r="G64" s="177"/>
-    </x:row>
-    <x:row r="65" spans="1:11">
+      <x:c r="F64" s="177"/>
+    </x:row>
+    <x:row r="65" spans="1:10">
       <x:c r="A65" s="175"/>
       <x:c r="B65" s="176"/>
       <x:c r="C65" s="176"/>
       <x:c r="D65" s="176"/>
       <x:c r="E65" s="176"/>
-      <x:c r="F65" s="176"/>
-      <x:c r="G65" s="177"/>
-    </x:row>
-    <x:row r="66" spans="1:11">
+      <x:c r="F65" s="177"/>
+    </x:row>
+    <x:row r="66" spans="1:10">
       <x:c r="A66" s="175"/>
       <x:c r="B66" s="176"/>
       <x:c r="C66" s="176"/>
       <x:c r="D66" s="176"/>
       <x:c r="E66" s="176"/>
-      <x:c r="F66" s="176"/>
-      <x:c r="G66" s="177"/>
-    </x:row>
-    <x:row r="67" spans="1:11">
+      <x:c r="F66" s="177"/>
+    </x:row>
+    <x:row r="67" spans="1:10">
       <x:c r="A67" s="175"/>
       <x:c r="B67" s="176"/>
       <x:c r="C67" s="176"/>
       <x:c r="D67" s="176"/>
       <x:c r="E67" s="176"/>
-      <x:c r="F67" s="176"/>
-      <x:c r="G67" s="177"/>
-    </x:row>
-    <x:row r="68" spans="1:11">
+      <x:c r="F67" s="177"/>
+    </x:row>
+    <x:row r="68" spans="1:10">
       <x:c r="A68" s="175"/>
       <x:c r="B68" s="176"/>
       <x:c r="C68" s="176"/>
       <x:c r="D68" s="176"/>
       <x:c r="E68" s="176"/>
-      <x:c r="F68" s="176"/>
-      <x:c r="G68" s="177"/>
-    </x:row>
-    <x:row r="69" spans="1:11">
+      <x:c r="F68" s="177"/>
+    </x:row>
+    <x:row r="69" spans="1:10">
       <x:c r="A69" s="175"/>
       <x:c r="B69" s="176"/>
       <x:c r="C69" s="176"/>
       <x:c r="D69" s="176"/>
       <x:c r="E69" s="176"/>
-      <x:c r="F69" s="176"/>
-      <x:c r="G69" s="177"/>
-    </x:row>
-    <x:row r="70" spans="1:11">
+      <x:c r="F69" s="177"/>
+    </x:row>
+    <x:row r="70" spans="1:10">
       <x:c r="A70" s="175"/>
       <x:c r="B70" s="176"/>
       <x:c r="C70" s="176"/>
       <x:c r="D70" s="176"/>
       <x:c r="E70" s="176"/>
-      <x:c r="F70" s="176"/>
-      <x:c r="G70" s="177"/>
-    </x:row>
-    <x:row r="71" spans="1:11">
+      <x:c r="F70" s="177"/>
+    </x:row>
+    <x:row r="71" spans="1:10">
       <x:c r="A71" s="175"/>
       <x:c r="B71" s="176"/>
       <x:c r="C71" s="176"/>
       <x:c r="D71" s="176"/>
       <x:c r="E71" s="176"/>
-      <x:c r="F71" s="176"/>
-      <x:c r="G71" s="177"/>
-    </x:row>
-    <x:row r="72" spans="1:11">
+      <x:c r="F71" s="177"/>
+    </x:row>
+    <x:row r="72" spans="1:10">
       <x:c r="A72" s="175"/>
       <x:c r="B72" s="176"/>
       <x:c r="C72" s="176"/>
       <x:c r="D72" s="176"/>
       <x:c r="E72" s="176"/>
-      <x:c r="F72" s="176"/>
-      <x:c r="G72" s="177"/>
-    </x:row>
-    <x:row r="73" spans="1:11">
+      <x:c r="F72" s="177"/>
+    </x:row>
+    <x:row r="73" spans="1:10">
       <x:c r="A73" s="175"/>
       <x:c r="B73" s="176"/>
       <x:c r="C73" s="176"/>
       <x:c r="D73" s="176"/>
       <x:c r="E73" s="176"/>
-      <x:c r="F73" s="176"/>
-      <x:c r="G73" s="177"/>
-    </x:row>
-    <x:row r="74" spans="1:11">
+      <x:c r="F73" s="177"/>
+    </x:row>
+    <x:row r="74" spans="1:10">
       <x:c r="A74" s="175"/>
       <x:c r="B74" s="176"/>
       <x:c r="C74" s="176"/>
       <x:c r="D74" s="176"/>
       <x:c r="E74" s="176"/>
-      <x:c r="F74" s="176"/>
-      <x:c r="G74" s="177"/>
-    </x:row>
-    <x:row r="75" spans="1:11">
+      <x:c r="F74" s="177"/>
+    </x:row>
+    <x:row r="75" spans="1:10">
       <x:c r="A75" s="175"/>
       <x:c r="B75" s="176"/>
       <x:c r="C75" s="176"/>
       <x:c r="D75" s="176"/>
       <x:c r="E75" s="176"/>
-      <x:c r="F75" s="176"/>
-      <x:c r="G75" s="177"/>
-    </x:row>
-    <x:row r="76" spans="1:11">
+      <x:c r="F75" s="177"/>
+    </x:row>
+    <x:row r="76" spans="1:10">
       <x:c r="A76" s="175"/>
       <x:c r="B76" s="176"/>
       <x:c r="C76" s="176"/>
       <x:c r="D76" s="176"/>
       <x:c r="E76" s="176"/>
-      <x:c r="F76" s="176"/>
-      <x:c r="G76" s="177"/>
-    </x:row>
-    <x:row r="77" spans="1:11">
+      <x:c r="F76" s="177"/>
+    </x:row>
+    <x:row r="77" spans="1:10">
       <x:c r="A77" s="175"/>
       <x:c r="B77" s="176"/>
       <x:c r="C77" s="176"/>
       <x:c r="D77" s="176"/>
       <x:c r="E77" s="176"/>
-      <x:c r="F77" s="176"/>
-      <x:c r="G77" s="177"/>
-    </x:row>
-    <x:row r="78" spans="1:11">
+      <x:c r="F77" s="177"/>
+    </x:row>
+    <x:row r="78" spans="1:10">
       <x:c r="A78" s="175"/>
       <x:c r="B78" s="176"/>
       <x:c r="C78" s="176"/>
       <x:c r="D78" s="176"/>
       <x:c r="E78" s="176"/>
-      <x:c r="F78" s="176"/>
-      <x:c r="G78" s="177"/>
-    </x:row>
-    <x:row r="79" spans="1:11">
+      <x:c r="F78" s="177"/>
+    </x:row>
+    <x:row r="79" spans="1:10">
       <x:c r="A79" s="175"/>
       <x:c r="B79" s="176"/>
       <x:c r="C79" s="176"/>
       <x:c r="D79" s="176"/>
       <x:c r="E79" s="176"/>
-      <x:c r="F79" s="176"/>
-      <x:c r="G79" s="177"/>
-    </x:row>
-    <x:row r="80" spans="1:11">
+      <x:c r="F79" s="177"/>
+    </x:row>
+    <x:row r="80" spans="1:10">
       <x:c r="A80" s="175"/>
       <x:c r="B80" s="176"/>
       <x:c r="C80" s="176"/>
       <x:c r="D80" s="176"/>
       <x:c r="E80" s="176"/>
-      <x:c r="F80" s="176"/>
-      <x:c r="G80" s="177"/>
-    </x:row>
-    <x:row r="81" spans="1:11">
+      <x:c r="F80" s="177"/>
+    </x:row>
+    <x:row r="81" spans="1:10">
       <x:c r="A81" s="175"/>
       <x:c r="B81" s="176"/>
       <x:c r="C81" s="176"/>
       <x:c r="D81" s="176"/>
       <x:c r="E81" s="176"/>
-      <x:c r="F81" s="176"/>
-      <x:c r="G81" s="177"/>
-    </x:row>
-    <x:row r="82" spans="1:11">
+      <x:c r="F81" s="177"/>
+    </x:row>
+    <x:row r="82" spans="1:10">
       <x:c r="A82" s="175"/>
       <x:c r="B82" s="176"/>
       <x:c r="C82" s="176"/>
       <x:c r="D82" s="176"/>
       <x:c r="E82" s="176"/>
-      <x:c r="F82" s="176"/>
-      <x:c r="G82" s="177"/>
-    </x:row>
-    <x:row r="83" spans="1:11">
+      <x:c r="F82" s="177"/>
+    </x:row>
+    <x:row r="83" spans="1:10">
       <x:c r="A83" s="175"/>
       <x:c r="B83" s="176"/>
       <x:c r="C83" s="176"/>
       <x:c r="D83" s="176"/>
       <x:c r="E83" s="176"/>
-      <x:c r="F83" s="176"/>
-      <x:c r="G83" s="177"/>
-    </x:row>
-    <x:row r="84" spans="1:11">
+      <x:c r="F83" s="177"/>
+    </x:row>
+    <x:row r="84" spans="1:10">
       <x:c r="A84" s="175"/>
       <x:c r="B84" s="176"/>
       <x:c r="C84" s="176"/>
       <x:c r="D84" s="176"/>
       <x:c r="E84" s="176"/>
-      <x:c r="F84" s="176"/>
-      <x:c r="G84" s="177"/>
-    </x:row>
-    <x:row r="85" spans="1:11">
+      <x:c r="F84" s="177"/>
+    </x:row>
+    <x:row r="85" spans="1:10">
       <x:c r="A85" s="175"/>
       <x:c r="B85" s="176"/>
       <x:c r="C85" s="176"/>
       <x:c r="D85" s="176"/>
       <x:c r="E85" s="176"/>
-      <x:c r="F85" s="176"/>
-      <x:c r="G85" s="177"/>
-    </x:row>
-    <x:row r="86" spans="1:11">
+      <x:c r="F85" s="177"/>
+    </x:row>
+    <x:row r="86" spans="1:10">
       <x:c r="A86" s="175"/>
       <x:c r="B86" s="176"/>
       <x:c r="C86" s="176"/>
       <x:c r="D86" s="176"/>
       <x:c r="E86" s="176"/>
-      <x:c r="F86" s="176"/>
-      <x:c r="G86" s="177"/>
-    </x:row>
-    <x:row r="87" spans="1:11">
+      <x:c r="F86" s="177"/>
+    </x:row>
+    <x:row r="87" spans="1:10">
       <x:c r="A87" s="175"/>
       <x:c r="B87" s="176"/>
       <x:c r="C87" s="176"/>
       <x:c r="D87" s="176"/>
       <x:c r="E87" s="176"/>
-      <x:c r="F87" s="176"/>
-      <x:c r="G87" s="177"/>
-    </x:row>
-    <x:row r="88" spans="1:11">
+      <x:c r="F87" s="177"/>
+    </x:row>
+    <x:row r="88" spans="1:10">
       <x:c r="A88" s="175"/>
       <x:c r="B88" s="176"/>
       <x:c r="C88" s="176"/>
       <x:c r="D88" s="176"/>
       <x:c r="E88" s="176"/>
-      <x:c r="F88" s="176"/>
-      <x:c r="G88" s="177"/>
-    </x:row>
-    <x:row r="89" spans="1:11">
+      <x:c r="F88" s="177"/>
+    </x:row>
+    <x:row r="89" spans="1:10">
       <x:c r="A89" s="175"/>
       <x:c r="B89" s="176"/>
       <x:c r="C89" s="176"/>
       <x:c r="D89" s="176"/>
       <x:c r="E89" s="176"/>
-      <x:c r="F89" s="176"/>
-      <x:c r="G89" s="177"/>
-    </x:row>
-    <x:row r="90" spans="1:11">
+      <x:c r="F89" s="177"/>
+    </x:row>
+    <x:row r="90" spans="1:10">
       <x:c r="A90" s="175"/>
       <x:c r="B90" s="176"/>
       <x:c r="C90" s="176"/>
       <x:c r="D90" s="176"/>
       <x:c r="E90" s="176"/>
-      <x:c r="F90" s="176"/>
-      <x:c r="G90" s="177"/>
-    </x:row>
-    <x:row r="91" spans="1:11">
+      <x:c r="F90" s="177"/>
+    </x:row>
+    <x:row r="91" spans="1:10">
       <x:c r="A91" s="175"/>
       <x:c r="B91" s="176"/>
       <x:c r="C91" s="176"/>
       <x:c r="D91" s="176"/>
       <x:c r="E91" s="176"/>
-      <x:c r="F91" s="176"/>
-      <x:c r="G91" s="177"/>
-    </x:row>
-    <x:row r="92" spans="1:11">
+      <x:c r="F91" s="177"/>
+    </x:row>
+    <x:row r="92" spans="1:10">
       <x:c r="A92" s="175"/>
       <x:c r="B92" s="176"/>
       <x:c r="C92" s="176"/>
       <x:c r="D92" s="176"/>
       <x:c r="E92" s="176"/>
-      <x:c r="F92" s="176"/>
-      <x:c r="G92" s="177"/>
-    </x:row>
-    <x:row r="93" spans="1:11">
+      <x:c r="F92" s="177"/>
+    </x:row>
+    <x:row r="93" spans="1:10">
       <x:c r="A93" s="175"/>
       <x:c r="B93" s="176"/>
       <x:c r="C93" s="176"/>
       <x:c r="D93" s="176"/>
       <x:c r="E93" s="176"/>
-      <x:c r="F93" s="176"/>
-      <x:c r="G93" s="177"/>
-    </x:row>
-    <x:row r="94" spans="1:11">
+      <x:c r="F93" s="177"/>
+    </x:row>
+    <x:row r="94" spans="1:10">
       <x:c r="A94" s="175"/>
       <x:c r="B94" s="176"/>
       <x:c r="C94" s="176"/>
       <x:c r="D94" s="176"/>
       <x:c r="E94" s="176"/>
-      <x:c r="F94" s="176"/>
-      <x:c r="G94" s="177"/>
-    </x:row>
-    <x:row r="95" spans="1:11">
+      <x:c r="F94" s="177"/>
+    </x:row>
+    <x:row r="95" spans="1:10">
       <x:c r="A95" s="175"/>
       <x:c r="B95" s="176"/>
       <x:c r="C95" s="176"/>
       <x:c r="D95" s="176"/>
       <x:c r="E95" s="176"/>
-      <x:c r="F95" s="176"/>
-      <x:c r="G95" s="177"/>
-    </x:row>
-    <x:row r="96" spans="1:11">
+      <x:c r="F95" s="177"/>
+    </x:row>
+    <x:row r="96" spans="1:10">
       <x:c r="A96" s="175"/>
       <x:c r="B96" s="176"/>
       <x:c r="C96" s="176"/>
       <x:c r="D96" s="176"/>
       <x:c r="E96" s="176"/>
-      <x:c r="F96" s="176"/>
-      <x:c r="G96" s="177"/>
-    </x:row>
-    <x:row r="97" spans="1:11">
+      <x:c r="F96" s="177"/>
+    </x:row>
+    <x:row r="97" spans="1:10">
       <x:c r="A97" s="175"/>
       <x:c r="B97" s="176"/>
       <x:c r="C97" s="176"/>
       <x:c r="D97" s="176"/>
       <x:c r="E97" s="176"/>
-      <x:c r="F97" s="176"/>
-      <x:c r="G97" s="177"/>
-    </x:row>
-    <x:row r="98" spans="1:11">
+      <x:c r="F97" s="177"/>
+    </x:row>
+    <x:row r="98" spans="1:10">
       <x:c r="A98" s="175"/>
       <x:c r="B98" s="176"/>
       <x:c r="C98" s="176"/>
       <x:c r="D98" s="176"/>
       <x:c r="E98" s="176"/>
-      <x:c r="F98" s="176"/>
-      <x:c r="G98" s="177"/>
-    </x:row>
-    <x:row r="99" spans="1:11">
+      <x:c r="F98" s="177"/>
+    </x:row>
+    <x:row r="99" spans="1:10">
       <x:c r="A99" s="175"/>
       <x:c r="B99" s="176"/>
       <x:c r="C99" s="176"/>
       <x:c r="D99" s="176"/>
       <x:c r="E99" s="176"/>
-      <x:c r="F99" s="176"/>
-      <x:c r="G99" s="177"/>
-    </x:row>
-    <x:row r="100" spans="1:11">
+      <x:c r="F99" s="177"/>
+    </x:row>
+    <x:row r="100" spans="1:10">
       <x:c r="A100" s="175"/>
       <x:c r="B100" s="176"/>
       <x:c r="C100" s="176"/>
       <x:c r="D100" s="176"/>
       <x:c r="E100" s="176"/>
-      <x:c r="F100" s="176"/>
-      <x:c r="G100" s="177"/>
-    </x:row>
-    <x:row r="101" spans="1:11">
+      <x:c r="F100" s="177"/>
+    </x:row>
+    <x:row r="101" spans="1:10">
       <x:c r="A101" s="175"/>
       <x:c r="B101" s="176"/>
       <x:c r="C101" s="176"/>
       <x:c r="D101" s="176"/>
       <x:c r="E101" s="176"/>
-      <x:c r="F101" s="176"/>
-      <x:c r="G101" s="177"/>
-    </x:row>
-    <x:row r="102" spans="1:11">
+      <x:c r="F101" s="177"/>
+    </x:row>
+    <x:row r="102" spans="1:10">
       <x:c r="A102" s="175"/>
       <x:c r="B102" s="176"/>
       <x:c r="C102" s="176"/>
       <x:c r="D102" s="176"/>
       <x:c r="E102" s="176"/>
-      <x:c r="F102" s="176"/>
-      <x:c r="G102" s="177"/>
-    </x:row>
-    <x:row r="103" spans="1:11">
+      <x:c r="F102" s="177"/>
+    </x:row>
+    <x:row r="103" spans="1:10">
       <x:c r="A103" s="175"/>
       <x:c r="B103" s="176"/>
       <x:c r="C103" s="176"/>
       <x:c r="D103" s="176"/>
       <x:c r="E103" s="176"/>
-      <x:c r="F103" s="176"/>
-      <x:c r="G103" s="177"/>
-    </x:row>
-    <x:row r="104" spans="1:11">
+      <x:c r="F103" s="177"/>
+    </x:row>
+    <x:row r="104" spans="1:10">
       <x:c r="A104" s="175"/>
       <x:c r="B104" s="176"/>
       <x:c r="C104" s="176"/>
       <x:c r="D104" s="176"/>
       <x:c r="E104" s="176"/>
-      <x:c r="F104" s="176"/>
-      <x:c r="G104" s="177"/>
-    </x:row>
-    <x:row r="105" spans="1:11">
+      <x:c r="F104" s="177"/>
+    </x:row>
+    <x:row r="105" spans="1:10">
       <x:c r="A105" s="175"/>
       <x:c r="B105" s="176"/>
       <x:c r="C105" s="176"/>
       <x:c r="D105" s="176"/>
       <x:c r="E105" s="176"/>
-      <x:c r="F105" s="176"/>
-      <x:c r="G105" s="177"/>
-    </x:row>
-    <x:row r="106" spans="1:11">
+      <x:c r="F105" s="177"/>
+    </x:row>
+    <x:row r="106" spans="1:10">
       <x:c r="A106" s="175"/>
       <x:c r="B106" s="176"/>
       <x:c r="C106" s="176"/>
       <x:c r="D106" s="176"/>
       <x:c r="E106" s="176"/>
-      <x:c r="F106" s="176"/>
-      <x:c r="G106" s="177"/>
-    </x:row>
-    <x:row r="107" spans="1:11">
+      <x:c r="F106" s="177"/>
+    </x:row>
+    <x:row r="107" spans="1:10">
       <x:c r="A107" s="175"/>
       <x:c r="B107" s="176"/>
       <x:c r="C107" s="176"/>
       <x:c r="D107" s="176"/>
       <x:c r="E107" s="176"/>
-      <x:c r="F107" s="176"/>
-      <x:c r="G107" s="177"/>
-    </x:row>
-    <x:row r="108" spans="1:11">
+      <x:c r="F107" s="177"/>
+    </x:row>
+    <x:row r="108" spans="1:10">
       <x:c r="A108" s="175"/>
       <x:c r="B108" s="176"/>
       <x:c r="C108" s="176"/>
       <x:c r="D108" s="176"/>
       <x:c r="E108" s="176"/>
-      <x:c r="F108" s="176"/>
-      <x:c r="G108" s="177"/>
-    </x:row>
-    <x:row r="109" spans="1:11">
+      <x:c r="F108" s="177"/>
+    </x:row>
+    <x:row r="109" spans="1:10">
       <x:c r="A109" s="175"/>
       <x:c r="B109" s="176"/>
       <x:c r="C109" s="176"/>
       <x:c r="D109" s="176"/>
       <x:c r="E109" s="176"/>
-      <x:c r="F109" s="176"/>
-      <x:c r="G109" s="177"/>
-    </x:row>
-    <x:row r="110" spans="1:11">
+      <x:c r="F109" s="177"/>
+    </x:row>
+    <x:row r="110" spans="1:10">
       <x:c r="A110" s="175"/>
       <x:c r="B110" s="176"/>
       <x:c r="C110" s="176"/>
       <x:c r="D110" s="176"/>
       <x:c r="E110" s="176"/>
-      <x:c r="F110" s="176"/>
-      <x:c r="G110" s="177"/>
-    </x:row>
-    <x:row r="111" spans="1:11">
+      <x:c r="F110" s="177"/>
+    </x:row>
+    <x:row r="111" spans="1:10">
       <x:c r="A111" s="175"/>
       <x:c r="B111" s="176"/>
       <x:c r="C111" s="176"/>
       <x:c r="D111" s="176"/>
       <x:c r="E111" s="176"/>
-      <x:c r="F111" s="176"/>
-      <x:c r="G111" s="177"/>
-    </x:row>
-    <x:row r="112" spans="1:11">
+      <x:c r="F111" s="177"/>
+    </x:row>
+    <x:row r="112" spans="1:10">
       <x:c r="A112" s="175"/>
       <x:c r="B112" s="176"/>
       <x:c r="C112" s="176"/>
       <x:c r="D112" s="176"/>
       <x:c r="E112" s="176"/>
-      <x:c r="F112" s="176"/>
-      <x:c r="G112" s="177"/>
-    </x:row>
-    <x:row r="113" spans="1:11">
+      <x:c r="F112" s="177"/>
+    </x:row>
+    <x:row r="113" spans="1:10">
       <x:c r="A113" s="175"/>
       <x:c r="B113" s="176"/>
       <x:c r="C113" s="176"/>
       <x:c r="D113" s="176"/>
       <x:c r="E113" s="176"/>
-      <x:c r="F113" s="176"/>
-      <x:c r="G113" s="177"/>
-    </x:row>
-    <x:row r="114" spans="1:11">
+      <x:c r="F113" s="177"/>
+    </x:row>
+    <x:row r="114" spans="1:10">
       <x:c r="A114" s="175"/>
       <x:c r="B114" s="176"/>
       <x:c r="C114" s="176"/>
       <x:c r="D114" s="176"/>
       <x:c r="E114" s="176"/>
-      <x:c r="F114" s="176"/>
-      <x:c r="G114" s="177"/>
-    </x:row>
-    <x:row r="115" spans="1:11">
+      <x:c r="F114" s="177"/>
+    </x:row>
+    <x:row r="115" spans="1:10">
       <x:c r="A115" s="175"/>
       <x:c r="B115" s="176"/>
       <x:c r="C115" s="176"/>
       <x:c r="D115" s="176"/>
       <x:c r="E115" s="176"/>
-      <x:c r="F115" s="176"/>
-      <x:c r="G115" s="177"/>
-    </x:row>
-    <x:row r="116" spans="1:11">
+      <x:c r="F115" s="177"/>
+    </x:row>
+    <x:row r="116" spans="1:10">
       <x:c r="A116" s="175"/>
       <x:c r="B116" s="176"/>
       <x:c r="C116" s="176"/>
       <x:c r="D116" s="176"/>
       <x:c r="E116" s="176"/>
-      <x:c r="F116" s="176"/>
-      <x:c r="G116" s="177"/>
-    </x:row>
-    <x:row r="117" spans="1:11">
+      <x:c r="F116" s="177"/>
+    </x:row>
+    <x:row r="117" spans="1:10">
       <x:c r="A117" s="175"/>
       <x:c r="B117" s="176"/>
       <x:c r="C117" s="176"/>
       <x:c r="D117" s="176"/>
       <x:c r="E117" s="176"/>
-      <x:c r="F117" s="176"/>
-      <x:c r="G117" s="177"/>
-    </x:row>
-    <x:row r="118" spans="1:11">
+      <x:c r="F117" s="177"/>
+    </x:row>
+    <x:row r="118" spans="1:10">
       <x:c r="A118" s="175"/>
       <x:c r="B118" s="176"/>
       <x:c r="C118" s="176"/>
       <x:c r="D118" s="176"/>
       <x:c r="E118" s="176"/>
-      <x:c r="F118" s="176"/>
-      <x:c r="G118" s="177"/>
-    </x:row>
-    <x:row r="119" spans="1:11">
+      <x:c r="F118" s="177"/>
+    </x:row>
+    <x:row r="119" spans="1:10">
       <x:c r="A119" s="175"/>
       <x:c r="B119" s="176"/>
       <x:c r="C119" s="176"/>
       <x:c r="D119" s="176"/>
       <x:c r="E119" s="176"/>
-      <x:c r="F119" s="176"/>
-      <x:c r="G119" s="177"/>
-    </x:row>
-    <x:row r="120" spans="1:11">
+      <x:c r="F119" s="177"/>
+    </x:row>
+    <x:row r="120" spans="1:10">
       <x:c r="A120" s="175"/>
       <x:c r="B120" s="176"/>
       <x:c r="C120" s="176"/>
       <x:c r="D120" s="176"/>
       <x:c r="E120" s="176"/>
-      <x:c r="F120" s="176"/>
-      <x:c r="G120" s="177"/>
-    </x:row>
-    <x:row r="121" spans="1:11">
+      <x:c r="F120" s="177"/>
+    </x:row>
+    <x:row r="121" spans="1:10">
       <x:c r="A121" s="175"/>
       <x:c r="B121" s="176"/>
       <x:c r="C121" s="176"/>
       <x:c r="D121" s="176"/>
       <x:c r="E121" s="176"/>
-      <x:c r="F121" s="176"/>
-      <x:c r="G121" s="177"/>
-    </x:row>
-    <x:row r="122" spans="1:11">
+      <x:c r="F121" s="177"/>
+    </x:row>
+    <x:row r="122" spans="1:10">
       <x:c r="A122" s="175"/>
       <x:c r="B122" s="176"/>
       <x:c r="C122" s="176"/>
       <x:c r="D122" s="176"/>
       <x:c r="E122" s="176"/>
-      <x:c r="F122" s="176"/>
-      <x:c r="G122" s="177"/>
-    </x:row>
-    <x:row r="123" spans="1:11">
+      <x:c r="F122" s="177"/>
+    </x:row>
+    <x:row r="123" spans="1:10">
       <x:c r="A123" s="175"/>
       <x:c r="B123" s="176"/>
       <x:c r="C123" s="176"/>
       <x:c r="D123" s="176"/>
       <x:c r="E123" s="176"/>
-      <x:c r="F123" s="176"/>
-      <x:c r="G123" s="177"/>
-    </x:row>
-    <x:row r="124" spans="1:11">
+      <x:c r="F123" s="177"/>
+    </x:row>
+    <x:row r="124" spans="1:10">
       <x:c r="A124" s="175"/>
       <x:c r="B124" s="176"/>
       <x:c r="C124" s="176"/>
       <x:c r="D124" s="176"/>
       <x:c r="E124" s="176"/>
-      <x:c r="F124" s="176"/>
-      <x:c r="G124" s="177"/>
-    </x:row>
-    <x:row r="125" spans="1:11">
+      <x:c r="F124" s="177"/>
+    </x:row>
+    <x:row r="125" spans="1:10">
       <x:c r="A125" s="175"/>
       <x:c r="B125" s="176"/>
       <x:c r="C125" s="176"/>
       <x:c r="D125" s="176"/>
       <x:c r="E125" s="176"/>
-      <x:c r="F125" s="176"/>
-      <x:c r="G125" s="177"/>
-    </x:row>
-    <x:row r="126" spans="1:11">
+      <x:c r="F125" s="177"/>
+    </x:row>
+    <x:row r="126" spans="1:10">
       <x:c r="A126" s="175"/>
       <x:c r="B126" s="176"/>
       <x:c r="C126" s="176"/>
       <x:c r="D126" s="176"/>
       <x:c r="E126" s="176"/>
-      <x:c r="F126" s="176"/>
-      <x:c r="G126" s="177"/>
-    </x:row>
-    <x:row r="127" spans="1:11">
+      <x:c r="F126" s="177"/>
+    </x:row>
+    <x:row r="127" spans="1:10">
       <x:c r="A127" s="175"/>
       <x:c r="B127" s="176"/>
       <x:c r="C127" s="176"/>
       <x:c r="D127" s="176"/>
       <x:c r="E127" s="176"/>
-      <x:c r="F127" s="176"/>
-      <x:c r="G127" s="177"/>
-    </x:row>
-    <x:row r="128" spans="1:11">
+      <x:c r="F127" s="177"/>
+    </x:row>
+    <x:row r="128" spans="1:10">
       <x:c r="A128" s="175"/>
       <x:c r="B128" s="176"/>
       <x:c r="C128" s="176"/>
       <x:c r="D128" s="176"/>
       <x:c r="E128" s="176"/>
-      <x:c r="F128" s="176"/>
-      <x:c r="G128" s="177"/>
-    </x:row>
-    <x:row r="129" spans="1:11">
+      <x:c r="F128" s="177"/>
+    </x:row>
+    <x:row r="129" spans="1:10">
       <x:c r="A129" s="175"/>
       <x:c r="B129" s="176"/>
       <x:c r="C129" s="176"/>
       <x:c r="D129" s="176"/>
       <x:c r="E129" s="176"/>
-      <x:c r="F129" s="176"/>
-      <x:c r="G129" s="177"/>
-    </x:row>
-    <x:row r="130" spans="1:11">
+      <x:c r="F129" s="177"/>
+    </x:row>
+    <x:row r="130" spans="1:10">
       <x:c r="A130" s="175"/>
       <x:c r="B130" s="176"/>
       <x:c r="C130" s="176"/>
       <x:c r="D130" s="176"/>
       <x:c r="E130" s="176"/>
-      <x:c r="F130" s="176"/>
-      <x:c r="G130" s="177"/>
-    </x:row>
-    <x:row r="131" spans="1:11">
+      <x:c r="F130" s="177"/>
+    </x:row>
+    <x:row r="131" spans="1:10">
       <x:c r="A131" s="175"/>
       <x:c r="B131" s="176"/>
       <x:c r="C131" s="176"/>
       <x:c r="D131" s="176"/>
       <x:c r="E131" s="176"/>
-      <x:c r="F131" s="176"/>
-      <x:c r="G131" s="177"/>
-    </x:row>
-    <x:row r="132" spans="1:11">
+      <x:c r="F131" s="177"/>
+    </x:row>
+    <x:row r="132" spans="1:10">
       <x:c r="A132" s="175"/>
       <x:c r="B132" s="176"/>
       <x:c r="C132" s="176"/>
       <x:c r="D132" s="176"/>
       <x:c r="E132" s="176"/>
-      <x:c r="F132" s="176"/>
-      <x:c r="G132" s="177"/>
-    </x:row>
-    <x:row r="133" spans="1:11">
+      <x:c r="F132" s="177"/>
+    </x:row>
+    <x:row r="133" spans="1:10">
       <x:c r="A133" s="175"/>
       <x:c r="B133" s="176"/>
       <x:c r="C133" s="176"/>
       <x:c r="D133" s="176"/>
       <x:c r="E133" s="176"/>
-      <x:c r="F133" s="176"/>
-      <x:c r="G133" s="177"/>
-    </x:row>
-    <x:row r="134" spans="1:11">
+      <x:c r="F133" s="177"/>
+    </x:row>
+    <x:row r="134" spans="1:10">
       <x:c r="A134" s="175"/>
       <x:c r="B134" s="176"/>
       <x:c r="C134" s="176"/>
       <x:c r="D134" s="176"/>
       <x:c r="E134" s="176"/>
-      <x:c r="F134" s="176"/>
-      <x:c r="G134" s="177"/>
-    </x:row>
-    <x:row r="135" spans="1:11">
+      <x:c r="F134" s="177"/>
+    </x:row>
+    <x:row r="135" spans="1:10">
       <x:c r="A135" s="175"/>
       <x:c r="B135" s="176"/>
       <x:c r="C135" s="176"/>
       <x:c r="D135" s="176"/>
       <x:c r="E135" s="176"/>
-      <x:c r="F135" s="176"/>
-      <x:c r="G135" s="177"/>
-    </x:row>
-    <x:row r="136" spans="1:11">
+      <x:c r="F135" s="177"/>
+    </x:row>
+    <x:row r="136" spans="1:10">
       <x:c r="A136" s="175"/>
       <x:c r="B136" s="176"/>
       <x:c r="C136" s="176"/>
       <x:c r="D136" s="176"/>
       <x:c r="E136" s="176"/>
-      <x:c r="F136" s="176"/>
-      <x:c r="G136" s="177"/>
-    </x:row>
-    <x:row r="137" spans="1:11">
+      <x:c r="F136" s="177"/>
+    </x:row>
+    <x:row r="137" spans="1:10">
       <x:c r="A137" s="175"/>
       <x:c r="B137" s="176"/>
       <x:c r="C137" s="176"/>
       <x:c r="D137" s="176"/>
       <x:c r="E137" s="176"/>
-      <x:c r="F137" s="176"/>
-      <x:c r="G137" s="177"/>
-    </x:row>
-    <x:row r="138" spans="1:11">
+      <x:c r="F137" s="177"/>
+    </x:row>
+    <x:row r="138" spans="1:10">
       <x:c r="A138" s="175"/>
       <x:c r="B138" s="176"/>
       <x:c r="C138" s="176"/>
       <x:c r="D138" s="176"/>
       <x:c r="E138" s="176"/>
-      <x:c r="F138" s="176"/>
-      <x:c r="G138" s="177"/>
-    </x:row>
-    <x:row r="139" spans="1:11">
+      <x:c r="F138" s="177"/>
+    </x:row>
+    <x:row r="139" spans="1:10">
       <x:c r="A139" s="175"/>
       <x:c r="B139" s="176"/>
       <x:c r="C139" s="176"/>
       <x:c r="D139" s="176"/>
       <x:c r="E139" s="176"/>
-      <x:c r="F139" s="176"/>
-      <x:c r="G139" s="177"/>
-    </x:row>
-    <x:row r="140" spans="1:11">
+      <x:c r="F139" s="177"/>
+    </x:row>
+    <x:row r="140" spans="1:10">
       <x:c r="A140" s="175"/>
       <x:c r="B140" s="176"/>
       <x:c r="C140" s="176"/>
       <x:c r="D140" s="176"/>
       <x:c r="E140" s="176"/>
-      <x:c r="F140" s="176"/>
-      <x:c r="G140" s="177"/>
-    </x:row>
-    <x:row r="141" spans="1:11">
+      <x:c r="F140" s="177"/>
+    </x:row>
+    <x:row r="141" spans="1:10">
       <x:c r="A141" s="175"/>
       <x:c r="B141" s="176"/>
       <x:c r="C141" s="176"/>
       <x:c r="D141" s="176"/>
       <x:c r="E141" s="176"/>
-      <x:c r="F141" s="176"/>
-      <x:c r="G141" s="177"/>
-    </x:row>
-    <x:row r="142" spans="1:11">
+      <x:c r="F141" s="177"/>
+    </x:row>
+    <x:row r="142" spans="1:10">
       <x:c r="A142" s="175"/>
       <x:c r="B142" s="176"/>
       <x:c r="C142" s="176"/>
       <x:c r="D142" s="176"/>
       <x:c r="E142" s="176"/>
-      <x:c r="F142" s="176"/>
-      <x:c r="G142" s="177"/>
-    </x:row>
-    <x:row r="143" spans="1:11">
+      <x:c r="F142" s="177"/>
+    </x:row>
+    <x:row r="143" spans="1:10">
       <x:c r="A143" s="175"/>
       <x:c r="B143" s="176"/>
       <x:c r="C143" s="176"/>
       <x:c r="D143" s="176"/>
       <x:c r="E143" s="176"/>
-      <x:c r="F143" s="176"/>
-      <x:c r="G143" s="177"/>
-    </x:row>
-    <x:row r="144" spans="1:11">
+      <x:c r="F143" s="177"/>
+    </x:row>
+    <x:row r="144" spans="1:10">
       <x:c r="A144" s="175"/>
       <x:c r="B144" s="176"/>
       <x:c r="C144" s="176"/>
       <x:c r="D144" s="176"/>
       <x:c r="E144" s="176"/>
-      <x:c r="F144" s="176"/>
-      <x:c r="G144" s="177"/>
-    </x:row>
-    <x:row r="145" spans="1:11">
+      <x:c r="F144" s="177"/>
+    </x:row>
+    <x:row r="145" spans="1:10">
       <x:c r="A145" s="175"/>
       <x:c r="B145" s="176"/>
       <x:c r="C145" s="176"/>
       <x:c r="D145" s="176"/>
       <x:c r="E145" s="176"/>
-      <x:c r="F145" s="176"/>
-      <x:c r="G145" s="177"/>
-    </x:row>
-    <x:row r="146" spans="1:11">
+      <x:c r="F145" s="177"/>
+    </x:row>
+    <x:row r="146" spans="1:10">
       <x:c r="A146" s="175"/>
       <x:c r="B146" s="176"/>
       <x:c r="C146" s="176"/>
       <x:c r="D146" s="176"/>
       <x:c r="E146" s="176"/>
-      <x:c r="F146" s="176"/>
-      <x:c r="G146" s="177"/>
-    </x:row>
-    <x:row r="147" spans="1:11">
+      <x:c r="F146" s="177"/>
+    </x:row>
+    <x:row r="147" spans="1:10">
       <x:c r="A147" s="175"/>
       <x:c r="B147" s="176"/>
       <x:c r="C147" s="176"/>
       <x:c r="D147" s="176"/>
       <x:c r="E147" s="176"/>
-      <x:c r="F147" s="176"/>
-      <x:c r="G147" s="177"/>
-    </x:row>
-    <x:row r="148" spans="1:11">
+      <x:c r="F147" s="177"/>
+    </x:row>
+    <x:row r="148" spans="1:10">
       <x:c r="A148" s="175"/>
       <x:c r="B148" s="176"/>
       <x:c r="C148" s="176"/>
       <x:c r="D148" s="176"/>
       <x:c r="E148" s="176"/>
-      <x:c r="F148" s="176"/>
-      <x:c r="G148" s="177"/>
-    </x:row>
-    <x:row r="149" spans="1:11">
+      <x:c r="F148" s="177"/>
+    </x:row>
+    <x:row r="149" spans="1:10">
       <x:c r="A149" s="175"/>
       <x:c r="B149" s="176"/>
       <x:c r="C149" s="176"/>
       <x:c r="D149" s="176"/>
       <x:c r="E149" s="176"/>
-      <x:c r="F149" s="176"/>
-      <x:c r="G149" s="177"/>
-    </x:row>
-    <x:row r="150" spans="1:11">
+      <x:c r="F149" s="177"/>
+    </x:row>
+    <x:row r="150" spans="1:10">
       <x:c r="A150" s="175"/>
       <x:c r="B150" s="176"/>
       <x:c r="C150" s="176"/>
       <x:c r="D150" s="176"/>
       <x:c r="E150" s="176"/>
-      <x:c r="F150" s="176"/>
-      <x:c r="G150" s="177"/>
-    </x:row>
-    <x:row r="151" spans="1:11">
+      <x:c r="F150" s="177"/>
+    </x:row>
+    <x:row r="151" spans="1:10">
       <x:c r="A151" s="175"/>
       <x:c r="B151" s="176"/>
       <x:c r="C151" s="176"/>
       <x:c r="D151" s="176"/>
       <x:c r="E151" s="176"/>
-      <x:c r="F151" s="176"/>
-      <x:c r="G151" s="177"/>
-    </x:row>
-    <x:row r="152" spans="1:11">
+      <x:c r="F151" s="177"/>
+    </x:row>
+    <x:row r="152" spans="1:10">
       <x:c r="A152" s="175"/>
       <x:c r="B152" s="176"/>
       <x:c r="C152" s="176"/>
       <x:c r="D152" s="176"/>
       <x:c r="E152" s="176"/>
-      <x:c r="F152" s="176"/>
-      <x:c r="G152" s="177"/>
-    </x:row>
-    <x:row r="153" spans="1:11">
+      <x:c r="F152" s="177"/>
+    </x:row>
+    <x:row r="153" spans="1:10">
       <x:c r="A153" s="175"/>
       <x:c r="B153" s="176"/>
       <x:c r="C153" s="176"/>
       <x:c r="D153" s="176"/>
       <x:c r="E153" s="176"/>
-      <x:c r="F153" s="176"/>
-      <x:c r="G153" s="177"/>
-    </x:row>
-    <x:row r="154" spans="1:11">
+      <x:c r="F153" s="177"/>
+    </x:row>
+    <x:row r="154" spans="1:10">
       <x:c r="A154" s="175"/>
       <x:c r="B154" s="176"/>
       <x:c r="C154" s="176"/>
       <x:c r="D154" s="176"/>
       <x:c r="E154" s="176"/>
-      <x:c r="F154" s="176"/>
-      <x:c r="G154" s="177"/>
-    </x:row>
-    <x:row r="155" spans="1:11">
+      <x:c r="F154" s="177"/>
+    </x:row>
+    <x:row r="155" spans="1:10">
       <x:c r="A155" s="175"/>
       <x:c r="B155" s="176"/>
       <x:c r="C155" s="176"/>
       <x:c r="D155" s="176"/>
       <x:c r="E155" s="176"/>
-      <x:c r="F155" s="176"/>
-      <x:c r="G155" s="177"/>
-    </x:row>
-    <x:row r="156" spans="1:11">
+      <x:c r="F155" s="177"/>
+    </x:row>
+    <x:row r="156" spans="1:10">
       <x:c r="A156" s="175"/>
       <x:c r="B156" s="176"/>
       <x:c r="C156" s="176"/>
       <x:c r="D156" s="176"/>
       <x:c r="E156" s="176"/>
-      <x:c r="F156" s="176"/>
-      <x:c r="G156" s="177"/>
-    </x:row>
-    <x:row r="157" spans="1:11">
+      <x:c r="F156" s="177"/>
+    </x:row>
+    <x:row r="157" spans="1:10">
       <x:c r="A157" s="175"/>
       <x:c r="B157" s="176"/>
       <x:c r="C157" s="176"/>
       <x:c r="D157" s="176"/>
       <x:c r="E157" s="176"/>
-      <x:c r="F157" s="176"/>
-      <x:c r="G157" s="177"/>
-    </x:row>
-    <x:row r="158" spans="1:11">
+      <x:c r="F157" s="177"/>
+    </x:row>
+    <x:row r="158" spans="1:10">
       <x:c r="A158" s="175"/>
       <x:c r="B158" s="176"/>
       <x:c r="C158" s="176"/>
       <x:c r="D158" s="176"/>
       <x:c r="E158" s="176"/>
-      <x:c r="F158" s="176"/>
-      <x:c r="G158" s="177"/>
-    </x:row>
-    <x:row r="159" spans="1:11">
+      <x:c r="F158" s="177"/>
+    </x:row>
+    <x:row r="159" spans="1:10">
       <x:c r="A159" s="175"/>
       <x:c r="B159" s="176"/>
       <x:c r="C159" s="176"/>
       <x:c r="D159" s="176"/>
       <x:c r="E159" s="176"/>
-      <x:c r="F159" s="176"/>
-      <x:c r="G159" s="177"/>
-    </x:row>
-    <x:row r="160" spans="1:11">
+      <x:c r="F159" s="177"/>
+    </x:row>
+    <x:row r="160" spans="1:10">
       <x:c r="A160" s="175"/>
       <x:c r="B160" s="176"/>
       <x:c r="C160" s="176"/>
       <x:c r="D160" s="176"/>
       <x:c r="E160" s="176"/>
-      <x:c r="F160" s="176"/>
-      <x:c r="G160" s="177"/>
-    </x:row>
-    <x:row r="161" spans="1:11">
+      <x:c r="F160" s="177"/>
+    </x:row>
+    <x:row r="161" spans="1:10">
       <x:c r="A161" s="175"/>
       <x:c r="B161" s="176"/>
       <x:c r="C161" s="176"/>
       <x:c r="D161" s="176"/>
       <x:c r="E161" s="176"/>
-      <x:c r="F161" s="176"/>
-      <x:c r="G161" s="177"/>
-    </x:row>
-    <x:row r="162" spans="1:11">
+      <x:c r="F161" s="177"/>
+    </x:row>
+    <x:row r="162" spans="1:10">
       <x:c r="A162" s="175"/>
       <x:c r="B162" s="176"/>
       <x:c r="C162" s="176"/>
       <x:c r="D162" s="176"/>
       <x:c r="E162" s="176"/>
-      <x:c r="F162" s="176"/>
-      <x:c r="G162" s="177"/>
-    </x:row>
-    <x:row r="163" spans="1:11">
+      <x:c r="F162" s="177"/>
+    </x:row>
+    <x:row r="163" spans="1:10">
       <x:c r="A163" s="175"/>
       <x:c r="B163" s="176"/>
       <x:c r="C163" s="176"/>
       <x:c r="D163" s="176"/>
       <x:c r="E163" s="176"/>
-      <x:c r="F163" s="176"/>
-      <x:c r="G163" s="177"/>
-    </x:row>
-    <x:row r="164" spans="1:11">
+      <x:c r="F163" s="177"/>
+    </x:row>
+    <x:row r="164" spans="1:10">
       <x:c r="A164" s="175"/>
       <x:c r="B164" s="176"/>
       <x:c r="C164" s="176"/>
       <x:c r="D164" s="176"/>
       <x:c r="E164" s="176"/>
-      <x:c r="F164" s="176"/>
-      <x:c r="G164" s="177"/>
-    </x:row>
-    <x:row r="165" spans="1:11">
+      <x:c r="F164" s="177"/>
+    </x:row>
+    <x:row r="165" spans="1:10">
       <x:c r="A165" s="175"/>
       <x:c r="B165" s="176"/>
       <x:c r="C165" s="176"/>
       <x:c r="D165" s="176"/>
       <x:c r="E165" s="176"/>
-      <x:c r="F165" s="176"/>
-      <x:c r="G165" s="177"/>
-    </x:row>
-    <x:row r="166" spans="1:11">
+      <x:c r="F165" s="177"/>
+    </x:row>
+    <x:row r="166" spans="1:10">
       <x:c r="A166" s="175"/>
       <x:c r="B166" s="176"/>
       <x:c r="C166" s="176"/>
       <x:c r="D166" s="176"/>
       <x:c r="E166" s="176"/>
-      <x:c r="F166" s="176"/>
-      <x:c r="G166" s="177"/>
-    </x:row>
-    <x:row r="167" spans="1:11">
+      <x:c r="F166" s="177"/>
+    </x:row>
+    <x:row r="167" spans="1:10">
       <x:c r="A167" s="175"/>
       <x:c r="B167" s="176"/>
       <x:c r="C167" s="176"/>
       <x:c r="D167" s="176"/>
       <x:c r="E167" s="176"/>
-      <x:c r="F167" s="176"/>
-      <x:c r="G167" s="177"/>
-    </x:row>
-    <x:row r="168" spans="1:11">
+      <x:c r="F167" s="177"/>
+    </x:row>
+    <x:row r="168" spans="1:10">
       <x:c r="A168" s="175"/>
       <x:c r="B168" s="176"/>
       <x:c r="C168" s="176"/>
       <x:c r="D168" s="176"/>
       <x:c r="E168" s="176"/>
-      <x:c r="F168" s="176"/>
-      <x:c r="G168" s="177"/>
-    </x:row>
-    <x:row r="169" spans="1:11">
+      <x:c r="F168" s="177"/>
+    </x:row>
+    <x:row r="169" spans="1:10">
       <x:c r="A169" s="175"/>
       <x:c r="B169" s="176"/>
       <x:c r="C169" s="176"/>
       <x:c r="D169" s="176"/>
       <x:c r="E169" s="176"/>
-      <x:c r="F169" s="176"/>
-      <x:c r="G169" s="177"/>
-    </x:row>
-    <x:row r="170" spans="1:11">
+      <x:c r="F169" s="177"/>
+    </x:row>
+    <x:row r="170" spans="1:10">
       <x:c r="A170" s="175"/>
       <x:c r="B170" s="176"/>
       <x:c r="C170" s="176"/>
       <x:c r="D170" s="176"/>
       <x:c r="E170" s="176"/>
-      <x:c r="F170" s="176"/>
-      <x:c r="G170" s="177"/>
-    </x:row>
-    <x:row r="171" spans="1:11">
+      <x:c r="F170" s="177"/>
+    </x:row>
+    <x:row r="171" spans="1:10">
       <x:c r="A171" s="175"/>
       <x:c r="B171" s="176"/>
       <x:c r="C171" s="176"/>
       <x:c r="D171" s="176"/>
       <x:c r="E171" s="176"/>
-      <x:c r="F171" s="176"/>
-      <x:c r="G171" s="177"/>
-    </x:row>
-    <x:row r="172" spans="1:11">
+      <x:c r="F171" s="177"/>
+    </x:row>
+    <x:row r="172" spans="1:10">
       <x:c r="A172" s="175"/>
       <x:c r="B172" s="176"/>
       <x:c r="C172" s="176"/>
       <x:c r="D172" s="176"/>
       <x:c r="E172" s="176"/>
-      <x:c r="F172" s="176"/>
-      <x:c r="G172" s="177"/>
-    </x:row>
-    <x:row r="173" spans="1:11">
+      <x:c r="F172" s="177"/>
+    </x:row>
+    <x:row r="173" spans="1:10">
       <x:c r="A173" s="175"/>
       <x:c r="B173" s="176"/>
       <x:c r="C173" s="176"/>
       <x:c r="D173" s="176"/>
       <x:c r="E173" s="176"/>
-      <x:c r="F173" s="176"/>
-      <x:c r="G173" s="177"/>
-    </x:row>
-    <x:row r="174" spans="1:11">
+      <x:c r="F173" s="177"/>
+    </x:row>
+    <x:row r="174" spans="1:10">
       <x:c r="A174" s="175"/>
       <x:c r="B174" s="176"/>
       <x:c r="C174" s="176"/>
       <x:c r="D174" s="176"/>
       <x:c r="E174" s="176"/>
-      <x:c r="F174" s="176"/>
-      <x:c r="G174" s="177"/>
-    </x:row>
-    <x:row r="175" spans="1:11">
+      <x:c r="F174" s="177"/>
+    </x:row>
+    <x:row r="175" spans="1:10">
       <x:c r="A175" s="175"/>
       <x:c r="B175" s="176"/>
       <x:c r="C175" s="176"/>
       <x:c r="D175" s="176"/>
       <x:c r="E175" s="176"/>
-      <x:c r="F175" s="176"/>
-      <x:c r="G175" s="177"/>
-    </x:row>
-    <x:row r="176" spans="1:11">
+      <x:c r="F175" s="177"/>
+    </x:row>
+    <x:row r="176" spans="1:10">
       <x:c r="A176" s="175"/>
       <x:c r="B176" s="176"/>
       <x:c r="C176" s="176"/>
       <x:c r="D176" s="176"/>
       <x:c r="E176" s="176"/>
-      <x:c r="F176" s="176"/>
-      <x:c r="G176" s="177"/>
-    </x:row>
-    <x:row r="177" spans="1:11">
+      <x:c r="F176" s="177"/>
+    </x:row>
+    <x:row r="177" spans="1:10">
       <x:c r="A177" s="175"/>
       <x:c r="B177" s="176"/>
       <x:c r="C177" s="176"/>
       <x:c r="D177" s="176"/>
       <x:c r="E177" s="176"/>
-      <x:c r="F177" s="176"/>
-      <x:c r="G177" s="177"/>
-    </x:row>
-    <x:row r="178" spans="1:11">
+      <x:c r="F177" s="177"/>
+    </x:row>
+    <x:row r="178" spans="1:10">
       <x:c r="A178" s="175"/>
       <x:c r="B178" s="176"/>
       <x:c r="C178" s="176"/>
       <x:c r="D178" s="176"/>
       <x:c r="E178" s="176"/>
-      <x:c r="F178" s="176"/>
-      <x:c r="G178" s="177"/>
-    </x:row>
-    <x:row r="179" spans="1:11">
+      <x:c r="F178" s="177"/>
+    </x:row>
+    <x:row r="179" spans="1:10">
       <x:c r="A179" s="175"/>
       <x:c r="B179" s="176"/>
       <x:c r="C179" s="176"/>
       <x:c r="D179" s="176"/>
       <x:c r="E179" s="176"/>
-      <x:c r="F179" s="176"/>
-      <x:c r="G179" s="177"/>
-    </x:row>
-    <x:row r="180" spans="1:11">
+      <x:c r="F179" s="177"/>
+    </x:row>
+    <x:row r="180" spans="1:10">
       <x:c r="A180" s="175"/>
       <x:c r="B180" s="176"/>
       <x:c r="C180" s="176"/>
       <x:c r="D180" s="176"/>
       <x:c r="E180" s="176"/>
-      <x:c r="F180" s="176"/>
-      <x:c r="G180" s="177"/>
-    </x:row>
-    <x:row r="181" spans="1:11">
+      <x:c r="F180" s="177"/>
+    </x:row>
+    <x:row r="181" spans="1:10">
       <x:c r="A181" s="175"/>
       <x:c r="B181" s="176"/>
       <x:c r="C181" s="176"/>
       <x:c r="D181" s="176"/>
       <x:c r="E181" s="176"/>
-      <x:c r="F181" s="176"/>
-      <x:c r="G181" s="177"/>
-    </x:row>
-    <x:row r="182" spans="1:11">
+      <x:c r="F181" s="177"/>
+    </x:row>
+    <x:row r="182" spans="1:10">
       <x:c r="A182" s="175"/>
       <x:c r="B182" s="176"/>
       <x:c r="C182" s="176"/>
       <x:c r="D182" s="176"/>
       <x:c r="E182" s="176"/>
-      <x:c r="F182" s="176"/>
-      <x:c r="G182" s="177"/>
-    </x:row>
-    <x:row r="183" spans="1:11">
+      <x:c r="F182" s="177"/>
+    </x:row>
+    <x:row r="183" spans="1:10">
       <x:c r="A183" s="175"/>
       <x:c r="B183" s="176"/>
       <x:c r="C183" s="176"/>
       <x:c r="D183" s="176"/>
       <x:c r="E183" s="176"/>
-      <x:c r="F183" s="176"/>
-      <x:c r="G183" s="177"/>
-    </x:row>
-    <x:row r="184" spans="1:11">
+      <x:c r="F183" s="177"/>
+    </x:row>
+    <x:row r="184" spans="1:10">
       <x:c r="A184" s="175"/>
       <x:c r="B184" s="176"/>
       <x:c r="C184" s="176"/>
       <x:c r="D184" s="176"/>
       <x:c r="E184" s="176"/>
-      <x:c r="F184" s="176"/>
-      <x:c r="G184" s="177"/>
-    </x:row>
-    <x:row r="185" spans="1:11">
+      <x:c r="F184" s="177"/>
+    </x:row>
+    <x:row r="185" spans="1:10">
       <x:c r="A185" s="175"/>
       <x:c r="B185" s="176"/>
       <x:c r="C185" s="176"/>
       <x:c r="D185" s="176"/>
       <x:c r="E185" s="176"/>
-      <x:c r="F185" s="176"/>
-      <x:c r="G185" s="177"/>
-    </x:row>
-    <x:row r="186" spans="1:11">
+      <x:c r="F185" s="177"/>
+    </x:row>
+    <x:row r="186" spans="1:10">
       <x:c r="A186" s="175"/>
       <x:c r="B186" s="176"/>
       <x:c r="C186" s="176"/>
       <x:c r="D186" s="176"/>
       <x:c r="E186" s="176"/>
-      <x:c r="F186" s="176"/>
-      <x:c r="G186" s="177"/>
-    </x:row>
-    <x:row r="187" spans="1:11">
+      <x:c r="F186" s="177"/>
+    </x:row>
+    <x:row r="187" spans="1:10">
       <x:c r="A187" s="175"/>
       <x:c r="B187" s="176"/>
       <x:c r="C187" s="176"/>
       <x:c r="D187" s="176"/>
       <x:c r="E187" s="176"/>
-      <x:c r="F187" s="176"/>
-      <x:c r="G187" s="177"/>
-    </x:row>
-    <x:row r="188" spans="1:11">
+      <x:c r="F187" s="177"/>
+    </x:row>
+    <x:row r="188" spans="1:10">
       <x:c r="A188" s="175"/>
       <x:c r="B188" s="176"/>
       <x:c r="C188" s="176"/>
       <x:c r="D188" s="176"/>
       <x:c r="E188" s="176"/>
-      <x:c r="F188" s="176"/>
-      <x:c r="G188" s="177"/>
-    </x:row>
-    <x:row r="189" spans="1:11">
+      <x:c r="F188" s="177"/>
+    </x:row>
+    <x:row r="189" spans="1:10">
       <x:c r="A189" s="175"/>
       <x:c r="B189" s="176"/>
       <x:c r="C189" s="176"/>
       <x:c r="D189" s="176"/>
       <x:c r="E189" s="176"/>
-      <x:c r="F189" s="176"/>
-      <x:c r="G189" s="177"/>
-    </x:row>
-    <x:row r="190" spans="1:11">
+      <x:c r="F189" s="177"/>
+    </x:row>
+    <x:row r="190" spans="1:10">
       <x:c r="A190" s="175"/>
       <x:c r="B190" s="176"/>
       <x:c r="C190" s="176"/>
       <x:c r="D190" s="176"/>
       <x:c r="E190" s="176"/>
-      <x:c r="F190" s="176"/>
-      <x:c r="G190" s="177"/>
-    </x:row>
-    <x:row r="191" spans="1:11">
+      <x:c r="F190" s="177"/>
+    </x:row>
+    <x:row r="191" spans="1:10">
       <x:c r="A191" s="175"/>
       <x:c r="B191" s="176"/>
       <x:c r="C191" s="176"/>
       <x:c r="D191" s="176"/>
       <x:c r="E191" s="176"/>
-      <x:c r="F191" s="176"/>
-      <x:c r="G191" s="177"/>
-    </x:row>
-    <x:row r="192" spans="1:11">
+      <x:c r="F191" s="177"/>
+    </x:row>
+    <x:row r="192" spans="1:10">
       <x:c r="A192" s="175"/>
       <x:c r="B192" s="176"/>
       <x:c r="C192" s="176"/>
       <x:c r="D192" s="176"/>
       <x:c r="E192" s="176"/>
-      <x:c r="F192" s="176"/>
-      <x:c r="G192" s="177"/>
-    </x:row>
-    <x:row r="193" spans="1:11">
+      <x:c r="F192" s="177"/>
+    </x:row>
+    <x:row r="193" spans="1:10">
       <x:c r="A193" s="175"/>
       <x:c r="B193" s="176"/>
       <x:c r="C193" s="176"/>
       <x:c r="D193" s="176"/>
       <x:c r="E193" s="176"/>
-      <x:c r="F193" s="176"/>
-      <x:c r="G193" s="177"/>
-    </x:row>
-    <x:row r="194" spans="1:11">
+      <x:c r="F193" s="177"/>
+    </x:row>
+    <x:row r="194" spans="1:10">
       <x:c r="A194" s="175"/>
       <x:c r="B194" s="176"/>
       <x:c r="C194" s="176"/>
       <x:c r="D194" s="176"/>
       <x:c r="E194" s="176"/>
-      <x:c r="F194" s="176"/>
-      <x:c r="G194" s="177"/>
-    </x:row>
-    <x:row r="195" spans="1:11">
+      <x:c r="F194" s="177"/>
+    </x:row>
+    <x:row r="195" spans="1:10">
       <x:c r="A195" s="175"/>
       <x:c r="B195" s="176"/>
       <x:c r="C195" s="176"/>
       <x:c r="D195" s="176"/>
       <x:c r="E195" s="176"/>
-      <x:c r="F195" s="176"/>
-      <x:c r="G195" s="177"/>
-    </x:row>
-    <x:row r="196" spans="1:11">
+      <x:c r="F195" s="177"/>
+    </x:row>
+    <x:row r="196" spans="1:10">
       <x:c r="A196" s="175"/>
       <x:c r="B196" s="176"/>
       <x:c r="C196" s="176"/>
       <x:c r="D196" s="176"/>
       <x:c r="E196" s="176"/>
-      <x:c r="F196" s="176"/>
-      <x:c r="G196" s="177"/>
-    </x:row>
-    <x:row r="197" spans="1:11">
+      <x:c r="F196" s="177"/>
+    </x:row>
+    <x:row r="197" spans="1:10">
       <x:c r="A197" s="175"/>
       <x:c r="B197" s="176"/>
       <x:c r="C197" s="176"/>
       <x:c r="D197" s="176"/>
       <x:c r="E197" s="176"/>
-      <x:c r="F197" s="176"/>
-      <x:c r="G197" s="177"/>
-    </x:row>
-    <x:row r="198" spans="1:11">
+      <x:c r="F197" s="177"/>
+    </x:row>
+    <x:row r="198" spans="1:10">
       <x:c r="A198" s="175"/>
       <x:c r="B198" s="176"/>
       <x:c r="C198" s="176"/>
       <x:c r="D198" s="176"/>
       <x:c r="E198" s="176"/>
-      <x:c r="F198" s="176"/>
-      <x:c r="G198" s="177"/>
-    </x:row>
-    <x:row r="199" spans="1:11">
+      <x:c r="F198" s="177"/>
+    </x:row>
+    <x:row r="199" spans="1:10">
       <x:c r="A199" s="175"/>
       <x:c r="B199" s="176"/>
       <x:c r="C199" s="176"/>
       <x:c r="D199" s="176"/>
       <x:c r="E199" s="176"/>
-      <x:c r="F199" s="176"/>
-      <x:c r="G199" s="177"/>
-    </x:row>
-    <x:row r="200" spans="1:11">
+      <x:c r="F199" s="177"/>
+    </x:row>
+    <x:row r="200" spans="1:10">
       <x:c r="A200" s="175"/>
       <x:c r="B200" s="176"/>
       <x:c r="C200" s="176"/>
       <x:c r="D200" s="176"/>
       <x:c r="E200" s="176"/>
-      <x:c r="F200" s="176"/>
-      <x:c r="G200" s="177"/>
+      <x:c r="F200" s="177"/>
     </x:row>
   </x:sheetData>
-  <x:autoFilter ref="A1:G7"/>
+  <x:autoFilter ref="A1:F7"/>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
@@ -3870,16 +3675,16 @@
         </x:is>
       </x:c>
       <x:c r="C1" s="170" t="s">
-        <x:v>0</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D1" s="170" t="s">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E1" s="170" t="s">
-        <x:v>2</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F1" s="170" t="s">
-        <x:v>3</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G1" s="170" t="inlineStr">
         <x:is>
@@ -3887,7 +3692,7 @@
         </x:is>
       </x:c>
       <x:c r="H1" s="178" t="s">
-        <x:v>4</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="I1" s="178"/>
       <x:c r="J1" s="178"/>
@@ -3906,7 +3711,7 @@
       </x:c>
       <x:c r="C2" s="180"/>
       <x:c r="D2" s="173" t="s">
-        <x:v>5</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E2" s="173"/>
       <x:c r="F2" s="172"/>
@@ -3927,9 +3732,11 @@
           <x:t>branch05.02A</x:t>
         </x:is>
       </x:c>
-      <x:c r="C3" s="180"/>
+      <x:c r="C3" s="180" t="s">
+        <x:v>9</x:v>
+      </x:c>
       <x:c r="D3" s="173" t="s">
-        <x:v>6</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E3" s="173"/>
       <x:c r="F3" s="172" t="inlineStr">
@@ -3958,9 +3765,11 @@
           <x:t>main05.03</x:t>
         </x:is>
       </x:c>
-      <x:c r="C4" s="180"/>
+      <x:c r="C4" s="180" t="s">
+        <x:v>9</x:v>
+      </x:c>
       <x:c r="D4" s="173" t="s">
-        <x:v>7</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="E4" s="173"/>
       <x:c r="F4" s="172"/>
@@ -3983,7 +3792,7 @@
       </x:c>
       <x:c r="C5" s="180"/>
       <x:c r="D5" s="173" t="s">
-        <x:v>5</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E5" s="173"/>
       <x:c r="F5" s="172"/>
@@ -4006,13 +3815,13 @@
       </x:c>
       <x:c r="C6" s="180"/>
       <x:c r="D6" s="173" t="s">
-        <x:v>5</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E6" s="173"/>
       <x:c r="F6" s="172"/>
       <x:c r="G6" s="173"/>
       <x:c r="H6" s="177" t="s">
-        <x:v>8</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="I6" s="176"/>
       <x:c r="J6" s="176"/>
@@ -6581,13 +6390,13 @@
         </x:is>
       </x:c>
       <x:c r="B1" s="181" t="s">
-        <x:v>9</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C1" s="181" t="s">
-        <x:v>10</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D1" s="181" t="s">
-        <x:v>11</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E1" s="181" t="inlineStr">
         <x:is>
@@ -6607,13 +6416,13 @@
         </x:is>
       </x:c>
       <x:c r="B2" s="179" t="s">
-        <x:v>12</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C2" s="172" t="s">
-        <x:v>13</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D2" s="172" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="E2" s="174" t="inlineStr">
         <x:is>
@@ -6628,13 +6437,13 @@
         </x:is>
       </x:c>
       <x:c r="B3" s="179" t="s">
-        <x:v>15</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C3" s="172" t="s">
-        <x:v>13</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D3" s="172" t="s">
-        <x:v>16</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="E3" s="174" t="inlineStr">
         <x:is>
@@ -6667,17 +6476,15 @@
           <x:t>복도완료</x:t>
         </x:is>
       </x:c>
-      <x:c r="B5" s="179" t="inlineStr">
-        <x:is>
-          <x:t>cleared:main05.02</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C5" s="172"/>
+      <x:c r="B5" s="179" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C5" s="172" t="s">
+        <x:v>22</x:v>
+      </x:c>
       <x:c r="D5" s="172"/>
-      <x:c r="E5" s="174" t="inlineStr">
-        <x:is>
-          <x:t>해당 에피소드 클리어 여부</x:t>
-        </x:is>
+      <x:c r="E5" s="174" t="s">
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:7">
@@ -8112,11 +7919,11 @@
         </x:is>
       </x:c>
       <x:c r="F1" s="183" t="s">
-        <x:v>17</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="G1" s="10"/>
       <x:c r="H1" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:8">
@@ -8186,12 +7993,20 @@
       <x:c r="F4" s="187"/>
     </x:row>
     <x:row r="5" spans="1:8">
-      <x:c r="A5" s="188"/>
-      <x:c r="B5" s="187"/>
-      <x:c r="C5" s="187"/>
+      <x:c r="A5" s="188" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B5" s="187" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C5" s="187" t="s">
+        <x:v>27</x:v>
+      </x:c>
       <x:c r="D5" s="187"/>
       <x:c r="E5" s="187"/>
-      <x:c r="F5" s="187"/>
+      <x:c r="F5" s="187" t="s">
+        <x:v>28</x:v>
+      </x:c>
     </x:row>
     <x:row r="6" spans="1:8">
       <x:c r="A6" s="188"/>
@@ -11507,143 +11322,143 @@
   <x:sheetData>
     <x:row r="1" spans="1:11">
       <x:c r="A1" s="169" t="s">
-        <x:v>19</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B1" s="169" t="s">
-        <x:v>20</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C1" s="169" t="s">
-        <x:v>21</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D1" s="168" t="s">
-        <x:v>22</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E1" s="169" t="s">
-        <x:v>23</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="F1" s="169" t="s">
-        <x:v>24</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:11">
       <x:c r="C2" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D2" s="167" t="s">
-        <x:v>26</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E2" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="F2" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:11">
       <x:c r="C3" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D3" s="167" t="s">
-        <x:v>30</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E3" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>42</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:11">
       <x:c r="A4" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D4" s="167"/>
     </x:row>
     <x:row r="5" spans="1:11">
       <x:c r="C5" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="D5" s="167" t="s">
-        <x:v>36</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E5" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="F5" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:11">
       <x:c r="A6" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D6" s="167"/>
     </x:row>
     <x:row r="7" spans="1:11">
       <x:c r="C7" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D7" s="167" t="s">
-        <x:v>40</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E7" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="F7" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:11">
       <x:c r="A8" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:11">
       <x:c r="A9" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="D9" s="167"/>
     </x:row>
     <x:row r="10" spans="1:11">
       <x:c r="C10" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D10" s="167" t="s">
-        <x:v>46</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E10" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="F10" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>57</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:11">
       <x:c r="A11" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:11">
       <x:c r="C12" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="D12" s="167" t="s">
-        <x:v>49</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E12" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="F12" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>60</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -11672,7 +11487,7 @@
   <x:sheetData>
     <x:row r="1" spans="1:3">
       <x:c r="B1" s="43" t="s">
-        <x:v>51</x:v>
+        <x:v>61</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:3">
@@ -11725,7 +11540,7 @@
         </x:is>
       </x:c>
       <x:c r="C7" s="45" t="s">
-        <x:v>52</x:v>
+        <x:v>62</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:3">
@@ -11809,12 +11624,12 @@
         </x:is>
       </x:c>
       <x:c r="C17" s="166" t="s">
-        <x:v>53</x:v>
+        <x:v>63</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="B19" s="46" t="s">
-        <x:v>54</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:3">
@@ -11824,7 +11639,7 @@
         </x:is>
       </x:c>
       <x:c r="C20" s="45" t="s">
-        <x:v>55</x:v>
+        <x:v>65</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:3">
@@ -11853,7 +11668,7 @@
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="B24" s="46" t="s">
-        <x:v>56</x:v>
+        <x:v>66</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:3">
@@ -11863,7 +11678,7 @@
         </x:is>
       </x:c>
       <x:c r="C25" s="45" t="s">
-        <x:v>57</x:v>
+        <x:v>67</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:3">
@@ -12094,13 +11909,13 @@
   <x:sheetData>
     <x:row r="1" spans="1:3">
       <x:c r="A1" s="195" t="s">
-        <x:v>21</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B1" s="195" t="s">
-        <x:v>58</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C1" s="195" t="s">
-        <x:v>59</x:v>
+        <x:v>69</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:3">
@@ -12108,7 +11923,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B2" s="176" t="s">
-        <x:v>6</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C2" s="177"/>
     </x:row>
@@ -12117,7 +11932,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B3" s="176" t="s">
-        <x:v>7</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C3" s="177"/>
     </x:row>
